--- a/26-27_Admin_Calendar_Events_CTE-LL_Version.xlsx
+++ b/26-27_Admin_Calendar_Events_CTE-LL_Version.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lausd.sharepoint.com/teams/CTE-LLLeadership/Shared Documents/Calendaring/CTELL_Calendar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{AFEB7EE0-A3A0-BE46-B68A-F48D580478B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0886A684-F525-F04D-B5F3-C795F5885A2A}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{AFEB7EE0-A3A0-BE46-B68A-F48D580478B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E637176-F9E3-F14C-A248-07011BE82A2E}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="LinkedLearning" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'26-27_Events'!$A$1:$M$198</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'26-27_Events'!$A$1:$M$209</definedName>
     <definedName name="Z_8F656852_D603_4744_997A_DE0F92A7585E_.wvu.FilterData" localSheetId="0" hidden="1">'26-27_Events'!$A$1:$M$198</definedName>
   </definedNames>
   <calcPr calcId="0" iterateDelta="1E-4"/>
@@ -1469,7 +1469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1563,32 +1563,29 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="169" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -2697,7 +2694,7 @@
         <v>0.4375</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="F13" s="15"/>
       <c r="G13" s="19" t="s">
@@ -3427,7 +3424,7 @@
       <c r="K28" s="43" t="s">
         <v>307</v>
       </c>
-      <c r="L28" s="51"/>
+      <c r="L28" s="50"/>
       <c r="M28" s="15" t="s">
         <v>83</v>
       </c>
@@ -3651,7 +3648,7 @@
         <v>0.4375</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="F33" s="15"/>
       <c r="G33" s="19" t="s">
@@ -4198,7 +4195,7 @@
       <c r="J44" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="K44" s="49" t="s">
+      <c r="K44" s="24" t="s">
         <v>40</v>
       </c>
       <c r="L44" s="15"/>
@@ -4495,7 +4492,7 @@
       <c r="K50" s="43" t="s">
         <v>309</v>
       </c>
-      <c r="L50" s="51"/>
+      <c r="L50" s="50"/>
       <c r="M50" s="15" t="s">
         <v>83</v>
       </c>
@@ -4577,7 +4574,7 @@
         <v>0.4375</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="F52" s="15"/>
       <c r="G52" s="19" t="s">
@@ -5125,7 +5122,7 @@
       <c r="K63" s="43" t="s">
         <v>310</v>
       </c>
-      <c r="L63" s="51"/>
+      <c r="L63" s="50"/>
       <c r="M63" s="15" t="s">
         <v>83</v>
       </c>
@@ -5449,7 +5446,7 @@
         <v>0.4375</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="F70" s="15"/>
       <c r="G70" s="19" t="s">
@@ -6073,7 +6070,7 @@
       <c r="K83" s="43" t="s">
         <v>310</v>
       </c>
-      <c r="L83" s="51"/>
+      <c r="L83" s="50"/>
       <c r="M83" s="15" t="s">
         <v>83</v>
       </c>
@@ -6255,7 +6252,7 @@
         <v>0.4375</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="F87" s="15"/>
       <c r="G87" s="19" t="s">
@@ -6699,7 +6696,7 @@
         <v>0.4375</v>
       </c>
       <c r="E96" s="15" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="F96" s="15"/>
       <c r="G96" s="19" t="s">
@@ -7161,7 +7158,7 @@
       <c r="K105" s="43" t="s">
         <v>310</v>
       </c>
-      <c r="L105" s="51"/>
+      <c r="L105" s="50"/>
       <c r="M105" s="15" t="s">
         <v>83</v>
       </c>
@@ -7315,7 +7312,7 @@
       <c r="K108" s="43" t="s">
         <v>310</v>
       </c>
-      <c r="L108" s="51"/>
+      <c r="L108" s="50"/>
       <c r="M108" s="15" t="s">
         <v>83</v>
       </c>
@@ -7349,7 +7346,7 @@
         <v>0.4375</v>
       </c>
       <c r="E109" s="15" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="F109" s="15"/>
       <c r="G109" s="19" t="s">
@@ -8083,7 +8080,7 @@
       <c r="K124" s="43" t="s">
         <v>310</v>
       </c>
-      <c r="L124" s="51"/>
+      <c r="L124" s="50"/>
       <c r="M124" s="15" t="s">
         <v>83</v>
       </c>
@@ -8117,7 +8114,7 @@
         <v>0.4375</v>
       </c>
       <c r="E125" s="15" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="F125" s="15"/>
       <c r="G125" s="19" t="s">
@@ -9089,7 +9086,7 @@
       <c r="K145" s="43" t="s">
         <v>310</v>
       </c>
-      <c r="L145" s="51"/>
+      <c r="L145" s="50"/>
       <c r="M145" s="15" t="s">
         <v>83</v>
       </c>
@@ -9413,7 +9410,7 @@
         <v>0.4375</v>
       </c>
       <c r="E152" s="15" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="F152" s="15"/>
       <c r="G152" s="19" t="s">
@@ -9853,7 +9850,7 @@
         <v>0.4375</v>
       </c>
       <c r="E161" s="15" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="F161" s="15"/>
       <c r="G161" s="19" t="s">
@@ -10169,7 +10166,7 @@
       <c r="K167" s="43" t="s">
         <v>310</v>
       </c>
-      <c r="L167" s="51"/>
+      <c r="L167" s="50"/>
       <c r="M167" s="15" t="s">
         <v>83</v>
       </c>
@@ -10489,7 +10486,7 @@
         <v>0.4375</v>
       </c>
       <c r="E175" s="15" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="F175" s="15"/>
       <c r="G175" s="19" t="s">
@@ -10747,7 +10744,7 @@
       <c r="K183" s="43" t="s">
         <v>310</v>
       </c>
-      <c r="L183" s="51"/>
+      <c r="L183" s="50"/>
       <c r="M183" s="15" t="s">
         <v>83</v>
       </c>
@@ -10867,7 +10864,7 @@
         <v>0.4375</v>
       </c>
       <c r="E187" s="15" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="F187" s="15"/>
       <c r="G187" s="19" t="s">
@@ -11175,7 +11172,7 @@
         <v>0.4375</v>
       </c>
       <c r="E197" s="15" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="F197" s="15"/>
       <c r="G197" s="19" t="s">
@@ -11240,11 +11237,11 @@
       <c r="D199" s="47">
         <v>0.5</v>
       </c>
-      <c r="E199" s="49" t="s">
-        <v>23</v>
-      </c>
-      <c r="F199" s="50"/>
-      <c r="G199" s="49" t="s">
+      <c r="E199" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F199" s="49"/>
+      <c r="G199" s="24" t="s">
         <v>171</v>
       </c>
       <c r="H199" s="19" t="s">
@@ -11253,11 +11250,11 @@
       <c r="I199" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="J199" s="50" t="s">
+      <c r="J199" s="49" t="s">
         <v>173</v>
       </c>
-      <c r="K199" s="50"/>
-      <c r="L199" s="50"/>
+      <c r="K199" s="49"/>
+      <c r="L199" s="49"/>
       <c r="M199" s="15" t="s">
         <v>114</v>
       </c>
@@ -11303,11 +11300,11 @@
       <c r="B201" s="44"/>
       <c r="C201" s="47"/>
       <c r="D201" s="47"/>
-      <c r="E201" s="49" t="s">
-        <v>23</v>
-      </c>
-      <c r="F201" s="50"/>
-      <c r="G201" s="49" t="s">
+      <c r="E201" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F201" s="49"/>
+      <c r="G201" s="24" t="s">
         <v>153</v>
       </c>
       <c r="H201" s="19" t="s">
@@ -11316,9 +11313,9 @@
       <c r="I201" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="J201" s="50"/>
-      <c r="K201" s="50"/>
-      <c r="L201" s="50"/>
+      <c r="J201" s="49"/>
+      <c r="K201" s="49"/>
+      <c r="L201" s="49"/>
       <c r="M201" s="15" t="s">
         <v>83</v>
       </c>
@@ -11336,11 +11333,11 @@
       <c r="D202" s="47">
         <v>0.64583333333333337</v>
       </c>
-      <c r="E202" s="50" t="s">
+      <c r="E202" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F202" s="50"/>
-      <c r="G202" s="49" t="s">
+      <c r="F202" s="49"/>
+      <c r="G202" s="24" t="s">
         <v>298</v>
       </c>
       <c r="H202" s="15" t="s">
@@ -11349,9 +11346,9 @@
       <c r="I202" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="J202" s="50"/>
-      <c r="K202" s="50"/>
-      <c r="L202" s="50"/>
+      <c r="J202" s="49"/>
+      <c r="K202" s="49"/>
+      <c r="L202" s="49"/>
       <c r="M202" s="15" t="s">
         <v>114</v>
       </c>
@@ -11367,11 +11364,11 @@
       <c r="D203" s="48">
         <v>0.54166666666666663</v>
       </c>
-      <c r="E203" s="50" t="s">
+      <c r="E203" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F203" s="50"/>
-      <c r="G203" s="49" t="s">
+      <c r="F203" s="49"/>
+      <c r="G203" s="24" t="s">
         <v>94</v>
       </c>
       <c r="H203" s="19" t="s">
@@ -11380,13 +11377,13 @@
       <c r="I203" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="J203" s="50" t="s">
+      <c r="J203" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="K203" s="50" t="s">
+      <c r="K203" s="49" t="s">
         <v>299</v>
       </c>
-      <c r="L203" s="50"/>
+      <c r="L203" s="49"/>
       <c r="M203" s="15" t="s">
         <v>83</v>
       </c>
@@ -11402,22 +11399,22 @@
       <c r="D204" s="48">
         <v>0.4375</v>
       </c>
-      <c r="E204" s="50" t="s">
-        <v>74</v>
-      </c>
-      <c r="F204" s="50"/>
-      <c r="G204" s="49" t="s">
+      <c r="E204" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F204" s="49"/>
+      <c r="G204" s="24" t="s">
         <v>148</v>
       </c>
       <c r="H204" s="15"/>
       <c r="I204" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="J204" s="50" t="s">
+      <c r="J204" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="K204" s="49"/>
-      <c r="L204" s="50"/>
+      <c r="K204" s="24"/>
+      <c r="L204" s="49"/>
       <c r="M204" s="15" t="s">
         <v>83</v>
       </c>
@@ -11429,20 +11426,20 @@
       <c r="B205" s="44"/>
       <c r="C205" s="48"/>
       <c r="D205" s="48"/>
-      <c r="E205" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="F205" s="50"/>
-      <c r="G205" s="49" t="s">
+      <c r="E205" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="F205" s="49"/>
+      <c r="G205" s="24" t="s">
         <v>300</v>
       </c>
       <c r="H205" s="15"/>
       <c r="I205" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="J205" s="50"/>
-      <c r="K205" s="50"/>
-      <c r="L205" s="50"/>
+      <c r="J205" s="49"/>
+      <c r="K205" s="49"/>
+      <c r="L205" s="49"/>
       <c r="M205" s="15" t="s">
         <v>83</v>
       </c>
@@ -11454,11 +11451,11 @@
       <c r="B206" s="44"/>
       <c r="C206" s="48"/>
       <c r="D206" s="48"/>
-      <c r="E206" s="50" t="s">
+      <c r="E206" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F206" s="50"/>
-      <c r="G206" s="49" t="s">
+      <c r="F206" s="49"/>
+      <c r="G206" s="24" t="s">
         <v>301</v>
       </c>
       <c r="H206" s="19" t="s">
@@ -11467,9 +11464,9 @@
       <c r="I206" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="J206" s="50"/>
-      <c r="K206" s="50"/>
-      <c r="L206" s="50"/>
+      <c r="J206" s="49"/>
+      <c r="K206" s="49"/>
+      <c r="L206" s="49"/>
       <c r="M206" s="15" t="s">
         <v>83</v>
       </c>
@@ -11481,11 +11478,11 @@
       <c r="B207" s="44"/>
       <c r="C207" s="47"/>
       <c r="D207" s="47"/>
-      <c r="E207" s="49" t="s">
-        <v>23</v>
-      </c>
-      <c r="F207" s="50"/>
-      <c r="G207" s="49" t="s">
+      <c r="E207" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F207" s="49"/>
+      <c r="G207" s="24" t="s">
         <v>302</v>
       </c>
       <c r="H207" s="19" t="s">
@@ -11494,9 +11491,9 @@
       <c r="I207" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="J207" s="50"/>
-      <c r="K207" s="50"/>
-      <c r="L207" s="50"/>
+      <c r="J207" s="49"/>
+      <c r="K207" s="49"/>
+      <c r="L207" s="49"/>
       <c r="M207" s="15" t="s">
         <v>83</v>
       </c>
@@ -11508,18 +11505,18 @@
       <c r="B208" s="44"/>
       <c r="C208" s="48"/>
       <c r="D208" s="48"/>
-      <c r="E208" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="F208" s="50"/>
-      <c r="G208" s="49" t="s">
+      <c r="E208" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="F208" s="49"/>
+      <c r="G208" s="24" t="s">
         <v>303</v>
       </c>
       <c r="H208" s="15"/>
       <c r="I208" s="15"/>
-      <c r="J208" s="50"/>
-      <c r="K208" s="50"/>
-      <c r="L208" s="50"/>
+      <c r="J208" s="49"/>
+      <c r="K208" s="49"/>
+      <c r="L208" s="49"/>
       <c r="M208" s="15" t="s">
         <v>83</v>
       </c>
@@ -11531,18 +11528,18 @@
       <c r="B209" s="44"/>
       <c r="C209" s="48"/>
       <c r="D209" s="48"/>
-      <c r="E209" s="50" t="s">
+      <c r="E209" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F209" s="50"/>
-      <c r="G209" s="49" t="s">
+      <c r="F209" s="49"/>
+      <c r="G209" s="24" t="s">
         <v>304</v>
       </c>
       <c r="H209" s="15"/>
       <c r="I209" s="15"/>
-      <c r="J209" s="50"/>
-      <c r="K209" s="50"/>
-      <c r="L209" s="50"/>
+      <c r="J209" s="49"/>
+      <c r="K209" s="49"/>
+      <c r="L209" s="49"/>
       <c r="M209" s="15" t="s">
         <v>83</v>
       </c>
@@ -16258,14 +16255,14 @@
       <c r="K994" s="36"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M198" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:M209" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M209">
     <sortCondition ref="A175:A209"/>
   </sortState>
   <customSheetViews>
     <customSheetView guid="{8F656852-D603-4744-997A-DE0F92A7585E}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:M198" xr:uid="{0A171728-216B-3140-B9F8-3464F194BC25}">
+      <autoFilter ref="A1:M198" xr:uid="{5A09B934-4EA4-B648-B067-E162CCE675CB}">
         <filterColumn colId="6">
           <filters>
             <filter val="GSPP Action Planning Implementation Pathways Region E Day 1  🌁"/>
@@ -16287,7 +16284,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L2:M198 M199:M209" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E198" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E198 E204" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"● Confirmed,◆ Hold, ☓ Cancel"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="I175" xr:uid="{00000000-0002-0000-0000-000003000000}">
@@ -18856,26 +18853,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f51bf047-e00d-4111-9acd-3b648a8df45c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb5933e1-39c5-43d4-bb0e-9e063605db7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FC47CB1A92F76B4FA38F66E0A126B066" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c0dc230b441f24b1df5c0a570d224bc1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb5933e1-39c5-43d4-bb0e-9e063605db7e" xmlns:ns3="f51bf047-e00d-4111-9acd-3b648a8df45c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d343ed676125dbafcd5314f1cfe67f7c" ns2:_="" ns3:_="">
     <xsd:import namespace="bb5933e1-39c5-43d4-bb0e-9e063605db7e"/>
@@ -19104,32 +19081,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B318E1E-A80F-4091-9E4D-E3248AE98C97}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="bb5933e1-39c5-43d4-bb0e-9e063605db7e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f51bf047-e00d-4111-9acd-3b648a8df45c"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE723B2C-1BFC-4804-B7F3-9EA38C1D43D6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f51bf047-e00d-4111-9acd-3b648a8df45c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb5933e1-39c5-43d4-bb0e-9e063605db7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DDBE47C-C6A7-41E9-8322-5F40C8EF948C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19146,4 +19118,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE723B2C-1BFC-4804-B7F3-9EA38C1D43D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B318E1E-A80F-4091-9E4D-E3248AE98C97}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="f51bf047-e00d-4111-9acd-3b648a8df45c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bb5933e1-39c5-43d4-bb0e-9e063605db7e"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/26-27_Admin_Calendar_Events_CTE-LL_Version.xlsx
+++ b/26-27_Admin_Calendar_Events_CTE-LL_Version.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lausd.sharepoint.com/teams/CTE-LLLeadership/Shared Documents/Calendaring/CTELL_Calendar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="8_{AFEB7EE0-A3A0-BE46-B68A-F48D580478B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1F17BFE-28AD-4AA5-82BE-5AA675D3D99C}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="8_{AFEB7EE0-A3A0-BE46-B68A-F48D580478B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A9120B8-50DB-48AD-A896-CB0254279430}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -392,7 +392,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1831" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1836" uniqueCount="320">
   <si>
     <t>Date</t>
   </si>
@@ -795,6 +795,9 @@
   </si>
   <si>
     <t>CSUN/LAUSD HSMT Symposium (Region North - Patient Care)</t>
+  </si>
+  <si>
+    <t>TBD (In Person)</t>
   </si>
   <si>
     <t>LL Microcredential #2 ▶️</t>
@@ -2104,7 +2107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AD1002"/>
@@ -2183,7 +2186,7 @@
       <c r="AC1" s="12"/>
       <c r="AD1" s="12"/>
     </row>
-    <row r="2" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="2" spans="1:30" ht="15.75" customHeight="1">
       <c r="A2" s="44">
         <v>46119</v>
       </c>
@@ -2233,7 +2236,7 @@
       <c r="AC2" s="12"/>
       <c r="AD2" s="12"/>
     </row>
-    <row r="3" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="3" spans="1:30" ht="15.75" customHeight="1">
       <c r="A3" s="44">
         <v>46210</v>
       </c>
@@ -2285,7 +2288,7 @@
       <c r="AC3" s="12"/>
       <c r="AD3" s="12"/>
     </row>
-    <row r="4" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="4" spans="1:30" ht="15.75" customHeight="1">
       <c r="A4" s="44">
         <v>46227</v>
       </c>
@@ -2331,7 +2334,7 @@
       <c r="AC4" s="12"/>
       <c r="AD4" s="12"/>
     </row>
-    <row r="5" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="5" spans="1:30" ht="15.75" customHeight="1">
       <c r="A5" s="44">
         <v>46232</v>
       </c>
@@ -2377,7 +2380,7 @@
       <c r="AC5" s="12"/>
       <c r="AD5" s="12"/>
     </row>
-    <row r="6" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="6" spans="1:30" ht="15.75" customHeight="1">
       <c r="A6" s="44">
         <v>46233</v>
       </c>
@@ -2425,7 +2428,7 @@
       <c r="AC6" s="12"/>
       <c r="AD6" s="12"/>
     </row>
-    <row r="7" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="7" spans="1:30" ht="15.75" customHeight="1">
       <c r="A7" s="44">
         <v>46233</v>
       </c>
@@ -2473,7 +2476,7 @@
       <c r="AC7" s="12"/>
       <c r="AD7" s="12"/>
     </row>
-    <row r="8" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="8" spans="1:30" ht="15.75" customHeight="1">
       <c r="A8" s="44">
         <v>46237</v>
       </c>
@@ -2525,7 +2528,7 @@
       <c r="AC8" s="12"/>
       <c r="AD8" s="12"/>
     </row>
-    <row r="9" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="9" spans="1:30" ht="15.75" customHeight="1">
       <c r="A9" s="44">
         <v>46237</v>
       </c>
@@ -2577,7 +2580,7 @@
       <c r="AC9" s="12"/>
       <c r="AD9" s="12"/>
     </row>
-    <row r="10" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="10" spans="1:30" ht="15.75" customHeight="1">
       <c r="A10" s="44">
         <v>46239</v>
       </c>
@@ -2629,7 +2632,7 @@
       <c r="AC10" s="12"/>
       <c r="AD10" s="12"/>
     </row>
-    <row r="11" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="11" spans="1:30" ht="15.75" customHeight="1">
       <c r="A11" s="44">
         <v>46240</v>
       </c>
@@ -2682,7 +2685,7 @@
       <c r="AC11" s="12"/>
       <c r="AD11" s="12"/>
     </row>
-    <row r="12" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="12" spans="1:30" ht="15.75" customHeight="1">
       <c r="A12" s="44">
         <v>46246</v>
       </c>
@@ -2731,7 +2734,7 @@
       <c r="AC12" s="12"/>
       <c r="AD12" s="12"/>
     </row>
-    <row r="13" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="13" spans="1:30" ht="15.75" customHeight="1">
       <c r="A13" s="44">
         <v>46248</v>
       </c>
@@ -2781,7 +2784,7 @@
       <c r="AC13" s="12"/>
       <c r="AD13" s="12"/>
     </row>
-    <row r="14" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="14" spans="1:30" ht="15.75" customHeight="1">
       <c r="A14" s="44">
         <v>46248</v>
       </c>
@@ -2825,7 +2828,7 @@
       <c r="AC14" s="12"/>
       <c r="AD14" s="12"/>
     </row>
-    <row r="15" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="15" spans="1:30" ht="15.75" customHeight="1">
       <c r="A15" s="44">
         <v>46253</v>
       </c>
@@ -2877,7 +2880,7 @@
       <c r="AC15" s="12"/>
       <c r="AD15" s="12"/>
     </row>
-    <row r="16" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="16" spans="1:30" ht="15.75" customHeight="1">
       <c r="A16" s="44">
         <v>46253</v>
       </c>
@@ -2929,7 +2932,7 @@
       <c r="AC16" s="12"/>
       <c r="AD16" s="12"/>
     </row>
-    <row r="17" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="17" spans="1:30" ht="15.75" customHeight="1">
       <c r="A17" s="44">
         <v>46258</v>
       </c>
@@ -2973,7 +2976,7 @@
       <c r="AC17" s="12"/>
       <c r="AD17" s="12"/>
     </row>
-    <row r="18" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="18" spans="1:30" ht="15.75" customHeight="1">
       <c r="A18" s="44">
         <v>46260</v>
       </c>
@@ -3025,7 +3028,7 @@
       <c r="AC18" s="12"/>
       <c r="AD18" s="12"/>
     </row>
-    <row r="19" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="19" spans="1:30" ht="15.75" customHeight="1">
       <c r="A19" s="44">
         <v>46262</v>
       </c>
@@ -3067,7 +3070,7 @@
       <c r="AC19" s="12"/>
       <c r="AD19" s="12"/>
     </row>
-    <row r="20" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="20" spans="1:30" ht="15.75" customHeight="1">
       <c r="A20" s="44">
         <v>46262</v>
       </c>
@@ -3111,7 +3114,7 @@
       <c r="AC20" s="12"/>
       <c r="AD20" s="12"/>
     </row>
-    <row r="21" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="21" spans="1:30" ht="15.75" customHeight="1">
       <c r="A21" s="44">
         <v>46263</v>
       </c>
@@ -3161,7 +3164,7 @@
       <c r="AC21" s="12"/>
       <c r="AD21" s="12"/>
     </row>
-    <row r="22" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="22" spans="1:30" ht="15.75" customHeight="1">
       <c r="A22" s="44">
         <v>46265</v>
       </c>
@@ -3205,7 +3208,7 @@
       <c r="AC22" s="12"/>
       <c r="AD22" s="12"/>
     </row>
-    <row r="23" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="23" spans="1:30" ht="15.75" customHeight="1">
       <c r="A23" s="44">
         <v>46265</v>
       </c>
@@ -3247,7 +3250,7 @@
       <c r="AC23" s="12"/>
       <c r="AD23" s="12"/>
     </row>
-    <row r="24" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="24" spans="1:30" ht="15.75" customHeight="1">
       <c r="A24" s="44">
         <v>46265</v>
       </c>
@@ -3291,7 +3294,7 @@
       <c r="AC24" s="12"/>
       <c r="AD24" s="12"/>
     </row>
-    <row r="25" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="25" spans="1:30" ht="15.75" customHeight="1">
       <c r="A25" s="44">
         <v>46266</v>
       </c>
@@ -3339,7 +3342,7 @@
       <c r="AC25" s="12"/>
       <c r="AD25" s="12"/>
     </row>
-    <row r="26" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="26" spans="1:30" ht="15.75" customHeight="1">
       <c r="A26" s="44">
         <v>46267</v>
       </c>
@@ -3391,7 +3394,7 @@
       <c r="AC26" s="12"/>
       <c r="AD26" s="12"/>
     </row>
-    <row r="27" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="27" spans="1:30" ht="15.75" customHeight="1">
       <c r="A27" s="44">
         <v>46268</v>
       </c>
@@ -3443,7 +3446,7 @@
       <c r="AC27" s="12"/>
       <c r="AD27" s="12"/>
     </row>
-    <row r="28" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="28" spans="1:30" ht="15.75" customHeight="1">
       <c r="A28" s="45">
         <v>46268</v>
       </c>
@@ -3495,7 +3498,7 @@
       <c r="AC28" s="12"/>
       <c r="AD28" s="12"/>
     </row>
-    <row r="29" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="29" spans="1:30" ht="15.75" customHeight="1">
       <c r="A29" s="44">
         <v>46274</v>
       </c>
@@ -3547,7 +3550,7 @@
       <c r="AC29" s="12"/>
       <c r="AD29" s="12"/>
     </row>
-    <row r="30" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="30" spans="1:30" ht="15.75" customHeight="1">
       <c r="A30" s="44">
         <v>46274</v>
       </c>
@@ -3591,7 +3594,7 @@
       <c r="AC30" s="12"/>
       <c r="AD30" s="12"/>
     </row>
-    <row r="31" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="31" spans="1:30" ht="15.75" customHeight="1">
       <c r="A31" s="44">
         <v>46274</v>
       </c>
@@ -3641,7 +3644,7 @@
       <c r="AC31" s="12"/>
       <c r="AD31" s="12"/>
     </row>
-    <row r="32" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="32" spans="1:30" ht="15.75" customHeight="1">
       <c r="A32" s="44">
         <v>46275</v>
       </c>
@@ -3685,7 +3688,7 @@
       <c r="AC32" s="12"/>
       <c r="AD32" s="12"/>
     </row>
-    <row r="33" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="33" spans="1:30" ht="15.75" customHeight="1">
       <c r="A33" s="44">
         <v>46276</v>
       </c>
@@ -3733,7 +3736,7 @@
       <c r="AC33" s="12"/>
       <c r="AD33" s="12"/>
     </row>
-    <row r="34" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="34" spans="1:30" ht="15.75" customHeight="1">
       <c r="A34" s="44">
         <v>46279</v>
       </c>
@@ -3777,7 +3780,7 @@
       <c r="AC34" s="12"/>
       <c r="AD34" s="12"/>
     </row>
-    <row r="35" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="35" spans="1:30" ht="15.75" customHeight="1">
       <c r="A35" s="44">
         <v>46280</v>
       </c>
@@ -3825,7 +3828,7 @@
       <c r="AC35" s="12"/>
       <c r="AD35" s="12"/>
     </row>
-    <row r="36" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="36" spans="1:30" ht="15.75" customHeight="1">
       <c r="A36" s="44">
         <v>46281</v>
       </c>
@@ -3877,7 +3880,7 @@
       <c r="AC36" s="12"/>
       <c r="AD36" s="12"/>
     </row>
-    <row r="37" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="37" spans="1:30" ht="15.75" customHeight="1">
       <c r="A37" s="44">
         <v>46281</v>
       </c>
@@ -3927,7 +3930,7 @@
       <c r="AC37" s="12"/>
       <c r="AD37" s="12"/>
     </row>
-    <row r="38" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="38" spans="1:30" ht="15.75" customHeight="1">
       <c r="A38" s="44">
         <v>46282</v>
       </c>
@@ -3977,7 +3980,7 @@
       <c r="AC38" s="12"/>
       <c r="AD38" s="12"/>
     </row>
-    <row r="39" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="39" spans="1:30" ht="15.75" customHeight="1">
       <c r="A39" s="44">
         <v>46282</v>
       </c>
@@ -4029,7 +4032,7 @@
       <c r="AC39" s="12"/>
       <c r="AD39" s="12"/>
     </row>
-    <row r="40" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="40" spans="1:30" ht="15.75" customHeight="1">
       <c r="A40" s="44">
         <v>46283</v>
       </c>
@@ -4073,7 +4076,7 @@
       <c r="AC40" s="8"/>
       <c r="AD40" s="8"/>
     </row>
-    <row r="41" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="41" spans="1:30" ht="15.75" customHeight="1">
       <c r="A41" s="44">
         <v>46283</v>
       </c>
@@ -4121,7 +4124,7 @@
       <c r="AC41" s="12"/>
       <c r="AD41" s="12"/>
     </row>
-    <row r="42" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="42" spans="1:30" ht="15.75" customHeight="1">
       <c r="A42" s="44">
         <v>46284</v>
       </c>
@@ -4169,7 +4172,7 @@
       <c r="AC42" s="8"/>
       <c r="AD42" s="8"/>
     </row>
-    <row r="43" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="43" spans="1:30" ht="15.75" customHeight="1">
       <c r="A43" s="44">
         <v>46287</v>
       </c>
@@ -4217,7 +4220,7 @@
       <c r="AC43" s="12"/>
       <c r="AD43" s="12"/>
     </row>
-    <row r="44" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="44" spans="1:30" ht="15.75" customHeight="1">
       <c r="A44" s="44">
         <v>46288</v>
       </c>
@@ -4269,7 +4272,7 @@
       <c r="AC44" s="12"/>
       <c r="AD44" s="12"/>
     </row>
-    <row r="45" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="45" spans="1:30" ht="15.75" customHeight="1">
       <c r="A45" s="44">
         <v>46289</v>
       </c>
@@ -4317,7 +4320,7 @@
       <c r="AC45" s="12"/>
       <c r="AD45" s="12"/>
     </row>
-    <row r="46" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="46" spans="1:30" ht="15.75" customHeight="1">
       <c r="A46" s="44">
         <v>46291</v>
       </c>
@@ -4367,7 +4370,7 @@
       <c r="AC46" s="12"/>
       <c r="AD46" s="12"/>
     </row>
-    <row r="47" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="47" spans="1:30" ht="15.75" customHeight="1">
       <c r="A47" s="44">
         <v>46294</v>
       </c>
@@ -4411,7 +4414,7 @@
       <c r="AC47" s="12"/>
       <c r="AD47" s="12"/>
     </row>
-    <row r="48" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="48" spans="1:30" ht="15.75" customHeight="1">
       <c r="A48" s="44">
         <v>46295</v>
       </c>
@@ -4459,7 +4462,7 @@
       <c r="AC48" s="8"/>
       <c r="AD48" s="8"/>
     </row>
-    <row r="49" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="49" spans="1:30" ht="15.75" customHeight="1">
       <c r="A49" s="44">
         <v>46295</v>
       </c>
@@ -4511,7 +4514,7 @@
       <c r="AC49" s="12"/>
       <c r="AD49" s="12"/>
     </row>
-    <row r="50" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="50" spans="1:30" ht="15.75" customHeight="1">
       <c r="A50" s="45">
         <v>46295</v>
       </c>
@@ -4615,7 +4618,7 @@
       <c r="AC51" s="8"/>
       <c r="AD51" s="8"/>
     </row>
-    <row r="52" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="52" spans="1:30" ht="15.75" customHeight="1">
       <c r="A52" s="44">
         <v>46297</v>
       </c>
@@ -4665,7 +4668,7 @@
       <c r="AC52" s="12"/>
       <c r="AD52" s="12"/>
     </row>
-    <row r="53" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="53" spans="1:30" ht="15.75" customHeight="1">
       <c r="A53" s="44">
         <v>46297</v>
       </c>
@@ -4713,7 +4716,7 @@
       <c r="AC53" s="12"/>
       <c r="AD53" s="12"/>
     </row>
-    <row r="54" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="54" spans="1:30" ht="15.75" customHeight="1">
       <c r="A54" s="44">
         <v>46298</v>
       </c>
@@ -4763,7 +4766,7 @@
       <c r="AC54" s="12"/>
       <c r="AD54" s="12"/>
     </row>
-    <row r="55" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="55" spans="1:30" ht="15.75" customHeight="1">
       <c r="A55" s="44">
         <v>46298</v>
       </c>
@@ -4805,7 +4808,7 @@
       <c r="AC55" s="12"/>
       <c r="AD55" s="12"/>
     </row>
-    <row r="56" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="56" spans="1:30" ht="15.75" customHeight="1">
       <c r="A56" s="44">
         <v>46302</v>
       </c>
@@ -4857,7 +4860,7 @@
       <c r="AC56" s="12"/>
       <c r="AD56" s="12"/>
     </row>
-    <row r="57" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="57" spans="1:30" ht="15.75" customHeight="1">
       <c r="A57" s="44">
         <v>46302</v>
       </c>
@@ -4907,7 +4910,7 @@
       <c r="AC57" s="12"/>
       <c r="AD57" s="12"/>
     </row>
-    <row r="58" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="58" spans="1:30" ht="15.75" customHeight="1">
       <c r="A58" s="44">
         <v>46303</v>
       </c>
@@ -4957,7 +4960,7 @@
       <c r="AC58" s="12"/>
       <c r="AD58" s="12"/>
     </row>
-    <row r="59" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="59" spans="1:30" ht="15.75" customHeight="1">
       <c r="A59" s="44">
         <v>46303</v>
       </c>
@@ -5007,7 +5010,7 @@
       <c r="AC59" s="12"/>
       <c r="AD59" s="12"/>
     </row>
-    <row r="60" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="60" spans="1:30" ht="15.75" customHeight="1">
       <c r="A60" s="44">
         <v>46304</v>
       </c>
@@ -5057,7 +5060,7 @@
       <c r="AC60" s="12"/>
       <c r="AD60" s="12"/>
     </row>
-    <row r="61" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="61" spans="1:30" ht="15.75" customHeight="1">
       <c r="A61" s="44">
         <v>46304</v>
       </c>
@@ -5107,7 +5110,7 @@
       <c r="AC61" s="12"/>
       <c r="AD61" s="12"/>
     </row>
-    <row r="62" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="62" spans="1:30" ht="15.75" customHeight="1">
       <c r="A62" s="44">
         <v>46304</v>
       </c>
@@ -5178,7 +5181,9 @@
       <c r="J63" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="K63" s="15"/>
+      <c r="K63" s="51" t="s">
+        <v>107</v>
+      </c>
       <c r="L63" s="15"/>
       <c r="M63" s="15" t="s">
         <v>32</v>
@@ -5201,7 +5206,7 @@
       <c r="AC63" s="12"/>
       <c r="AD63" s="12"/>
     </row>
-    <row r="64" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="64" spans="1:30" ht="15.75" customHeight="1">
       <c r="A64" s="44">
         <v>46309</v>
       </c>
@@ -5253,7 +5258,7 @@
       <c r="AC64" s="12"/>
       <c r="AD64" s="12"/>
     </row>
-    <row r="65" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="65" spans="1:30" ht="15.75" customHeight="1">
       <c r="A65" s="44">
         <v>46309</v>
       </c>
@@ -5305,7 +5310,7 @@
       <c r="AC65" s="12"/>
       <c r="AD65" s="12"/>
     </row>
-    <row r="66" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="66" spans="1:30" ht="15.75" customHeight="1">
       <c r="A66" s="44">
         <v>46310</v>
       </c>
@@ -5355,7 +5360,7 @@
       <c r="AC66" s="12"/>
       <c r="AD66" s="12"/>
     </row>
-    <row r="67" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="67" spans="1:30" ht="15.75" customHeight="1">
       <c r="A67" s="44">
         <v>46310</v>
       </c>
@@ -5432,7 +5437,9 @@
       <c r="J68" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="K68" s="15"/>
+      <c r="K68" s="51" t="s">
+        <v>107</v>
+      </c>
       <c r="L68" s="15"/>
       <c r="M68" s="15" t="s">
         <v>32</v>
@@ -5455,7 +5462,7 @@
       <c r="AC68" s="12"/>
       <c r="AD68" s="12"/>
     </row>
-    <row r="69" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="69" spans="1:30" ht="15.75" customHeight="1">
       <c r="A69" s="45">
         <v>46310</v>
       </c>
@@ -5507,7 +5514,7 @@
       <c r="AC69" s="12"/>
       <c r="AD69" s="12"/>
     </row>
-    <row r="70" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="70" spans="1:30" ht="15.75" customHeight="1">
       <c r="A70" s="44">
         <v>46311</v>
       </c>
@@ -5557,7 +5564,7 @@
       <c r="AC70" s="12"/>
       <c r="AD70" s="12"/>
     </row>
-    <row r="71" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="71" spans="1:30" ht="15.75" customHeight="1">
       <c r="A71" s="44">
         <v>46311</v>
       </c>
@@ -5607,7 +5614,7 @@
       <c r="AC71" s="12"/>
       <c r="AD71" s="12"/>
     </row>
-    <row r="72" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="72" spans="1:30" ht="15.75" customHeight="1">
       <c r="A72" s="44">
         <v>46312</v>
       </c>
@@ -5657,7 +5664,7 @@
       <c r="AC72" s="12"/>
       <c r="AD72" s="12"/>
     </row>
-    <row r="73" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="73" spans="1:30" ht="15.75" customHeight="1">
       <c r="A73" s="44">
         <v>46316</v>
       </c>
@@ -5707,7 +5714,7 @@
       <c r="AC73" s="12"/>
       <c r="AD73" s="12"/>
     </row>
-    <row r="74" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="74" spans="1:30" ht="15.75" customHeight="1">
       <c r="A74" s="44">
         <v>46316</v>
       </c>
@@ -5759,7 +5766,7 @@
       <c r="AC74" s="12"/>
       <c r="AD74" s="12"/>
     </row>
-    <row r="75" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="75" spans="1:30" ht="15.75" customHeight="1">
       <c r="A75" s="44">
         <v>46316</v>
       </c>
@@ -5807,7 +5814,7 @@
       <c r="AC75" s="12"/>
       <c r="AD75" s="12"/>
     </row>
-    <row r="76" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="76" spans="1:30" ht="15.75" customHeight="1">
       <c r="A76" s="44">
         <v>46317</v>
       </c>
@@ -5855,7 +5862,7 @@
       <c r="AC76" s="12"/>
       <c r="AD76" s="12"/>
     </row>
-    <row r="77" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="77" spans="1:30" ht="15.75" customHeight="1">
       <c r="A77" s="44">
         <v>46318</v>
       </c>
@@ -5897,7 +5904,7 @@
       <c r="AC77" s="12"/>
       <c r="AD77" s="12"/>
     </row>
-    <row r="78" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="78" spans="1:30" ht="15.75" customHeight="1">
       <c r="A78" s="44">
         <v>46318</v>
       </c>
@@ -5945,7 +5952,7 @@
       <c r="AC78" s="12"/>
       <c r="AD78" s="12"/>
     </row>
-    <row r="79" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="79" spans="1:30" ht="15.75" customHeight="1">
       <c r="A79" s="44">
         <v>46319</v>
       </c>
@@ -5991,7 +5998,7 @@
       <c r="AC79" s="12"/>
       <c r="AD79" s="12"/>
     </row>
-    <row r="80" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="80" spans="1:30" ht="15.75" customHeight="1">
       <c r="A80" s="44">
         <v>46323</v>
       </c>
@@ -6043,7 +6050,7 @@
       <c r="AC80" s="12"/>
       <c r="AD80" s="12"/>
     </row>
-    <row r="81" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="81" spans="1:30" ht="15.75" customHeight="1">
       <c r="A81" s="44">
         <v>46324</v>
       </c>
@@ -6091,7 +6098,7 @@
       <c r="AC81" s="12"/>
       <c r="AD81" s="12"/>
     </row>
-    <row r="82" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="82" spans="1:30" ht="15.75" customHeight="1">
       <c r="A82" s="44">
         <v>46324</v>
       </c>
@@ -6139,7 +6146,7 @@
       <c r="AC82" s="12"/>
       <c r="AD82" s="12"/>
     </row>
-    <row r="83" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="83" spans="1:30" ht="15.75" customHeight="1">
       <c r="A83" s="44">
         <v>46325</v>
       </c>
@@ -6179,7 +6186,7 @@
       <c r="AC83" s="12"/>
       <c r="AD83" s="12"/>
     </row>
-    <row r="84" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="84" spans="1:30" ht="15.75" customHeight="1">
       <c r="A84" s="44">
         <v>46325</v>
       </c>
@@ -6223,7 +6230,7 @@
       <c r="AC84" s="12"/>
       <c r="AD84" s="12"/>
     </row>
-    <row r="85" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="85" spans="1:30" ht="15.75" customHeight="1">
       <c r="A85" s="44">
         <v>46326</v>
       </c>
@@ -6294,7 +6301,9 @@
       <c r="J86" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="K86" s="15"/>
+      <c r="K86" s="51" t="s">
+        <v>107</v>
+      </c>
       <c r="L86" s="15"/>
       <c r="M86" s="15" t="s">
         <v>32</v>
@@ -6317,7 +6326,7 @@
       <c r="AC86" s="12"/>
       <c r="AD86" s="12"/>
     </row>
-    <row r="87" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="87" spans="1:30" ht="15.75" customHeight="1">
       <c r="A87" s="44">
         <v>46327</v>
       </c>
@@ -6359,7 +6368,7 @@
       <c r="AC87" s="12"/>
       <c r="AD87" s="12"/>
     </row>
-    <row r="88" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="88" spans="1:30" ht="15.75" customHeight="1">
       <c r="A88" s="44">
         <v>46330</v>
       </c>
@@ -6411,7 +6420,7 @@
       <c r="AC88" s="12"/>
       <c r="AD88" s="12"/>
     </row>
-    <row r="89" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="89" spans="1:30" ht="15.75" customHeight="1">
       <c r="A89" s="44">
         <v>46330</v>
       </c>
@@ -6455,7 +6464,7 @@
       <c r="AC89" s="12"/>
       <c r="AD89" s="12"/>
     </row>
-    <row r="90" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="90" spans="1:30" ht="15.75" customHeight="1">
       <c r="A90" s="44">
         <v>46330</v>
       </c>
@@ -6505,7 +6514,7 @@
       <c r="AC90" s="12"/>
       <c r="AD90" s="12"/>
     </row>
-    <row r="91" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="91" spans="1:30" ht="15.75" customHeight="1">
       <c r="A91" s="45">
         <v>46331</v>
       </c>
@@ -6581,8 +6590,12 @@
       <c r="I92" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="J92" s="15"/>
-      <c r="K92" s="15"/>
+      <c r="J92" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="K92" s="51" t="s">
+        <v>107</v>
+      </c>
       <c r="L92" s="15"/>
       <c r="M92" s="15" t="s">
         <v>32</v>
@@ -6605,7 +6618,7 @@
       <c r="AC92" s="12"/>
       <c r="AD92" s="12"/>
     </row>
-    <row r="93" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="93" spans="1:30" ht="15.75" customHeight="1">
       <c r="A93" s="44">
         <v>46333</v>
       </c>
@@ -6621,7 +6634,7 @@
       </c>
       <c r="F93" s="15"/>
       <c r="G93" s="19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H93" s="15" t="s">
         <v>85</v>
@@ -6653,7 +6666,7 @@
       <c r="AC93" s="12"/>
       <c r="AD93" s="12"/>
     </row>
-    <row r="94" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="94" spans="1:30" ht="15.75" customHeight="1">
       <c r="A94" s="44">
         <v>46338</v>
       </c>
@@ -6681,7 +6694,7 @@
         <v>17</v>
       </c>
       <c r="K94" s="19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L94" s="15"/>
       <c r="M94" s="15" t="s">
@@ -6705,7 +6718,7 @@
       <c r="AC94" s="12"/>
       <c r="AD94" s="12"/>
     </row>
-    <row r="95" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="95" spans="1:30" ht="15.75" customHeight="1">
       <c r="A95" s="44">
         <v>46339</v>
       </c>
@@ -6753,7 +6766,7 @@
       <c r="AC95" s="12"/>
       <c r="AD95" s="12"/>
     </row>
-    <row r="96" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="96" spans="1:30" ht="15.75" customHeight="1">
       <c r="A96" s="44">
         <v>46340</v>
       </c>
@@ -6803,7 +6816,7 @@
       <c r="AC96" s="12"/>
       <c r="AD96" s="12"/>
     </row>
-    <row r="97" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="97" spans="1:30" ht="15.75" customHeight="1">
       <c r="A97" s="44">
         <v>46344</v>
       </c>
@@ -6855,7 +6868,7 @@
       <c r="AC97" s="12"/>
       <c r="AD97" s="12"/>
     </row>
-    <row r="98" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="98" spans="1:30" ht="15.75" customHeight="1">
       <c r="A98" s="44">
         <v>46344</v>
       </c>
@@ -6871,7 +6884,7 @@
       </c>
       <c r="F98" s="15"/>
       <c r="G98" s="19" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H98" s="19" t="s">
         <v>46</v>
@@ -6905,7 +6918,7 @@
       <c r="AC98" s="12"/>
       <c r="AD98" s="12"/>
     </row>
-    <row r="99" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="99" spans="1:30" ht="15.75" customHeight="1">
       <c r="A99" s="44">
         <v>46345</v>
       </c>
@@ -6953,7 +6966,7 @@
       <c r="AC99" s="12"/>
       <c r="AD99" s="12"/>
     </row>
-    <row r="100" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="100" spans="1:30" ht="15.75" customHeight="1">
       <c r="A100" s="44">
         <v>46351</v>
       </c>
@@ -7005,7 +7018,7 @@
       <c r="AC100" s="12"/>
       <c r="AD100" s="12"/>
     </row>
-    <row r="101" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="101" spans="1:30" ht="15.75" customHeight="1">
       <c r="A101" s="44">
         <v>46356</v>
       </c>
@@ -7017,7 +7030,7 @@
       </c>
       <c r="F101" s="15"/>
       <c r="G101" s="19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H101" s="15" t="s">
         <v>25</v>
@@ -7049,7 +7062,7 @@
       <c r="AC101" s="12"/>
       <c r="AD101" s="12"/>
     </row>
-    <row r="102" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="102" spans="1:30" ht="15.75" customHeight="1">
       <c r="A102" s="44">
         <v>46357</v>
       </c>
@@ -7065,7 +7078,7 @@
       </c>
       <c r="F102" s="15"/>
       <c r="G102" s="19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H102" s="15" t="s">
         <v>57</v>
@@ -7097,7 +7110,7 @@
       <c r="AC102" s="12"/>
       <c r="AD102" s="12"/>
     </row>
-    <row r="103" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="103" spans="1:30" ht="15.75" customHeight="1">
       <c r="A103" s="44">
         <v>46358</v>
       </c>
@@ -7149,7 +7162,7 @@
       <c r="AC103" s="12"/>
       <c r="AD103" s="12"/>
     </row>
-    <row r="104" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="104" spans="1:30" ht="15.75" customHeight="1">
       <c r="A104" s="44">
         <v>46360</v>
       </c>
@@ -7197,7 +7210,7 @@
       <c r="AC104" s="12"/>
       <c r="AD104" s="12"/>
     </row>
-    <row r="105" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="105" spans="1:30" ht="15.75" customHeight="1">
       <c r="A105" s="44">
         <v>46365</v>
       </c>
@@ -7249,7 +7262,7 @@
       <c r="AC105" s="12"/>
       <c r="AD105" s="12"/>
     </row>
-    <row r="106" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="106" spans="1:30" ht="15.75" customHeight="1">
       <c r="A106" s="44">
         <v>46365</v>
       </c>
@@ -7277,7 +7290,7 @@
         <v>17</v>
       </c>
       <c r="K106" s="15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L106" s="15"/>
       <c r="M106" s="15" t="s">
@@ -7301,7 +7314,7 @@
       <c r="AC106" s="12"/>
       <c r="AD106" s="12"/>
     </row>
-    <row r="107" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="107" spans="1:30" ht="15.75" customHeight="1">
       <c r="A107" s="44">
         <v>46365</v>
       </c>
@@ -7326,7 +7339,7 @@
         <v>16</v>
       </c>
       <c r="J107" s="15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K107" s="15"/>
       <c r="L107" s="15"/>
@@ -7351,7 +7364,7 @@
       <c r="AC107" s="12"/>
       <c r="AD107" s="12"/>
     </row>
-    <row r="108" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="108" spans="1:30" ht="15.75" customHeight="1">
       <c r="A108" s="44">
         <v>46366</v>
       </c>
@@ -7363,7 +7376,7 @@
       </c>
       <c r="F108" s="15"/>
       <c r="G108" s="19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H108" s="19" t="s">
         <v>38</v>
@@ -7395,7 +7408,7 @@
       <c r="AC108" s="12"/>
       <c r="AD108" s="12"/>
     </row>
-    <row r="109" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="109" spans="1:30" ht="15.75" customHeight="1">
       <c r="A109" s="44">
         <v>46367</v>
       </c>
@@ -7407,7 +7420,7 @@
       </c>
       <c r="F109" s="15"/>
       <c r="G109" s="19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H109" s="15" t="s">
         <v>46</v>
@@ -7439,7 +7452,7 @@
       <c r="AC109" s="12"/>
       <c r="AD109" s="12"/>
     </row>
-    <row r="110" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="110" spans="1:30" ht="15.75" customHeight="1">
       <c r="A110" s="44">
         <v>46368</v>
       </c>
@@ -7489,7 +7502,7 @@
       <c r="AC110" s="12"/>
       <c r="AD110" s="12"/>
     </row>
-    <row r="111" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="111" spans="1:30" ht="15.75" customHeight="1">
       <c r="A111" s="44">
         <v>46372</v>
       </c>
@@ -7517,7 +7530,7 @@
         <v>97</v>
       </c>
       <c r="K111" s="19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L111" s="15"/>
       <c r="M111" s="15" t="s">
@@ -7541,7 +7554,7 @@
       <c r="AC111" s="12"/>
       <c r="AD111" s="12"/>
     </row>
-    <row r="112" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="112" spans="1:30" ht="15.75" customHeight="1">
       <c r="A112" s="44">
         <v>46372</v>
       </c>
@@ -7557,7 +7570,7 @@
       </c>
       <c r="F112" s="15"/>
       <c r="G112" s="19" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H112" s="15" t="s">
         <v>57</v>
@@ -7566,10 +7579,10 @@
         <v>61</v>
       </c>
       <c r="J112" s="15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K112" s="15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L112" s="15"/>
       <c r="M112" s="15" t="s">
@@ -7593,7 +7606,7 @@
       <c r="AC112" s="12"/>
       <c r="AD112" s="12"/>
     </row>
-    <row r="113" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="113" spans="1:30" ht="15.75" customHeight="1">
       <c r="A113" s="45">
         <v>46373</v>
       </c>
@@ -7645,7 +7658,7 @@
       <c r="AC113" s="12"/>
       <c r="AD113" s="12"/>
     </row>
-    <row r="114" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="114" spans="1:30" ht="15.75" customHeight="1">
       <c r="A114" s="44">
         <v>46400</v>
       </c>
@@ -7697,7 +7710,7 @@
       <c r="AC114" s="12"/>
       <c r="AD114" s="12"/>
     </row>
-    <row r="115" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="115" spans="1:30" ht="15.75" customHeight="1">
       <c r="A115" s="44">
         <v>46400</v>
       </c>
@@ -7747,7 +7760,7 @@
       <c r="AC115" s="12"/>
       <c r="AD115" s="12"/>
     </row>
-    <row r="116" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="116" spans="1:30" ht="15.75" customHeight="1">
       <c r="A116" s="45">
         <v>46401</v>
       </c>
@@ -7799,7 +7812,7 @@
       <c r="AC116" s="12"/>
       <c r="AD116" s="12"/>
     </row>
-    <row r="117" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="117" spans="1:30" ht="15.75" customHeight="1">
       <c r="A117" s="44">
         <v>46402</v>
       </c>
@@ -7847,7 +7860,7 @@
       <c r="AC117" s="12"/>
       <c r="AD117" s="12"/>
     </row>
-    <row r="118" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="118" spans="1:30" ht="15.75" customHeight="1">
       <c r="A118" s="44">
         <v>46407</v>
       </c>
@@ -7899,7 +7912,7 @@
       <c r="AC118" s="12"/>
       <c r="AD118" s="12"/>
     </row>
-    <row r="119" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="119" spans="1:30" ht="15.75" customHeight="1">
       <c r="A119" s="44">
         <v>46407</v>
       </c>
@@ -7927,7 +7940,7 @@
         <v>17</v>
       </c>
       <c r="K119" s="15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L119" s="15"/>
       <c r="M119" s="15" t="s">
@@ -7951,7 +7964,7 @@
       <c r="AC119" s="12"/>
       <c r="AD119" s="12"/>
     </row>
-    <row r="120" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="120" spans="1:30" ht="15.75" customHeight="1">
       <c r="A120" s="44">
         <v>46410</v>
       </c>
@@ -8001,7 +8014,7 @@
       <c r="AC120" s="12"/>
       <c r="AD120" s="12"/>
     </row>
-    <row r="121" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="121" spans="1:30" ht="15.75" customHeight="1">
       <c r="A121" s="44">
         <v>46410</v>
       </c>
@@ -8017,7 +8030,7 @@
       </c>
       <c r="F121" s="15"/>
       <c r="G121" s="19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H121" s="19" t="s">
         <v>85</v>
@@ -8049,7 +8062,7 @@
       <c r="AC121" s="12"/>
       <c r="AD121" s="12"/>
     </row>
-    <row r="122" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="122" spans="1:30" ht="15.75" customHeight="1">
       <c r="A122" s="44">
         <v>46411</v>
       </c>
@@ -8061,7 +8074,7 @@
       </c>
       <c r="F122" s="15"/>
       <c r="G122" s="19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H122" s="15"/>
       <c r="I122" s="15" t="s">
@@ -8091,7 +8104,7 @@
       <c r="AC122" s="12"/>
       <c r="AD122" s="12"/>
     </row>
-    <row r="123" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="123" spans="1:30" ht="15.75" customHeight="1">
       <c r="A123" s="44">
         <v>46411</v>
       </c>
@@ -8103,7 +8116,7 @@
       </c>
       <c r="F123" s="15"/>
       <c r="G123" s="19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H123" s="19" t="s">
         <v>25</v>
@@ -8113,7 +8126,7 @@
       </c>
       <c r="J123" s="15"/>
       <c r="K123" s="19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L123" s="15"/>
       <c r="M123" s="15" t="s">
@@ -8137,7 +8150,7 @@
       <c r="AC123" s="12"/>
       <c r="AD123" s="12"/>
     </row>
-    <row r="124" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="124" spans="1:30" ht="15.75" customHeight="1">
       <c r="A124" s="44">
         <v>46414</v>
       </c>
@@ -8189,7 +8202,7 @@
       <c r="AC124" s="12"/>
       <c r="AD124" s="12"/>
     </row>
-    <row r="125" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="125" spans="1:30" ht="15.75" customHeight="1">
       <c r="A125" s="44">
         <v>46415</v>
       </c>
@@ -8237,7 +8250,7 @@
       <c r="AC125" s="12"/>
       <c r="AD125" s="12"/>
     </row>
-    <row r="126" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="126" spans="1:30" ht="15.75" customHeight="1">
       <c r="A126" s="44">
         <v>46416</v>
       </c>
@@ -8249,7 +8262,7 @@
       </c>
       <c r="F126" s="15"/>
       <c r="G126" s="19" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H126" s="19" t="s">
         <v>25</v>
@@ -8281,7 +8294,7 @@
       <c r="AC126" s="12"/>
       <c r="AD126" s="12"/>
     </row>
-    <row r="127" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="127" spans="1:30" ht="15.75" customHeight="1">
       <c r="A127" s="44">
         <v>46417</v>
       </c>
@@ -8293,7 +8306,7 @@
       </c>
       <c r="F127" s="15"/>
       <c r="G127" s="19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H127" s="19" t="s">
         <v>25</v>
@@ -8325,7 +8338,7 @@
       <c r="AC127" s="12"/>
       <c r="AD127" s="12"/>
     </row>
-    <row r="128" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="128" spans="1:30" ht="15.75" customHeight="1">
       <c r="A128" s="44">
         <v>46418</v>
       </c>
@@ -8337,7 +8350,7 @@
       </c>
       <c r="F128" s="15"/>
       <c r="G128" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H128" s="15"/>
       <c r="I128" s="15"/>
@@ -8365,7 +8378,7 @@
       <c r="AC128" s="12"/>
       <c r="AD128" s="12"/>
     </row>
-    <row r="129" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="129" spans="1:30" ht="15.75" customHeight="1">
       <c r="A129" s="44">
         <v>46420</v>
       </c>
@@ -8381,7 +8394,7 @@
       </c>
       <c r="F129" s="15"/>
       <c r="G129" s="19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H129" s="15" t="s">
         <v>57</v>
@@ -8413,7 +8426,7 @@
       <c r="AC129" s="12"/>
       <c r="AD129" s="12"/>
     </row>
-    <row r="130" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="130" spans="1:30" ht="15.75" customHeight="1">
       <c r="A130" s="44">
         <v>46421</v>
       </c>
@@ -8465,7 +8478,7 @@
       <c r="AC130" s="12"/>
       <c r="AD130" s="12"/>
     </row>
-    <row r="131" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="131" spans="1:30" ht="15.75" customHeight="1">
       <c r="A131" s="44">
         <v>46421</v>
       </c>
@@ -8515,7 +8528,7 @@
       <c r="AC131" s="12"/>
       <c r="AD131" s="12"/>
     </row>
-    <row r="132" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="132" spans="1:30" ht="15.75" customHeight="1">
       <c r="A132" s="45">
         <v>46422</v>
       </c>
@@ -8567,7 +8580,7 @@
       <c r="AC132" s="12"/>
       <c r="AD132" s="12"/>
     </row>
-    <row r="133" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="133" spans="1:30" ht="15.75" customHeight="1">
       <c r="A133" s="44">
         <v>46423</v>
       </c>
@@ -8615,7 +8628,7 @@
       <c r="AC133" s="12"/>
       <c r="AD133" s="12"/>
     </row>
-    <row r="134" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="134" spans="1:30" ht="15.75" customHeight="1">
       <c r="A134" s="44">
         <v>46423</v>
       </c>
@@ -8631,7 +8644,7 @@
       </c>
       <c r="F134" s="15"/>
       <c r="G134" s="19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H134" s="15" t="s">
         <v>57</v>
@@ -8640,10 +8653,10 @@
         <v>35</v>
       </c>
       <c r="J134" s="15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K134" s="15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L134" s="15"/>
       <c r="M134" s="15" t="s">
@@ -8667,7 +8680,7 @@
       <c r="AC134" s="12"/>
       <c r="AD134" s="12"/>
     </row>
-    <row r="135" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="135" spans="1:30" ht="15.75" customHeight="1">
       <c r="A135" s="44">
         <v>46428</v>
       </c>
@@ -8719,7 +8732,7 @@
       <c r="AC135" s="12"/>
       <c r="AD135" s="12"/>
     </row>
-    <row r="136" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="136" spans="1:30" ht="15.75" customHeight="1">
       <c r="A136" s="44">
         <v>46428</v>
       </c>
@@ -8735,7 +8748,7 @@
       </c>
       <c r="F136" s="15"/>
       <c r="G136" s="19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H136" s="19" t="s">
         <v>46</v>
@@ -8747,7 +8760,7 @@
         <v>48</v>
       </c>
       <c r="K136" s="19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L136" s="15"/>
       <c r="M136" s="15" t="s">
@@ -8771,7 +8784,7 @@
       <c r="AC136" s="12"/>
       <c r="AD136" s="12"/>
     </row>
-    <row r="137" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="137" spans="1:30" ht="15.75" customHeight="1">
       <c r="A137" s="44">
         <v>46428</v>
       </c>
@@ -8799,7 +8812,7 @@
         <v>17</v>
       </c>
       <c r="K137" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L137" s="15"/>
       <c r="M137" s="15" t="s">
@@ -8823,7 +8836,7 @@
       <c r="AC137" s="12"/>
       <c r="AD137" s="12"/>
     </row>
-    <row r="138" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="138" spans="1:30" ht="15.75" customHeight="1">
       <c r="A138" s="44">
         <v>46430</v>
       </c>
@@ -8867,7 +8880,7 @@
       <c r="AC138" s="12"/>
       <c r="AD138" s="12"/>
     </row>
-    <row r="139" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="139" spans="1:30" ht="15.75" customHeight="1">
       <c r="A139" s="44">
         <v>46435</v>
       </c>
@@ -8919,7 +8932,7 @@
       <c r="AC139" s="12"/>
       <c r="AD139" s="12"/>
     </row>
-    <row r="140" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="140" spans="1:30" ht="15.75" customHeight="1">
       <c r="A140" s="44">
         <v>46438</v>
       </c>
@@ -8969,7 +8982,7 @@
       <c r="AC140" s="12"/>
       <c r="AD140" s="12"/>
     </row>
-    <row r="141" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="141" spans="1:30" ht="15.75" customHeight="1">
       <c r="A141" s="44">
         <v>46442</v>
       </c>
@@ -9021,7 +9034,7 @@
       <c r="AC141" s="12"/>
       <c r="AD141" s="12"/>
     </row>
-    <row r="142" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="142" spans="1:30" ht="15.75" customHeight="1">
       <c r="A142" s="44">
         <v>46443</v>
       </c>
@@ -9069,7 +9082,7 @@
       <c r="AC142" s="12"/>
       <c r="AD142" s="12"/>
     </row>
-    <row r="143" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="143" spans="1:30" ht="15.75" customHeight="1">
       <c r="A143" s="44">
         <v>46444</v>
       </c>
@@ -9081,7 +9094,7 @@
       </c>
       <c r="F143" s="15"/>
       <c r="G143" s="19" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H143" s="15"/>
       <c r="I143" s="15"/>
@@ -9109,7 +9122,7 @@
       <c r="AC143" s="12"/>
       <c r="AD143" s="12"/>
     </row>
-    <row r="144" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="144" spans="1:30" ht="15.75" customHeight="1">
       <c r="A144" s="44">
         <v>46445</v>
       </c>
@@ -9121,7 +9134,7 @@
       </c>
       <c r="F144" s="15"/>
       <c r="G144" s="19" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H144" s="19" t="s">
         <v>25</v>
@@ -9153,7 +9166,7 @@
       <c r="AC144" s="12"/>
       <c r="AD144" s="12"/>
     </row>
-    <row r="145" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="145" spans="1:30" ht="15.75" customHeight="1">
       <c r="A145" s="44">
         <v>46447</v>
       </c>
@@ -9165,7 +9178,7 @@
       </c>
       <c r="F145" s="15"/>
       <c r="G145" s="19" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H145" s="15" t="s">
         <v>25</v>
@@ -9197,7 +9210,7 @@
       <c r="AC145" s="12"/>
       <c r="AD145" s="12"/>
     </row>
-    <row r="146" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="146" spans="1:30" ht="15.75" customHeight="1">
       <c r="A146" s="44">
         <v>46447</v>
       </c>
@@ -9209,7 +9222,7 @@
       </c>
       <c r="F146" s="15"/>
       <c r="G146" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H146" s="15" t="s">
         <v>20</v>
@@ -9241,7 +9254,7 @@
       <c r="AC146" s="12"/>
       <c r="AD146" s="12"/>
     </row>
-    <row r="147" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="147" spans="1:30" ht="15.75" customHeight="1">
       <c r="A147" s="44">
         <v>46447</v>
       </c>
@@ -9253,7 +9266,7 @@
       </c>
       <c r="F147" s="15"/>
       <c r="G147" s="19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H147" s="15"/>
       <c r="I147" s="19" t="s">
@@ -9283,7 +9296,7 @@
       <c r="AC147" s="12"/>
       <c r="AD147" s="12"/>
     </row>
-    <row r="148" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="148" spans="1:30" ht="15.75" customHeight="1">
       <c r="A148" s="44">
         <v>46448</v>
       </c>
@@ -9299,7 +9312,7 @@
       </c>
       <c r="F148" s="15"/>
       <c r="G148" s="19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H148" s="15" t="s">
         <v>57</v>
@@ -9331,7 +9344,7 @@
       <c r="AC148" s="12"/>
       <c r="AD148" s="12"/>
     </row>
-    <row r="149" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="149" spans="1:30" ht="15.75" customHeight="1">
       <c r="A149" s="44">
         <v>46449</v>
       </c>
@@ -9383,7 +9396,7 @@
       <c r="AC149" s="12"/>
       <c r="AD149" s="12"/>
     </row>
-    <row r="150" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="150" spans="1:30" ht="15.75" customHeight="1">
       <c r="A150" s="44">
         <v>46450</v>
       </c>
@@ -9431,7 +9444,7 @@
       <c r="AC150" s="12"/>
       <c r="AD150" s="12"/>
     </row>
-    <row r="151" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="151" spans="1:30" ht="15.75" customHeight="1">
       <c r="A151" s="44">
         <v>46450</v>
       </c>
@@ -9443,7 +9456,7 @@
       </c>
       <c r="F151" s="15"/>
       <c r="G151" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H151" s="15" t="s">
         <v>25</v>
@@ -9475,7 +9488,7 @@
       <c r="AC151" s="12"/>
       <c r="AD151" s="12"/>
     </row>
-    <row r="152" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="152" spans="1:30" ht="15.75" customHeight="1">
       <c r="A152" s="44">
         <v>46450</v>
       </c>
@@ -9487,7 +9500,7 @@
       </c>
       <c r="F152" s="15"/>
       <c r="G152" s="19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H152" s="15" t="s">
         <v>25</v>
@@ -9497,7 +9510,7 @@
       </c>
       <c r="J152" s="15"/>
       <c r="K152" s="19" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L152" s="15"/>
       <c r="M152" s="15" t="s">
@@ -9521,7 +9534,7 @@
       <c r="AC152" s="12"/>
       <c r="AD152" s="12"/>
     </row>
-    <row r="153" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="153" spans="1:30" ht="15.75" customHeight="1">
       <c r="A153" s="45">
         <v>46450</v>
       </c>
@@ -9573,7 +9586,7 @@
       <c r="AC153" s="12"/>
       <c r="AD153" s="12"/>
     </row>
-    <row r="154" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="154" spans="1:30" ht="15.75" customHeight="1">
       <c r="A154" s="44">
         <v>46452</v>
       </c>
@@ -9589,7 +9602,7 @@
       </c>
       <c r="F154" s="15"/>
       <c r="G154" s="19" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H154" s="15" t="s">
         <v>85</v>
@@ -9621,7 +9634,7 @@
       <c r="AC154" s="12"/>
       <c r="AD154" s="12"/>
     </row>
-    <row r="155" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="155" spans="1:30" ht="15.75" customHeight="1">
       <c r="A155" s="44">
         <v>46454</v>
       </c>
@@ -9633,7 +9646,7 @@
       </c>
       <c r="F155" s="15"/>
       <c r="G155" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H155" s="15" t="s">
         <v>20</v>
@@ -9665,7 +9678,7 @@
       <c r="AC155" s="30"/>
       <c r="AD155" s="30"/>
     </row>
-    <row r="156" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="156" spans="1:30" ht="15.75" customHeight="1">
       <c r="A156" s="44">
         <v>46456</v>
       </c>
@@ -9693,7 +9706,7 @@
         <v>17</v>
       </c>
       <c r="K156" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L156" s="15"/>
       <c r="M156" s="15" t="s">
@@ -9717,7 +9730,7 @@
       <c r="AC156" s="12"/>
       <c r="AD156" s="12"/>
     </row>
-    <row r="157" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="157" spans="1:30" ht="15.75" customHeight="1">
       <c r="A157" s="44">
         <v>46456</v>
       </c>
@@ -9769,7 +9782,7 @@
       <c r="AC157" s="12"/>
       <c r="AD157" s="12"/>
     </row>
-    <row r="158" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="158" spans="1:30" ht="15.75" customHeight="1">
       <c r="A158" s="44">
         <v>46457</v>
       </c>
@@ -9781,7 +9794,7 @@
       </c>
       <c r="F158" s="15"/>
       <c r="G158" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H158" s="15" t="s">
         <v>46</v>
@@ -9813,7 +9826,7 @@
       <c r="AC158" s="12"/>
       <c r="AD158" s="12"/>
     </row>
-    <row r="159" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="159" spans="1:30" ht="15.75" customHeight="1">
       <c r="A159" s="44">
         <v>46458</v>
       </c>
@@ -9863,7 +9876,7 @@
       <c r="AC159" s="12"/>
       <c r="AD159" s="12"/>
     </row>
-    <row r="160" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="160" spans="1:30" ht="15.75" customHeight="1">
       <c r="A160" s="44">
         <v>46458</v>
       </c>
@@ -9915,7 +9928,7 @@
       <c r="AC160" s="12"/>
       <c r="AD160" s="12"/>
     </row>
-    <row r="161" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="161" spans="1:30" ht="15.75" customHeight="1">
       <c r="A161" s="44">
         <v>46459</v>
       </c>
@@ -9965,7 +9978,7 @@
       <c r="AC161" s="12"/>
       <c r="AD161" s="12"/>
     </row>
-    <row r="162" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="162" spans="1:30" ht="15.75" customHeight="1">
       <c r="A162" s="44">
         <v>46460</v>
       </c>
@@ -9979,7 +9992,7 @@
       </c>
       <c r="F162" s="15"/>
       <c r="G162" s="19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H162" s="15" t="s">
         <v>15</v>
@@ -10011,7 +10024,7 @@
       <c r="AC162" s="12"/>
       <c r="AD162" s="12"/>
     </row>
-    <row r="163" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="163" spans="1:30" ht="15.75" customHeight="1">
       <c r="A163" s="44">
         <v>46463</v>
       </c>
@@ -10063,7 +10076,7 @@
       <c r="AC163" s="12"/>
       <c r="AD163" s="12"/>
     </row>
-    <row r="164" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="164" spans="1:30" ht="15.75" customHeight="1">
       <c r="A164" s="44">
         <v>46463</v>
       </c>
@@ -10079,7 +10092,7 @@
       </c>
       <c r="F164" s="15"/>
       <c r="G164" s="19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H164" s="19" t="s">
         <v>46</v>
@@ -10091,7 +10104,7 @@
         <v>48</v>
       </c>
       <c r="K164" s="19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L164" s="15"/>
       <c r="M164" s="15" t="s">
@@ -10115,7 +10128,7 @@
       <c r="AC164" s="12"/>
       <c r="AD164" s="12"/>
     </row>
-    <row r="165" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="165" spans="1:30" ht="15.75" customHeight="1">
       <c r="A165" s="44">
         <v>46464</v>
       </c>
@@ -10163,7 +10176,7 @@
       <c r="AC165" s="12"/>
       <c r="AD165" s="12"/>
     </row>
-    <row r="166" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="166" spans="1:30" ht="15.75" customHeight="1">
       <c r="A166" s="44">
         <v>46464</v>
       </c>
@@ -10179,7 +10192,7 @@
       </c>
       <c r="F166" s="15"/>
       <c r="G166" s="19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H166" s="15"/>
       <c r="I166" s="15" t="s">
@@ -10211,7 +10224,7 @@
       <c r="AC166" s="12"/>
       <c r="AD166" s="12"/>
     </row>
-    <row r="167" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="167" spans="1:30" ht="15.75" customHeight="1">
       <c r="A167" s="44">
         <v>46468</v>
       </c>
@@ -10225,7 +10238,7 @@
       </c>
       <c r="F167" s="15"/>
       <c r="G167" s="19" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H167" s="15"/>
       <c r="I167" s="15"/>
@@ -10253,12 +10266,12 @@
       <c r="AC167" s="12"/>
       <c r="AD167" s="12"/>
     </row>
-    <row r="168" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="168" spans="1:30" ht="15.75" customHeight="1">
       <c r="A168" s="44">
         <v>46475</v>
       </c>
       <c r="B168" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C168" s="22">
         <v>0.60416666666666663</v>
@@ -10271,7 +10284,7 @@
       </c>
       <c r="F168" s="15"/>
       <c r="G168" s="19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H168" s="15" t="s">
         <v>57</v>
@@ -10303,7 +10316,7 @@
       <c r="AC168" s="12"/>
       <c r="AD168" s="12"/>
     </row>
-    <row r="169" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="169" spans="1:30" ht="15.75" customHeight="1">
       <c r="A169" s="44">
         <v>46479</v>
       </c>
@@ -10351,7 +10364,7 @@
       <c r="AC169" s="12"/>
       <c r="AD169" s="12"/>
     </row>
-    <row r="170" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="170" spans="1:30" ht="15.75" customHeight="1">
       <c r="A170" s="44">
         <v>46484</v>
       </c>
@@ -10403,7 +10416,7 @@
       <c r="AC170" s="12"/>
       <c r="AD170" s="12"/>
     </row>
-    <row r="171" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="171" spans="1:30" ht="15.75" customHeight="1">
       <c r="A171" s="44">
         <v>46484</v>
       </c>
@@ -10425,13 +10438,13 @@
         <v>57</v>
       </c>
       <c r="I171" s="15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J171" s="15" t="s">
         <v>17</v>
       </c>
       <c r="K171" s="15" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L171" s="15"/>
       <c r="M171" s="15" t="s">
@@ -10455,7 +10468,7 @@
       <c r="AC171" s="12"/>
       <c r="AD171" s="12"/>
     </row>
-    <row r="172" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="172" spans="1:30" ht="15.75" customHeight="1">
       <c r="A172" s="44">
         <v>46484</v>
       </c>
@@ -10480,7 +10493,7 @@
         <v>16</v>
       </c>
       <c r="J172" s="15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K172" s="15"/>
       <c r="L172" s="15"/>
@@ -10503,7 +10516,7 @@
       <c r="AC172" s="12"/>
       <c r="AD172" s="12"/>
     </row>
-    <row r="173" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="173" spans="1:30" ht="15.75" customHeight="1">
       <c r="A173" s="44">
         <v>46485</v>
       </c>
@@ -10515,7 +10528,7 @@
       </c>
       <c r="F173" s="15"/>
       <c r="G173" s="19" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H173" s="15" t="s">
         <v>46</v>
@@ -10549,7 +10562,7 @@
       <c r="AC173" s="12"/>
       <c r="AD173" s="12"/>
     </row>
-    <row r="174" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="174" spans="1:30" ht="15.75" customHeight="1">
       <c r="A174" s="44">
         <v>46491</v>
       </c>
@@ -10601,7 +10614,7 @@
       <c r="AC174" s="12"/>
       <c r="AD174" s="12"/>
     </row>
-    <row r="175" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="175" spans="1:30" ht="15.75" customHeight="1">
       <c r="A175" s="45">
         <v>46492</v>
       </c>
@@ -10653,7 +10666,7 @@
       <c r="AC175" s="12"/>
       <c r="AD175" s="12"/>
     </row>
-    <row r="176" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="176" spans="1:30" ht="15.75" customHeight="1">
       <c r="A176" s="44">
         <v>46493</v>
       </c>
@@ -10665,7 +10678,7 @@
       </c>
       <c r="F176" s="15"/>
       <c r="G176" s="19" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H176" s="15"/>
       <c r="I176" s="15"/>
@@ -10693,7 +10706,7 @@
       <c r="AC176" s="12"/>
       <c r="AD176" s="12"/>
     </row>
-    <row r="177" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="177" spans="1:30" ht="15.75" customHeight="1">
       <c r="A177" s="44">
         <v>46493</v>
       </c>
@@ -10705,7 +10718,7 @@
       </c>
       <c r="F177" s="15"/>
       <c r="G177" s="19" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H177" s="15"/>
       <c r="I177" s="19" t="s">
@@ -10713,7 +10726,7 @@
       </c>
       <c r="J177" s="15"/>
       <c r="K177" s="19" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L177" s="15"/>
       <c r="M177" s="15" t="s">
@@ -10737,7 +10750,7 @@
       <c r="AC177" s="12"/>
       <c r="AD177" s="12"/>
     </row>
-    <row r="178" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="178" spans="1:30" ht="15.75" customHeight="1">
       <c r="A178" s="44">
         <v>46494</v>
       </c>
@@ -10787,7 +10800,7 @@
       <c r="AC178" s="12"/>
       <c r="AD178" s="12"/>
     </row>
-    <row r="179" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="179" spans="1:30" ht="15.75" customHeight="1">
       <c r="A179" s="44">
         <v>46498</v>
       </c>
@@ -10839,7 +10852,7 @@
       <c r="AC179" s="12"/>
       <c r="AD179" s="12"/>
     </row>
-    <row r="180" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="180" spans="1:30" ht="15.75" customHeight="1">
       <c r="A180" s="44">
         <v>46499</v>
       </c>
@@ -10851,7 +10864,7 @@
       </c>
       <c r="F180" s="15"/>
       <c r="G180" s="19" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H180" s="15"/>
       <c r="I180" s="15" t="s">
@@ -10881,7 +10894,7 @@
       <c r="AC180" s="12"/>
       <c r="AD180" s="12"/>
     </row>
-    <row r="181" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="181" spans="1:30" ht="15.75" customHeight="1">
       <c r="A181" s="44">
         <v>46499</v>
       </c>
@@ -10912,7 +10925,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="182" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="182" spans="1:30" ht="15.75" customHeight="1">
       <c r="A182" s="44">
         <v>46499</v>
       </c>
@@ -10924,7 +10937,7 @@
       </c>
       <c r="F182" s="15"/>
       <c r="G182" s="19" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H182" s="19" t="s">
         <v>46</v>
@@ -10939,7 +10952,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="183" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="183" spans="1:30" ht="15.75" customHeight="1">
       <c r="A183" s="44">
         <v>46500</v>
       </c>
@@ -10970,7 +10983,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="184" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="184" spans="1:30" ht="15.75" customHeight="1">
       <c r="A184" s="44">
         <v>46501</v>
       </c>
@@ -10982,7 +10995,7 @@
       </c>
       <c r="F184" s="15"/>
       <c r="G184" s="19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H184" s="19" t="s">
         <v>25</v>
@@ -10997,7 +11010,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="185" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="185" spans="1:30" ht="15.75" customHeight="1">
       <c r="A185" s="44">
         <v>46501</v>
       </c>
@@ -11013,7 +11026,7 @@
       </c>
       <c r="F185" s="15"/>
       <c r="G185" s="19" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H185" s="15" t="s">
         <v>85</v>
@@ -11028,7 +11041,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="186" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="186" spans="1:30" ht="15.75" customHeight="1">
       <c r="A186" s="44">
         <v>46505</v>
       </c>
@@ -11063,7 +11076,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="187" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="187" spans="1:30" ht="15.75" customHeight="1">
       <c r="A187" s="44">
         <v>46507</v>
       </c>
@@ -11075,7 +11088,7 @@
       </c>
       <c r="F187" s="15"/>
       <c r="G187" s="19" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H187" s="15"/>
       <c r="I187" s="15"/>
@@ -11086,7 +11099,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="188" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="188" spans="1:30" ht="15.75" customHeight="1">
       <c r="A188" s="44">
         <v>46507</v>
       </c>
@@ -11098,7 +11111,7 @@
       </c>
       <c r="F188" s="15"/>
       <c r="G188" s="19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H188" s="19" t="s">
         <v>25</v>
@@ -11113,7 +11126,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="189" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="189" spans="1:30" ht="15.75" customHeight="1">
       <c r="A189" s="44">
         <v>46511</v>
       </c>
@@ -11129,7 +11142,7 @@
       </c>
       <c r="F189" s="15"/>
       <c r="G189" s="19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H189" s="15" t="s">
         <v>57</v>
@@ -11144,7 +11157,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="190" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="190" spans="1:30" ht="15.75" customHeight="1">
       <c r="A190" s="44">
         <v>46512</v>
       </c>
@@ -11179,7 +11192,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="191" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="191" spans="1:30" ht="15.75" customHeight="1">
       <c r="A191" s="45">
         <v>46513</v>
       </c>
@@ -11214,7 +11227,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="192" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="192" spans="1:30" ht="15.75" customHeight="1">
       <c r="A192" s="44">
         <v>46519</v>
       </c>
@@ -11249,7 +11262,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="193" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="193" spans="1:13" ht="15.75" customHeight="1">
       <c r="A193" s="44">
         <v>46519</v>
       </c>
@@ -11271,20 +11284,20 @@
         <v>57</v>
       </c>
       <c r="I193" s="15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J193" s="15" t="s">
         <v>17</v>
       </c>
       <c r="K193" s="15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L193" s="15"/>
       <c r="M193" s="15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="194" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="194" spans="1:13" ht="15.75" customHeight="1">
       <c r="A194" s="44">
         <v>46519</v>
       </c>
@@ -11309,7 +11322,7 @@
         <v>16</v>
       </c>
       <c r="J194" s="15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K194" s="15"/>
       <c r="L194" s="15"/>
@@ -11317,7 +11330,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="195" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="195" spans="1:13" ht="15.75" customHeight="1">
       <c r="A195" s="44">
         <v>46521</v>
       </c>
@@ -11348,7 +11361,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="196" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="196" spans="1:13" ht="15.75" customHeight="1">
       <c r="A196" s="44">
         <v>46522</v>
       </c>
@@ -11381,7 +11394,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="197" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="197" spans="1:13" ht="15.75" customHeight="1">
       <c r="A197" s="44">
         <v>46526</v>
       </c>
@@ -11416,7 +11429,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="198" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="198" spans="1:13" ht="15.75" customHeight="1">
       <c r="A198" s="44">
         <v>46526</v>
       </c>
@@ -11428,7 +11441,7 @@
       </c>
       <c r="F198" s="15"/>
       <c r="G198" s="19" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H198" s="15" t="s">
         <v>25</v>
@@ -11443,7 +11456,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="199" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="199" spans="1:13" ht="15.75" customHeight="1">
       <c r="A199" s="44">
         <v>46533</v>
       </c>
@@ -11478,7 +11491,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="200" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="200" spans="1:13" ht="15.75" customHeight="1">
       <c r="A200" s="44">
         <v>46534</v>
       </c>
@@ -11490,7 +11503,7 @@
       </c>
       <c r="F200" s="15"/>
       <c r="G200" s="19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H200" s="15"/>
       <c r="I200" s="19" t="s">
@@ -11503,7 +11516,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="201" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="201" spans="1:13" ht="15.75" customHeight="1">
       <c r="A201" s="44">
         <v>46535</v>
       </c>
@@ -11515,7 +11528,7 @@
       </c>
       <c r="F201" s="15"/>
       <c r="G201" s="19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H201" s="15"/>
       <c r="I201" s="15"/>
@@ -11526,7 +11539,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="202" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="202" spans="1:13" ht="15.75" customHeight="1">
       <c r="A202" s="44">
         <v>46539</v>
       </c>
@@ -11542,7 +11555,7 @@
       </c>
       <c r="F202" s="15"/>
       <c r="G202" s="19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H202" s="15" t="s">
         <v>57</v>
@@ -11557,7 +11570,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="203" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="203" spans="1:13" ht="15.75" customHeight="1">
       <c r="A203" s="44">
         <v>46540</v>
       </c>
@@ -11592,7 +11605,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="204" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="204" spans="1:13" ht="15.75" customHeight="1">
       <c r="A204" s="44">
         <v>46540</v>
       </c>
@@ -11625,7 +11638,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="205" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="205" spans="1:13" ht="15.75" customHeight="1">
       <c r="A205" s="44">
         <v>46542</v>
       </c>
@@ -11656,7 +11669,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="206" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="206" spans="1:13" ht="15.75" customHeight="1">
       <c r="A206" s="44">
         <v>46542</v>
       </c>
@@ -11672,7 +11685,7 @@
       </c>
       <c r="F206" s="15"/>
       <c r="G206" s="19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H206" s="15" t="s">
         <v>57</v>
@@ -11681,17 +11694,17 @@
         <v>16</v>
       </c>
       <c r="J206" s="15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K206" s="15" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L206" s="15"/>
       <c r="M206" s="15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="207" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="207" spans="1:13" ht="15.75" customHeight="1">
       <c r="A207" s="46">
         <v>46543</v>
       </c>
@@ -11724,7 +11737,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="208" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="208" spans="1:13" ht="15.75" customHeight="1">
       <c r="A208" s="47">
         <v>46545</v>
       </c>
@@ -11758,7 +11771,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="209" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="209" spans="1:13" ht="15.75" customHeight="1">
       <c r="A209" s="46">
         <v>46549</v>
       </c>
@@ -11785,12 +11798,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="210" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="210" spans="1:13" ht="15.75" customHeight="1">
       <c r="A210" s="46">
         <v>46552</v>
       </c>
       <c r="B210" s="37" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C210" s="39">
         <v>0.35416666666666669</v>
@@ -11803,7 +11816,7 @@
       </c>
       <c r="F210" s="41"/>
       <c r="G210" s="24" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H210" s="15" t="s">
         <v>46</v>
@@ -11818,7 +11831,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="211" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="211" spans="1:13" ht="15.75" customHeight="1">
       <c r="A211" s="46">
         <v>46554</v>
       </c>
@@ -11846,14 +11859,14 @@
         <v>17</v>
       </c>
       <c r="K211" s="41" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L211" s="41"/>
       <c r="M211" s="15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="212" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="212" spans="1:13" ht="15.75" customHeight="1">
       <c r="A212" s="46">
         <v>46563</v>
       </c>
@@ -11884,7 +11897,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="213" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="213" spans="1:13" ht="15.75" customHeight="1">
       <c r="A213" s="46">
         <v>46568</v>
       </c>
@@ -11896,7 +11909,7 @@
       </c>
       <c r="F213" s="41"/>
       <c r="G213" s="24" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H213" s="15"/>
       <c r="I213" s="15" t="s">
@@ -11909,7 +11922,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="214" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="214" spans="1:13" ht="15.75" customHeight="1">
       <c r="A214" s="46">
         <v>46592</v>
       </c>
@@ -11921,7 +11934,7 @@
       </c>
       <c r="F214" s="41"/>
       <c r="G214" s="24" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H214" s="19" t="s">
         <v>25</v>
@@ -11936,7 +11949,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="215" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="215" spans="1:13" ht="15.75" customHeight="1">
       <c r="A215" s="46">
         <v>46597</v>
       </c>
@@ -11948,7 +11961,7 @@
       </c>
       <c r="F215" s="41"/>
       <c r="G215" s="24" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H215" s="19" t="s">
         <v>25</v>
@@ -11963,7 +11976,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="216" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="216" spans="1:13" ht="15.75" customHeight="1">
       <c r="A216" s="46">
         <v>46623</v>
       </c>
@@ -11975,7 +11988,7 @@
       </c>
       <c r="F216" s="41"/>
       <c r="G216" s="24" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H216" s="15"/>
       <c r="I216" s="15"/>
@@ -11986,7 +11999,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="217" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="217" spans="1:13" ht="15.75" customHeight="1">
       <c r="A217" s="46">
         <v>46630</v>
       </c>
@@ -11998,7 +12011,7 @@
       </c>
       <c r="F217" s="41"/>
       <c r="G217" s="24" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H217" s="15"/>
       <c r="I217" s="15"/>
@@ -16721,12 +16734,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:M217" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="Work Readiness Training 101 📗"/>
-        <filter val="Work Readiness Training 201 (virtual) 📗"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M217">
       <sortCondition ref="A1:A217"/>
     </sortState>
@@ -16777,11 +16784,15 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="K51" r:id="rId1" xr:uid="{00E007F9-447C-4487-A00B-5A6C3EA6636B}"/>
+    <hyperlink ref="K63" r:id="rId2" xr:uid="{98622C98-31A5-41DD-B43F-A720A440A5A9}"/>
+    <hyperlink ref="K68" r:id="rId3" xr:uid="{C9D19773-6F55-4BAF-82A9-D84E17C370F2}"/>
+    <hyperlink ref="K86" r:id="rId4" xr:uid="{C4884129-06F2-48DB-B3E1-78C695AA16E7}"/>
+    <hyperlink ref="K92" r:id="rId5" xr:uid="{4FA583BB-674C-4565-88E5-E0217B2A9BA1}"/>
   </hyperlinks>
   <printOptions gridLines="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId6"/>
 </worksheet>
 </file>
 
@@ -16800,21 +16811,21 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C2" s="16">
         <v>46203</v>
@@ -16822,16 +16833,16 @@
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
       <c r="A3" s="18" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C3" s="20">
         <v>46199</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E3" s="18"/>
       <c r="F3" s="18"/>
@@ -16858,24 +16869,24 @@
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
       <c r="A4" s="18" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C4" s="20">
         <v>46199</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C5" s="21">
         <v>46266</v>
@@ -16883,10 +16894,10 @@
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C6" s="16">
         <v>46356</v>
@@ -16894,34 +16905,34 @@
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
       <c r="A8" s="19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
       <c r="A9" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C10" s="21">
         <v>46120</v>
@@ -16929,20 +16940,20 @@
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
       <c r="A11" s="19" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="15" customHeight="1">
       <c r="A13" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -16986,7 +16997,7 @@
         <v>4</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>6</v>
@@ -17022,16 +17033,16 @@
     </row>
     <row r="2" spans="1:26">
       <c r="A2" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>46</v>
@@ -17042,16 +17053,16 @@
         <v>46456</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:26">
@@ -17059,16 +17070,16 @@
         <v>46499</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -17134,15 +17145,15 @@
         <v>10</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1">
       <c r="A2" s="11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="15" t="s">
@@ -17159,7 +17170,7 @@
         <v>21</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I2" s="19" t="s">
         <v>23</v>
@@ -17169,17 +17180,17 @@
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>28</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="19" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F3" s="15" t="s">
         <v>105</v>
@@ -17209,7 +17220,7 @@
         <v>21</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I4" s="19" t="s">
         <v>23</v>
@@ -17219,7 +17230,7 @@
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1">
       <c r="A5" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>39</v>
@@ -17273,7 +17284,7 @@
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1">
       <c r="A7" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="19" t="s">
@@ -17281,7 +17292,7 @@
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="19" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F7" s="19" t="s">
         <v>57</v>
@@ -17295,7 +17306,7 @@
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1">
       <c r="A8" s="11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="15" t="s">
@@ -17322,7 +17333,7 @@
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
       <c r="A9" s="11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="15" t="s">
@@ -17336,7 +17347,7 @@
         <v>57</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H9" s="15"/>
       <c r="I9" s="15"/>
@@ -17345,7 +17356,7 @@
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="15" t="s">
@@ -17372,7 +17383,7 @@
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="15" t="s">
@@ -17399,7 +17410,7 @@
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1">
       <c r="A12" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="19" t="s">
@@ -17407,7 +17418,7 @@
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="19" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F12" s="19" t="s">
         <v>57</v>
@@ -17422,7 +17433,7 @@
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="15" t="s">
@@ -17449,7 +17460,7 @@
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1">
       <c r="A14" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="15" t="s">
@@ -17476,7 +17487,7 @@
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="19" t="s">
@@ -17501,7 +17512,7 @@
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="15" t="s">
@@ -17515,7 +17526,7 @@
         <v>57</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="15"/>
@@ -17524,7 +17535,7 @@
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="19" t="s">
@@ -17547,7 +17558,7 @@
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="15" t="s">
@@ -17574,7 +17585,7 @@
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="19" t="s">
@@ -17597,7 +17608,7 @@
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1">
       <c r="A20" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="15" t="s">
@@ -17624,7 +17635,7 @@
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1">
       <c r="A21" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="19" t="s">
@@ -17632,7 +17643,7 @@
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="19" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F21" s="15" t="s">
         <v>105</v>
@@ -17647,7 +17658,7 @@
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B22" s="13"/>
       <c r="C22" s="15" t="s">
@@ -17670,7 +17681,7 @@
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="15" t="s">
@@ -17697,7 +17708,7 @@
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="15" t="s">
@@ -17720,7 +17731,7 @@
     </row>
     <row r="25" spans="1:11" ht="15" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B25" s="13"/>
       <c r="C25" s="19" t="s">
@@ -17728,7 +17739,7 @@
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="19" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F25" s="15" t="s">
         <v>105</v>
@@ -17743,7 +17754,7 @@
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1">
       <c r="A26" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="15" t="s">
@@ -17770,7 +17781,7 @@
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B27" s="13"/>
       <c r="C27" s="15" t="s">
@@ -17784,7 +17795,7 @@
         <v>57</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H27" s="15"/>
       <c r="I27" s="15"/>
@@ -17793,7 +17804,7 @@
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="19" t="s">
@@ -17801,7 +17812,7 @@
       </c>
       <c r="D28" s="15"/>
       <c r="E28" s="19" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F28" s="15" t="s">
         <v>105</v>
@@ -17816,7 +17827,7 @@
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B29" s="13"/>
       <c r="C29" s="15" t="s">
@@ -17843,7 +17854,7 @@
     </row>
     <row r="30" spans="1:11" ht="15" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>121</v>
@@ -17865,14 +17876,14 @@
         <v>123</v>
       </c>
       <c r="I30" s="19" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J30" s="15"/>
       <c r="K30" s="15"/>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B31" s="13"/>
       <c r="C31" s="15" t="s">
@@ -17899,7 +17910,7 @@
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B32" s="13"/>
       <c r="C32" s="19" t="s">
@@ -17922,7 +17933,7 @@
     </row>
     <row r="33" spans="1:11" ht="15" customHeight="1">
       <c r="A33" s="11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B33" s="13"/>
       <c r="C33" s="19" t="s">
@@ -17945,7 +17956,7 @@
     </row>
     <row r="34" spans="1:11" ht="15" customHeight="1">
       <c r="A34" s="11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B34" s="13"/>
       <c r="C34" s="19" t="s">
@@ -17953,7 +17964,7 @@
       </c>
       <c r="D34" s="15"/>
       <c r="E34" s="19" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F34" s="15" t="s">
         <v>105</v>
@@ -17968,7 +17979,7 @@
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1">
       <c r="A35" s="11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="15" t="s">
@@ -17995,7 +18006,7 @@
     </row>
     <row r="36" spans="1:11" ht="15" customHeight="1">
       <c r="A36" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B36" s="13"/>
       <c r="C36" s="19" t="s">
@@ -18003,7 +18014,7 @@
       </c>
       <c r="D36" s="15"/>
       <c r="E36" s="19" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F36" s="15" t="s">
         <v>105</v>
@@ -18018,7 +18029,7 @@
     </row>
     <row r="37" spans="1:11" ht="15" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B37" s="13"/>
       <c r="C37" s="19" t="s">
@@ -18026,7 +18037,7 @@
       </c>
       <c r="D37" s="15"/>
       <c r="E37" s="19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F37" s="15" t="s">
         <v>85</v>
@@ -18041,7 +18052,7 @@
     </row>
     <row r="38" spans="1:11" ht="15" customHeight="1">
       <c r="A38" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B38" s="13"/>
       <c r="C38" s="15" t="s">
@@ -18055,18 +18066,18 @@
         <v>57</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H38" s="15"/>
       <c r="I38" s="19" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J38" s="15"/>
       <c r="K38" s="15"/>
     </row>
     <row r="39" spans="1:11" ht="15" customHeight="1">
       <c r="A39" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B39" s="13"/>
       <c r="C39" s="15" t="s">
@@ -18093,7 +18104,7 @@
     </row>
     <row r="40" spans="1:11" ht="15" customHeight="1">
       <c r="A40" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B40" s="13"/>
       <c r="C40" s="15" t="s">
@@ -18101,7 +18112,7 @@
       </c>
       <c r="D40" s="15"/>
       <c r="E40" s="19" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F40" s="15" t="s">
         <v>85</v>
@@ -18116,7 +18127,7 @@
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1">
       <c r="A41" s="11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B41" s="13"/>
       <c r="C41" s="15" t="s">
@@ -18143,7 +18154,7 @@
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1">
       <c r="A42" s="11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B42" s="13"/>
       <c r="C42" s="15" t="s">
@@ -18151,7 +18162,7 @@
       </c>
       <c r="D42" s="15"/>
       <c r="E42" s="19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F42" s="15" t="s">
         <v>57</v>
@@ -18166,7 +18177,7 @@
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1">
       <c r="A43" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="15" t="s">
@@ -18193,7 +18204,7 @@
     </row>
     <row r="44" spans="1:11" ht="15" customHeight="1">
       <c r="A44" s="11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B44" s="13"/>
       <c r="C44" s="15" t="s">
@@ -18201,7 +18212,7 @@
       </c>
       <c r="D44" s="15"/>
       <c r="E44" s="19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F44" s="15" t="s">
         <v>77</v>
@@ -18216,7 +18227,7 @@
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1">
       <c r="A45" s="11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B45" s="13"/>
       <c r="C45" s="15" t="s">
@@ -18243,7 +18254,7 @@
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1">
       <c r="A46" s="11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B46" s="13"/>
       <c r="C46" s="15" t="s">
@@ -18257,7 +18268,7 @@
         <v>57</v>
       </c>
       <c r="G46" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H46" s="15"/>
       <c r="I46" s="15"/>
@@ -18266,7 +18277,7 @@
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1">
       <c r="A47" s="11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B47" s="13"/>
       <c r="C47" s="19" t="s">
@@ -18274,7 +18285,7 @@
       </c>
       <c r="D47" s="15"/>
       <c r="E47" s="19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F47" s="19" t="s">
         <v>38</v>
@@ -18289,7 +18300,7 @@
     </row>
     <row r="48" spans="1:11" ht="15" customHeight="1">
       <c r="A48" s="11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B48" s="13"/>
       <c r="C48" s="15" t="s">
@@ -18316,7 +18327,7 @@
     </row>
     <row r="49" spans="1:11" ht="15" customHeight="1">
       <c r="A49" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B49" s="13"/>
       <c r="C49" s="15" t="s">
@@ -18343,7 +18354,7 @@
     </row>
     <row r="50" spans="1:11" ht="15" customHeight="1">
       <c r="A50" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B50" s="13"/>
       <c r="C50" s="15" t="s">
@@ -18370,7 +18381,7 @@
     </row>
     <row r="51" spans="1:11" ht="15" customHeight="1">
       <c r="A51" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B51" s="13"/>
       <c r="C51" s="15" t="s">
@@ -18384,7 +18395,7 @@
         <v>57</v>
       </c>
       <c r="G51" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H51" s="15"/>
       <c r="I51" s="15"/>
@@ -18393,7 +18404,7 @@
     </row>
     <row r="52" spans="1:11" ht="15" customHeight="1">
       <c r="A52" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B52" s="13"/>
       <c r="C52" s="19" t="s">
@@ -18401,7 +18412,7 @@
       </c>
       <c r="D52" s="15"/>
       <c r="E52" s="19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F52" s="19" t="s">
         <v>85</v>
@@ -18416,7 +18427,7 @@
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B53" s="13"/>
       <c r="C53" s="15" t="s">
@@ -18443,7 +18454,7 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="11" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B54" s="13"/>
       <c r="C54" s="19" t="s">
@@ -18466,7 +18477,7 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B55" s="13"/>
       <c r="C55" s="15" t="s">
@@ -18474,7 +18485,7 @@
       </c>
       <c r="D55" s="15"/>
       <c r="E55" s="19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F55" s="15" t="s">
         <v>57</v>
@@ -18489,7 +18500,7 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B56" s="13"/>
       <c r="C56" s="15" t="s">
@@ -18516,7 +18527,7 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B57" s="13"/>
       <c r="C57" s="15" t="s">
@@ -18524,7 +18535,7 @@
       </c>
       <c r="D57" s="15"/>
       <c r="E57" s="19" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F57" s="15" t="s">
         <v>57</v>
@@ -18539,7 +18550,7 @@
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B58" s="13"/>
       <c r="C58" s="15" t="s">
@@ -18566,7 +18577,7 @@
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B59" s="13"/>
       <c r="C59" s="15" t="s">
@@ -18580,7 +18591,7 @@
         <v>57</v>
       </c>
       <c r="G59" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H59" s="15"/>
       <c r="I59" s="15"/>
@@ -18589,7 +18600,7 @@
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B60" s="13"/>
       <c r="C60" s="15" t="s">
@@ -18616,7 +18627,7 @@
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B61" s="13"/>
       <c r="C61" s="15" t="s">
@@ -18643,7 +18654,7 @@
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B62" s="13"/>
       <c r="C62" s="19" t="s">
@@ -18666,7 +18677,7 @@
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B63" s="13"/>
       <c r="C63" s="15" t="s">
@@ -18693,7 +18704,7 @@
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B64" s="13"/>
       <c r="C64" s="15" t="s">
@@ -18701,7 +18712,7 @@
       </c>
       <c r="D64" s="15"/>
       <c r="E64" s="19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F64" s="15" t="s">
         <v>57</v>
@@ -18716,7 +18727,7 @@
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B65" s="13"/>
       <c r="C65" s="19" t="s">
@@ -18739,7 +18750,7 @@
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B66" s="13"/>
       <c r="C66" s="19" t="s">
@@ -18747,7 +18758,7 @@
       </c>
       <c r="D66" s="15"/>
       <c r="E66" s="19" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F66" s="15" t="s">
         <v>85</v>
@@ -18789,7 +18800,7 @@
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B68" s="13"/>
       <c r="C68" s="15" t="s">
@@ -18803,7 +18814,7 @@
         <v>57</v>
       </c>
       <c r="G68" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H68" s="15"/>
       <c r="I68" s="15"/>
@@ -18839,7 +18850,7 @@
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B70" s="13"/>
       <c r="C70" s="15" t="s">
@@ -18862,17 +18873,17 @@
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C71" s="15" t="s">
         <v>55</v>
       </c>
       <c r="D71" s="15"/>
       <c r="E71" s="19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F71" s="15" t="s">
         <v>57</v>
@@ -18887,7 +18898,7 @@
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B72" s="13"/>
       <c r="C72" s="15" t="s">
@@ -18914,7 +18925,7 @@
     </row>
     <row r="73" spans="1:11">
       <c r="A73" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B73" s="13"/>
       <c r="C73" s="15" t="s">
@@ -18922,7 +18933,7 @@
       </c>
       <c r="D73" s="15"/>
       <c r="E73" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F73" s="15" t="s">
         <v>20</v>
@@ -18935,7 +18946,7 @@
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B74" s="13"/>
       <c r="C74" s="15" t="s">
@@ -18949,7 +18960,7 @@
         <v>57</v>
       </c>
       <c r="G74" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H74" s="15"/>
       <c r="I74" s="15"/>
@@ -18958,7 +18969,7 @@
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B75" s="13"/>
       <c r="C75" s="15" t="s">
@@ -18985,7 +18996,7 @@
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B76" s="13"/>
       <c r="C76" s="15" t="s">
@@ -19012,7 +19023,7 @@
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B77" s="13"/>
       <c r="C77" s="19" t="s">
@@ -19035,7 +19046,7 @@
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B78" s="13"/>
       <c r="C78" s="19" t="s">
@@ -19043,7 +19054,7 @@
       </c>
       <c r="D78" s="15"/>
       <c r="E78" s="19" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F78" s="15" t="s">
         <v>85</v>
@@ -19058,7 +19069,7 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B79" s="13"/>
       <c r="C79" s="15" t="s">
@@ -19085,7 +19096,7 @@
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B80" s="13"/>
       <c r="C80" s="15" t="s">
@@ -19112,7 +19123,7 @@
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B81" s="13"/>
       <c r="C81" s="15" t="s">
@@ -19120,7 +19131,7 @@
       </c>
       <c r="D81" s="15"/>
       <c r="E81" s="19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F81" s="15" t="s">
         <v>57</v>
@@ -19135,7 +19146,7 @@
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B82" s="27"/>
       <c r="C82" s="15" t="s">
@@ -19162,7 +19173,7 @@
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B83" s="27"/>
       <c r="C83" s="15" t="s">
@@ -19176,7 +19187,7 @@
         <v>57</v>
       </c>
       <c r="G83" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H83" s="15"/>
       <c r="I83" s="15"/>
@@ -19185,7 +19196,7 @@
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="26" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B84" s="27"/>
       <c r="C84" s="15" t="s">
@@ -19212,7 +19223,7 @@
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="26" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B85" s="27"/>
       <c r="C85" s="15" t="s">
@@ -19239,7 +19250,7 @@
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="26" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B86" s="27"/>
       <c r="C86" s="15" t="s">
@@ -19266,7 +19277,7 @@
     </row>
     <row r="87" spans="1:11">
       <c r="A87" s="26" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B87" s="27"/>
       <c r="C87" s="15" t="s">
@@ -19274,7 +19285,7 @@
       </c>
       <c r="D87" s="15"/>
       <c r="E87" s="19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F87" s="15" t="s">
         <v>57</v>
@@ -19289,7 +19300,7 @@
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="26" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B88" s="27"/>
       <c r="C88" s="15" t="s">
@@ -19303,7 +19314,7 @@
         <v>57</v>
       </c>
       <c r="G88" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H88" s="15"/>
       <c r="I88" s="15"/>

--- a/26-27_Admin_Calendar_Events_CTE-LL_Version.xlsx
+++ b/26-27_Admin_Calendar_Events_CTE-LL_Version.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lausd.sharepoint.com/teams/CTE-LLLeadership/Shared Documents/Calendaring/CTELL_Calendar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="8_{AFEB7EE0-A3A0-BE46-B68A-F48D580478B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2D36061-1B6C-4C02-B515-18FE3AA1DF2A}"/>
+  <xr:revisionPtr revIDLastSave="111" documentId="8_{AFEB7EE0-A3A0-BE46-B68A-F48D580478B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{620FA9F9-7316-4513-BFA0-926929FBA686}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -392,7 +392,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1823" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1823" uniqueCount="336">
   <si>
     <t>Date</t>
   </si>
@@ -908,6 +908,12 @@
     <t>Nancy</t>
   </si>
   <si>
+    <t>LAHSA</t>
+  </si>
+  <si>
+    <t>Diego Rivera LC</t>
+  </si>
+  <si>
     <t>LAUSD / CSUN Healthcare Symposium w/EITM (All Regions - Biotech &amp; Mental Health) 🧰</t>
   </si>
   <si>
@@ -941,6 +947,9 @@
     <t>Hovik</t>
   </si>
   <si>
+    <t>Luskin OIC</t>
+  </si>
+  <si>
     <t>JA Inspire 2027 🏫</t>
   </si>
   <si>
@@ -971,6 +980,9 @@
     <t>4th Annual ABOTA @ LA Superior Court</t>
   </si>
   <si>
+    <t>Roosevelt HS</t>
+  </si>
+  <si>
     <t>Final Procurement Purchases 💰</t>
   </si>
   <si>
@@ -978,6 +990,9 @@
   </si>
   <si>
     <t>CTE student field trip to ELAC. date needs to be confirmed</t>
+  </si>
+  <si>
+    <t>MCLC</t>
   </si>
   <si>
     <t>Perkins Q3 Budget Revision 💰</t>
@@ -2168,7 +2183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AD1000"/>
@@ -2247,7 +2262,7 @@
       <c r="AC1" s="12"/>
       <c r="AD1" s="12"/>
     </row>
-    <row r="2" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="2" spans="1:30" ht="15.75" customHeight="1">
       <c r="A2" s="30">
         <v>46119</v>
       </c>
@@ -2297,7 +2312,7 @@
       <c r="AC2" s="12"/>
       <c r="AD2" s="12"/>
     </row>
-    <row r="3" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="3" spans="1:30" ht="15.75" customHeight="1">
       <c r="A3" s="30">
         <v>46210</v>
       </c>
@@ -2349,7 +2364,7 @@
       <c r="AC3" s="12"/>
       <c r="AD3" s="12"/>
     </row>
-    <row r="4" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="4" spans="1:30" ht="15.75" customHeight="1">
       <c r="A4" s="30">
         <v>46227</v>
       </c>
@@ -2395,7 +2410,7 @@
       <c r="AC4" s="12"/>
       <c r="AD4" s="12"/>
     </row>
-    <row r="5" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="5" spans="1:30" ht="15.75" customHeight="1">
       <c r="A5" s="30">
         <v>46232</v>
       </c>
@@ -2441,7 +2456,7 @@
       <c r="AC5" s="12"/>
       <c r="AD5" s="12"/>
     </row>
-    <row r="6" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="6" spans="1:30" ht="15.75" customHeight="1">
       <c r="A6" s="30">
         <v>46233</v>
       </c>
@@ -2489,7 +2504,7 @@
       <c r="AC6" s="12"/>
       <c r="AD6" s="12"/>
     </row>
-    <row r="7" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="7" spans="1:30" ht="15.75" customHeight="1">
       <c r="A7" s="30">
         <v>46233</v>
       </c>
@@ -2537,7 +2552,7 @@
       <c r="AC7" s="12"/>
       <c r="AD7" s="12"/>
     </row>
-    <row r="8" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="8" spans="1:30" ht="15.75" customHeight="1">
       <c r="A8" s="30">
         <v>46237</v>
       </c>
@@ -2589,7 +2604,7 @@
       <c r="AC8" s="12"/>
       <c r="AD8" s="12"/>
     </row>
-    <row r="9" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="9" spans="1:30" ht="15.75" customHeight="1">
       <c r="A9" s="30">
         <v>46237</v>
       </c>
@@ -2641,7 +2656,7 @@
       <c r="AC9" s="12"/>
       <c r="AD9" s="12"/>
     </row>
-    <row r="10" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="10" spans="1:30" ht="15.75" customHeight="1">
       <c r="A10" s="30">
         <v>46239</v>
       </c>
@@ -2693,7 +2708,7 @@
       <c r="AC10" s="12"/>
       <c r="AD10" s="12"/>
     </row>
-    <row r="11" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="11" spans="1:30" ht="15.75" customHeight="1">
       <c r="A11" s="30">
         <v>46240</v>
       </c>
@@ -2747,7 +2762,7 @@
       <c r="AC11" s="12"/>
       <c r="AD11" s="12"/>
     </row>
-    <row r="12" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="12" spans="1:30" ht="15.75" customHeight="1">
       <c r="A12" s="30">
         <v>46246</v>
       </c>
@@ -2797,7 +2812,7 @@
       <c r="AC12" s="12"/>
       <c r="AD12" s="12"/>
     </row>
-    <row r="13" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="13" spans="1:30" ht="15.75" customHeight="1">
       <c r="A13" s="30">
         <v>46248</v>
       </c>
@@ -2847,7 +2862,7 @@
       <c r="AC13" s="12"/>
       <c r="AD13" s="12"/>
     </row>
-    <row r="14" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="14" spans="1:30" ht="15.75" customHeight="1">
       <c r="A14" s="30">
         <v>46248</v>
       </c>
@@ -2943,7 +2958,7 @@
       <c r="AC15" s="12"/>
       <c r="AD15" s="12"/>
     </row>
-    <row r="16" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="16" spans="1:30" ht="15.75" customHeight="1">
       <c r="A16" s="30">
         <v>46253</v>
       </c>
@@ -2995,7 +3010,7 @@
       <c r="AC16" s="12"/>
       <c r="AD16" s="12"/>
     </row>
-    <row r="17" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="17" spans="1:30" ht="15.75" customHeight="1">
       <c r="A17" s="30">
         <v>46258</v>
       </c>
@@ -3091,7 +3106,7 @@
       <c r="AC18" s="12"/>
       <c r="AD18" s="12"/>
     </row>
-    <row r="19" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="19" spans="1:30" ht="15.75" customHeight="1">
       <c r="A19" s="30">
         <v>46262</v>
       </c>
@@ -3133,7 +3148,7 @@
       <c r="AC19" s="12"/>
       <c r="AD19" s="12"/>
     </row>
-    <row r="20" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="20" spans="1:30" ht="15.75" customHeight="1">
       <c r="A20" s="30">
         <v>46262</v>
       </c>
@@ -3177,7 +3192,7 @@
       <c r="AC20" s="12"/>
       <c r="AD20" s="12"/>
     </row>
-    <row r="21" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="21" spans="1:30" ht="15.75" customHeight="1">
       <c r="A21" s="30">
         <v>46263</v>
       </c>
@@ -3227,7 +3242,7 @@
       <c r="AC21" s="12"/>
       <c r="AD21" s="12"/>
     </row>
-    <row r="22" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="22" spans="1:30" ht="15.75" customHeight="1">
       <c r="A22" s="30">
         <v>46265</v>
       </c>
@@ -3271,7 +3286,7 @@
       <c r="AC22" s="12"/>
       <c r="AD22" s="12"/>
     </row>
-    <row r="23" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="23" spans="1:30" ht="15.75" customHeight="1">
       <c r="A23" s="30">
         <v>46265</v>
       </c>
@@ -3313,7 +3328,7 @@
       <c r="AC23" s="12"/>
       <c r="AD23" s="12"/>
     </row>
-    <row r="24" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="24" spans="1:30" ht="15.75" customHeight="1">
       <c r="A24" s="30">
         <v>46265</v>
       </c>
@@ -3357,7 +3372,7 @@
       <c r="AC24" s="12"/>
       <c r="AD24" s="12"/>
     </row>
-    <row r="25" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="25" spans="1:30" ht="15.75" customHeight="1">
       <c r="A25" s="30">
         <v>46266</v>
       </c>
@@ -3405,7 +3420,7 @@
       <c r="AC25" s="12"/>
       <c r="AD25" s="12"/>
     </row>
-    <row r="26" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="26" spans="1:30" ht="15.75" customHeight="1">
       <c r="A26" s="30">
         <v>46267</v>
       </c>
@@ -3457,7 +3472,7 @@
       <c r="AC26" s="12"/>
       <c r="AD26" s="12"/>
     </row>
-    <row r="27" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="27" spans="1:30" ht="15.75" customHeight="1">
       <c r="A27" s="30">
         <v>46268</v>
       </c>
@@ -3509,7 +3524,7 @@
       <c r="AC27" s="12"/>
       <c r="AD27" s="12"/>
     </row>
-    <row r="28" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="28" spans="1:30" ht="15.75" customHeight="1">
       <c r="A28" s="40">
         <v>46268</v>
       </c>
@@ -3613,7 +3628,7 @@
       <c r="AC29" s="12"/>
       <c r="AD29" s="12"/>
     </row>
-    <row r="30" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="30" spans="1:30" ht="15.75" customHeight="1">
       <c r="A30" s="30">
         <v>46274</v>
       </c>
@@ -3657,7 +3672,7 @@
       <c r="AC30" s="12"/>
       <c r="AD30" s="12"/>
     </row>
-    <row r="31" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="31" spans="1:30" ht="15.75" customHeight="1">
       <c r="A31" s="30">
         <v>46274</v>
       </c>
@@ -3707,7 +3722,7 @@
       <c r="AC31" s="12"/>
       <c r="AD31" s="12"/>
     </row>
-    <row r="32" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="32" spans="1:30" ht="15.75" customHeight="1">
       <c r="A32" s="30">
         <v>46275</v>
       </c>
@@ -3751,7 +3766,7 @@
       <c r="AC32" s="12"/>
       <c r="AD32" s="12"/>
     </row>
-    <row r="33" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="33" spans="1:30" ht="15.75" customHeight="1">
       <c r="A33" s="30">
         <v>46276</v>
       </c>
@@ -3799,7 +3814,7 @@
       <c r="AC33" s="12"/>
       <c r="AD33" s="12"/>
     </row>
-    <row r="34" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="34" spans="1:30" ht="15.75" customHeight="1">
       <c r="A34" s="30">
         <v>46279</v>
       </c>
@@ -3843,7 +3858,7 @@
       <c r="AC34" s="12"/>
       <c r="AD34" s="12"/>
     </row>
-    <row r="35" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="35" spans="1:30" ht="15.75" customHeight="1">
       <c r="A35" s="30">
         <v>46280</v>
       </c>
@@ -3943,7 +3958,7 @@
       <c r="AC36" s="12"/>
       <c r="AD36" s="12"/>
     </row>
-    <row r="37" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="37" spans="1:30" ht="15.75" customHeight="1">
       <c r="A37" s="30">
         <v>46281</v>
       </c>
@@ -3993,7 +4008,7 @@
       <c r="AC37" s="12"/>
       <c r="AD37" s="12"/>
     </row>
-    <row r="38" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="38" spans="1:30" ht="15.75" customHeight="1">
       <c r="A38" s="30">
         <v>46282</v>
       </c>
@@ -4043,7 +4058,7 @@
       <c r="AC38" s="12"/>
       <c r="AD38" s="12"/>
     </row>
-    <row r="39" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="39" spans="1:30" ht="15.75" customHeight="1">
       <c r="A39" s="30">
         <v>46282</v>
       </c>
@@ -4095,7 +4110,7 @@
       <c r="AC39" s="12"/>
       <c r="AD39" s="12"/>
     </row>
-    <row r="40" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="40" spans="1:30" ht="15.75" customHeight="1">
       <c r="A40" s="30">
         <v>46283</v>
       </c>
@@ -4139,7 +4154,7 @@
       <c r="AC40" s="8"/>
       <c r="AD40" s="8"/>
     </row>
-    <row r="41" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="41" spans="1:30" ht="15.75" customHeight="1">
       <c r="A41" s="30">
         <v>46283</v>
       </c>
@@ -4187,7 +4202,7 @@
       <c r="AC41" s="12"/>
       <c r="AD41" s="12"/>
     </row>
-    <row r="42" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="42" spans="1:30" ht="15.75" customHeight="1">
       <c r="A42" s="30">
         <v>46284</v>
       </c>
@@ -4235,7 +4250,7 @@
       <c r="AC42" s="8"/>
       <c r="AD42" s="8"/>
     </row>
-    <row r="43" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="43" spans="1:30" ht="15.75" customHeight="1">
       <c r="A43" s="30">
         <v>46287</v>
       </c>
@@ -4335,7 +4350,7 @@
       <c r="AC44" s="12"/>
       <c r="AD44" s="12"/>
     </row>
-    <row r="45" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="45" spans="1:30" ht="15.75" customHeight="1">
       <c r="A45" s="30">
         <v>46289</v>
       </c>
@@ -4383,7 +4398,7 @@
       <c r="AC45" s="12"/>
       <c r="AD45" s="12"/>
     </row>
-    <row r="46" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="46" spans="1:30" ht="15.75" customHeight="1">
       <c r="A46" s="30">
         <v>46291</v>
       </c>
@@ -4433,7 +4448,7 @@
       <c r="AC46" s="12"/>
       <c r="AD46" s="12"/>
     </row>
-    <row r="47" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="47" spans="1:30" ht="15.75" customHeight="1">
       <c r="A47" s="30">
         <v>46294</v>
       </c>
@@ -4477,7 +4492,7 @@
       <c r="AC47" s="12"/>
       <c r="AD47" s="12"/>
     </row>
-    <row r="48" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="48" spans="1:30" ht="15.75" customHeight="1">
       <c r="A48" s="30">
         <v>46295</v>
       </c>
@@ -4525,7 +4540,7 @@
       <c r="AC48" s="8"/>
       <c r="AD48" s="8"/>
     </row>
-    <row r="49" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="49" spans="1:30" ht="15.75" customHeight="1">
       <c r="A49" s="40">
         <v>46295</v>
       </c>
@@ -4577,7 +4592,7 @@
       <c r="AC49" s="12"/>
       <c r="AD49" s="12"/>
     </row>
-    <row r="50" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="50" spans="1:30" ht="15.75" customHeight="1">
       <c r="A50" s="30">
         <v>46296</v>
       </c>
@@ -4629,7 +4644,7 @@
       <c r="AC50" s="8"/>
       <c r="AD50" s="8"/>
     </row>
-    <row r="51" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="51" spans="1:30" ht="15.75" customHeight="1">
       <c r="A51" s="30">
         <v>46297</v>
       </c>
@@ -4679,7 +4694,7 @@
       <c r="AC51" s="12"/>
       <c r="AD51" s="12"/>
     </row>
-    <row r="52" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="52" spans="1:30" ht="15.75" customHeight="1">
       <c r="A52" s="30">
         <v>46297</v>
       </c>
@@ -4727,7 +4742,7 @@
       <c r="AC52" s="12"/>
       <c r="AD52" s="12"/>
     </row>
-    <row r="53" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="53" spans="1:30" ht="15.75" customHeight="1">
       <c r="A53" s="30">
         <v>46298</v>
       </c>
@@ -4777,7 +4792,7 @@
       <c r="AC53" s="12"/>
       <c r="AD53" s="12"/>
     </row>
-    <row r="54" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="54" spans="1:30" ht="15.75" customHeight="1">
       <c r="A54" s="30">
         <v>46298</v>
       </c>
@@ -4819,7 +4834,7 @@
       <c r="AC54" s="12"/>
       <c r="AD54" s="12"/>
     </row>
-    <row r="55" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="55" spans="1:30" ht="15.75" customHeight="1">
       <c r="A55" s="30">
         <v>46302</v>
       </c>
@@ -4871,7 +4886,7 @@
       <c r="AC55" s="12"/>
       <c r="AD55" s="12"/>
     </row>
-    <row r="56" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="56" spans="1:30" ht="15.75" customHeight="1">
       <c r="A56" s="30">
         <v>46302</v>
       </c>
@@ -4921,7 +4936,7 @@
       <c r="AC56" s="12"/>
       <c r="AD56" s="12"/>
     </row>
-    <row r="57" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="57" spans="1:30" ht="15.75" customHeight="1">
       <c r="A57" s="30">
         <v>46303</v>
       </c>
@@ -4971,7 +4986,7 @@
       <c r="AC57" s="12"/>
       <c r="AD57" s="12"/>
     </row>
-    <row r="58" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="58" spans="1:30" ht="15.75" customHeight="1">
       <c r="A58" s="30">
         <v>46303</v>
       </c>
@@ -5021,7 +5036,7 @@
       <c r="AC58" s="12"/>
       <c r="AD58" s="12"/>
     </row>
-    <row r="59" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="59" spans="1:30" ht="15.75" customHeight="1">
       <c r="A59" s="30">
         <v>46304</v>
       </c>
@@ -5071,7 +5086,7 @@
       <c r="AC59" s="12"/>
       <c r="AD59" s="12"/>
     </row>
-    <row r="60" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="60" spans="1:30" ht="15.75" customHeight="1">
       <c r="A60" s="30">
         <v>46304</v>
       </c>
@@ -5121,7 +5136,7 @@
       <c r="AC60" s="12"/>
       <c r="AD60" s="12"/>
     </row>
-    <row r="61" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="61" spans="1:30" ht="15.75" customHeight="1">
       <c r="A61" s="30">
         <v>46304</v>
       </c>
@@ -5165,7 +5180,7 @@
       <c r="AC61" s="12"/>
       <c r="AD61" s="12"/>
     </row>
-    <row r="62" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="62" spans="1:30" ht="15.75" customHeight="1">
       <c r="A62" s="30">
         <v>46305</v>
       </c>
@@ -5269,7 +5284,7 @@
       <c r="AC63" s="12"/>
       <c r="AD63" s="12"/>
     </row>
-    <row r="64" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="64" spans="1:30" ht="15.75" customHeight="1">
       <c r="A64" s="30">
         <v>46309</v>
       </c>
@@ -5321,7 +5336,7 @@
       <c r="AC64" s="12"/>
       <c r="AD64" s="12"/>
     </row>
-    <row r="65" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="65" spans="1:30" ht="15.75" customHeight="1">
       <c r="A65" s="30">
         <v>46310</v>
       </c>
@@ -5371,7 +5386,7 @@
       <c r="AC65" s="12"/>
       <c r="AD65" s="12"/>
     </row>
-    <row r="66" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="66" spans="1:30" ht="15.75" customHeight="1">
       <c r="A66" s="30">
         <v>46310</v>
       </c>
@@ -5421,7 +5436,7 @@
       <c r="AC66" s="12"/>
       <c r="AD66" s="12"/>
     </row>
-    <row r="67" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="67" spans="1:30" ht="15.75" customHeight="1">
       <c r="A67" s="30">
         <v>46310</v>
       </c>
@@ -5473,7 +5488,7 @@
       <c r="AC67" s="12"/>
       <c r="AD67" s="12"/>
     </row>
-    <row r="68" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="68" spans="1:30" ht="15.75" customHeight="1">
       <c r="A68" s="40">
         <v>46310</v>
       </c>
@@ -5525,7 +5540,7 @@
       <c r="AC68" s="12"/>
       <c r="AD68" s="12"/>
     </row>
-    <row r="69" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="69" spans="1:30" ht="15.75" customHeight="1">
       <c r="A69" s="30">
         <v>46311</v>
       </c>
@@ -5575,7 +5590,7 @@
       <c r="AC69" s="12"/>
       <c r="AD69" s="12"/>
     </row>
-    <row r="70" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="70" spans="1:30" ht="15.75" customHeight="1">
       <c r="A70" s="30">
         <v>46311</v>
       </c>
@@ -5625,7 +5640,7 @@
       <c r="AC70" s="12"/>
       <c r="AD70" s="12"/>
     </row>
-    <row r="71" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="71" spans="1:30" ht="15.75" customHeight="1">
       <c r="A71" s="30">
         <v>46312</v>
       </c>
@@ -5675,7 +5690,7 @@
       <c r="AC71" s="12"/>
       <c r="AD71" s="12"/>
     </row>
-    <row r="72" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="72" spans="1:30" ht="15.75" customHeight="1">
       <c r="A72" s="30">
         <v>46316</v>
       </c>
@@ -5777,7 +5792,7 @@
       <c r="AC73" s="12"/>
       <c r="AD73" s="12"/>
     </row>
-    <row r="74" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="74" spans="1:30" ht="15.75" customHeight="1">
       <c r="A74" s="30">
         <v>46316</v>
       </c>
@@ -5825,7 +5840,7 @@
       <c r="AC74" s="12"/>
       <c r="AD74" s="12"/>
     </row>
-    <row r="75" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="75" spans="1:30" ht="15.75" customHeight="1">
       <c r="A75" s="30">
         <v>46317</v>
       </c>
@@ -5873,7 +5888,7 @@
       <c r="AC75" s="12"/>
       <c r="AD75" s="12"/>
     </row>
-    <row r="76" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="76" spans="1:30" ht="15.75" customHeight="1">
       <c r="A76" s="30">
         <v>46318</v>
       </c>
@@ -5915,7 +5930,7 @@
       <c r="AC76" s="12"/>
       <c r="AD76" s="12"/>
     </row>
-    <row r="77" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="77" spans="1:30" ht="15.75" customHeight="1">
       <c r="A77" s="30">
         <v>46318</v>
       </c>
@@ -5963,7 +5978,7 @@
       <c r="AC77" s="12"/>
       <c r="AD77" s="12"/>
     </row>
-    <row r="78" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="78" spans="1:30" ht="15.75" customHeight="1">
       <c r="A78" s="30">
         <v>46319</v>
       </c>
@@ -6061,7 +6076,7 @@
       <c r="AC79" s="12"/>
       <c r="AD79" s="12"/>
     </row>
-    <row r="80" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="80" spans="1:30" ht="15.75" customHeight="1">
       <c r="A80" s="30">
         <v>46324</v>
       </c>
@@ -6109,7 +6124,7 @@
       <c r="AC80" s="12"/>
       <c r="AD80" s="12"/>
     </row>
-    <row r="81" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="81" spans="1:30" ht="15.75" customHeight="1">
       <c r="A81" s="30">
         <v>46324</v>
       </c>
@@ -6157,7 +6172,7 @@
       <c r="AC81" s="12"/>
       <c r="AD81" s="12"/>
     </row>
-    <row r="82" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="82" spans="1:30" ht="15.75" customHeight="1">
       <c r="A82" s="30">
         <v>46325</v>
       </c>
@@ -6197,7 +6212,7 @@
       <c r="AC82" s="12"/>
       <c r="AD82" s="12"/>
     </row>
-    <row r="83" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="83" spans="1:30" ht="15.75" customHeight="1">
       <c r="A83" s="30">
         <v>46325</v>
       </c>
@@ -6241,7 +6256,7 @@
       <c r="AC83" s="12"/>
       <c r="AD83" s="12"/>
     </row>
-    <row r="84" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="84" spans="1:30" ht="15.75" customHeight="1">
       <c r="A84" s="30">
         <v>46326</v>
       </c>
@@ -6285,7 +6300,7 @@
       <c r="AC84" s="12"/>
       <c r="AD84" s="12"/>
     </row>
-    <row r="85" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="85" spans="1:30" ht="15.75" customHeight="1">
       <c r="A85" s="30">
         <v>46326</v>
       </c>
@@ -6337,7 +6352,7 @@
       <c r="AC85" s="12"/>
       <c r="AD85" s="12"/>
     </row>
-    <row r="86" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="86" spans="1:30" ht="15.75" customHeight="1">
       <c r="A86" s="30">
         <v>46327</v>
       </c>
@@ -6379,7 +6394,7 @@
       <c r="AC86" s="12"/>
       <c r="AD86" s="12"/>
     </row>
-    <row r="87" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="87" spans="1:30" ht="15.75" customHeight="1">
       <c r="A87" s="30">
         <v>46330</v>
       </c>
@@ -6431,7 +6446,7 @@
       <c r="AC87" s="12"/>
       <c r="AD87" s="12"/>
     </row>
-    <row r="88" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="88" spans="1:30" ht="15.75" customHeight="1">
       <c r="A88" s="30">
         <v>46330</v>
       </c>
@@ -6475,7 +6490,7 @@
       <c r="AC88" s="12"/>
       <c r="AD88" s="12"/>
     </row>
-    <row r="89" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="89" spans="1:30" ht="15.75" customHeight="1">
       <c r="A89" s="30">
         <v>46330</v>
       </c>
@@ -6525,7 +6540,7 @@
       <c r="AC89" s="12"/>
       <c r="AD89" s="12"/>
     </row>
-    <row r="90" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="90" spans="1:30" ht="15.75" customHeight="1">
       <c r="A90" s="40">
         <v>46331</v>
       </c>
@@ -6577,7 +6592,7 @@
       <c r="AC90" s="12"/>
       <c r="AD90" s="12"/>
     </row>
-    <row r="91" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="91" spans="1:30" ht="15.75" customHeight="1">
       <c r="A91" s="30">
         <v>46333</v>
       </c>
@@ -6629,7 +6644,7 @@
       <c r="AC91" s="12"/>
       <c r="AD91" s="12"/>
     </row>
-    <row r="92" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="92" spans="1:30" ht="15.75" customHeight="1">
       <c r="A92" s="30">
         <v>46333</v>
       </c>
@@ -6677,7 +6692,7 @@
       <c r="AC92" s="12"/>
       <c r="AD92" s="12"/>
     </row>
-    <row r="93" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="93" spans="1:30" ht="15.75" customHeight="1">
       <c r="A93" s="30">
         <v>46338</v>
       </c>
@@ -6729,7 +6744,7 @@
       <c r="AC93" s="12"/>
       <c r="AD93" s="12"/>
     </row>
-    <row r="94" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="94" spans="1:30" ht="15.75" customHeight="1">
       <c r="A94" s="30">
         <v>46339</v>
       </c>
@@ -6777,7 +6792,7 @@
       <c r="AC94" s="12"/>
       <c r="AD94" s="12"/>
     </row>
-    <row r="95" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="95" spans="1:30" ht="15.75" customHeight="1">
       <c r="A95" s="30">
         <v>46340</v>
       </c>
@@ -6879,7 +6894,7 @@
       <c r="AC96" s="12"/>
       <c r="AD96" s="12"/>
     </row>
-    <row r="97" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="97" spans="1:30" ht="15.75" customHeight="1">
       <c r="A97" s="30">
         <v>46344</v>
       </c>
@@ -6929,7 +6944,7 @@
       <c r="AC97" s="12"/>
       <c r="AD97" s="12"/>
     </row>
-    <row r="98" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="98" spans="1:30" ht="15.75" customHeight="1">
       <c r="A98" s="30">
         <v>46345</v>
       </c>
@@ -6979,7 +6994,7 @@
       <c r="AC98" s="12"/>
       <c r="AD98" s="12"/>
     </row>
-    <row r="99" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="99" spans="1:30" ht="15.75" customHeight="1">
       <c r="A99" s="30">
         <v>46356</v>
       </c>
@@ -7023,7 +7038,7 @@
       <c r="AC99" s="12"/>
       <c r="AD99" s="12"/>
     </row>
-    <row r="100" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="100" spans="1:30" ht="15.75" customHeight="1">
       <c r="A100" s="30">
         <v>46357</v>
       </c>
@@ -7071,7 +7086,7 @@
       <c r="AC100" s="12"/>
       <c r="AD100" s="12"/>
     </row>
-    <row r="101" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="101" spans="1:30" ht="15.75" customHeight="1">
       <c r="A101" s="30">
         <v>46358</v>
       </c>
@@ -7123,7 +7138,7 @@
       <c r="AC101" s="12"/>
       <c r="AD101" s="12"/>
     </row>
-    <row r="102" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="102" spans="1:30" ht="15.75" customHeight="1">
       <c r="A102" s="30">
         <v>46360</v>
       </c>
@@ -7223,7 +7238,7 @@
       <c r="AC103" s="12"/>
       <c r="AD103" s="12"/>
     </row>
-    <row r="104" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="104" spans="1:30" ht="15.75" customHeight="1">
       <c r="A104" s="30">
         <v>46365</v>
       </c>
@@ -7275,7 +7290,7 @@
       <c r="AC104" s="12"/>
       <c r="AD104" s="12"/>
     </row>
-    <row r="105" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="105" spans="1:30" ht="15.75" customHeight="1">
       <c r="A105" s="30">
         <v>46365</v>
       </c>
@@ -7325,7 +7340,7 @@
       <c r="AC105" s="12"/>
       <c r="AD105" s="12"/>
     </row>
-    <row r="106" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="106" spans="1:30" ht="15.75" customHeight="1">
       <c r="A106" s="30">
         <v>46366</v>
       </c>
@@ -7369,7 +7384,7 @@
       <c r="AC106" s="12"/>
       <c r="AD106" s="12"/>
     </row>
-    <row r="107" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="107" spans="1:30" ht="15.75" customHeight="1">
       <c r="A107" s="30">
         <v>46367</v>
       </c>
@@ -7413,7 +7428,7 @@
       <c r="AC107" s="12"/>
       <c r="AD107" s="12"/>
     </row>
-    <row r="108" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="108" spans="1:30" ht="15.75" customHeight="1">
       <c r="A108" s="30">
         <v>46368</v>
       </c>
@@ -7515,7 +7530,7 @@
       <c r="AC109" s="12"/>
       <c r="AD109" s="12"/>
     </row>
-    <row r="110" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="110" spans="1:30" ht="15.75" customHeight="1">
       <c r="A110" s="30">
         <v>46372</v>
       </c>
@@ -7567,7 +7582,7 @@
       <c r="AC110" s="12"/>
       <c r="AD110" s="12"/>
     </row>
-    <row r="111" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="111" spans="1:30" ht="15.75" customHeight="1">
       <c r="A111" s="40">
         <v>46373</v>
       </c>
@@ -7619,7 +7634,7 @@
       <c r="AC111" s="12"/>
       <c r="AD111" s="12"/>
     </row>
-    <row r="112" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="112" spans="1:30" ht="15.75" customHeight="1">
       <c r="A112" s="30">
         <v>46400</v>
       </c>
@@ -7671,7 +7686,7 @@
       <c r="AC112" s="12"/>
       <c r="AD112" s="12"/>
     </row>
-    <row r="113" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="113" spans="1:30" ht="15.75" customHeight="1">
       <c r="A113" s="30">
         <v>46400</v>
       </c>
@@ -7721,7 +7736,7 @@
       <c r="AC113" s="12"/>
       <c r="AD113" s="12"/>
     </row>
-    <row r="114" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="114" spans="1:30" ht="15.75" customHeight="1">
       <c r="A114" s="40">
         <v>46401</v>
       </c>
@@ -7773,7 +7788,7 @@
       <c r="AC114" s="12"/>
       <c r="AD114" s="12"/>
     </row>
-    <row r="115" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="115" spans="1:30" ht="15.75" customHeight="1">
       <c r="A115" s="30">
         <v>46402</v>
       </c>
@@ -7873,7 +7888,7 @@
       <c r="AC116" s="12"/>
       <c r="AD116" s="12"/>
     </row>
-    <row r="117" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="117" spans="1:30" ht="15.75" customHeight="1">
       <c r="A117" s="30">
         <v>46407</v>
       </c>
@@ -7925,7 +7940,7 @@
       <c r="AC117" s="12"/>
       <c r="AD117" s="12"/>
     </row>
-    <row r="118" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="118" spans="1:30" ht="15.75" customHeight="1">
       <c r="A118" s="30">
         <v>46410</v>
       </c>
@@ -7975,7 +7990,7 @@
       <c r="AC118" s="12"/>
       <c r="AD118" s="12"/>
     </row>
-    <row r="119" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="119" spans="1:30" ht="15.75" customHeight="1">
       <c r="A119" s="30">
         <v>46410</v>
       </c>
@@ -8023,7 +8038,7 @@
       <c r="AC119" s="12"/>
       <c r="AD119" s="12"/>
     </row>
-    <row r="120" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="120" spans="1:30" ht="15.75" customHeight="1">
       <c r="A120" s="30">
         <v>46411</v>
       </c>
@@ -8065,7 +8080,7 @@
       <c r="AC120" s="12"/>
       <c r="AD120" s="12"/>
     </row>
-    <row r="121" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="121" spans="1:30" ht="15.75" customHeight="1">
       <c r="A121" s="30">
         <v>46411</v>
       </c>
@@ -8163,7 +8178,7 @@
       <c r="AC122" s="12"/>
       <c r="AD122" s="12"/>
     </row>
-    <row r="123" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="123" spans="1:30" ht="15.75" customHeight="1">
       <c r="A123" s="30">
         <v>46415</v>
       </c>
@@ -8211,7 +8226,7 @@
       <c r="AC123" s="12"/>
       <c r="AD123" s="12"/>
     </row>
-    <row r="124" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="124" spans="1:30" ht="15.75" customHeight="1">
       <c r="A124" s="30">
         <v>46416</v>
       </c>
@@ -8255,7 +8270,7 @@
       <c r="AC124" s="12"/>
       <c r="AD124" s="12"/>
     </row>
-    <row r="125" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="125" spans="1:30" ht="15.75" customHeight="1">
       <c r="A125" s="30">
         <v>46417</v>
       </c>
@@ -8299,7 +8314,7 @@
       <c r="AC125" s="12"/>
       <c r="AD125" s="12"/>
     </row>
-    <row r="126" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="126" spans="1:30" ht="15.75" customHeight="1">
       <c r="A126" s="30">
         <v>46418</v>
       </c>
@@ -8339,7 +8354,7 @@
       <c r="AC126" s="12"/>
       <c r="AD126" s="12"/>
     </row>
-    <row r="127" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="127" spans="1:30" ht="15.75" customHeight="1">
       <c r="A127" s="30">
         <v>46420</v>
       </c>
@@ -8387,7 +8402,7 @@
       <c r="AC127" s="12"/>
       <c r="AD127" s="12"/>
     </row>
-    <row r="128" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="128" spans="1:30" ht="15.75" customHeight="1">
       <c r="A128" s="30">
         <v>46421</v>
       </c>
@@ -8439,7 +8454,7 @@
       <c r="AC128" s="12"/>
       <c r="AD128" s="12"/>
     </row>
-    <row r="129" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="129" spans="1:30" ht="15.75" customHeight="1">
       <c r="A129" s="30">
         <v>46421</v>
       </c>
@@ -8489,7 +8504,7 @@
       <c r="AC129" s="12"/>
       <c r="AD129" s="12"/>
     </row>
-    <row r="130" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="130" spans="1:30" ht="15.75" customHeight="1">
       <c r="A130" s="40">
         <v>46422</v>
       </c>
@@ -8541,7 +8556,7 @@
       <c r="AC130" s="12"/>
       <c r="AD130" s="12"/>
     </row>
-    <row r="131" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="131" spans="1:30" ht="15.75" customHeight="1">
       <c r="A131" s="30">
         <v>46423</v>
       </c>
@@ -8589,7 +8604,7 @@
       <c r="AC131" s="12"/>
       <c r="AD131" s="12"/>
     </row>
-    <row r="132" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="132" spans="1:30" ht="15.75" customHeight="1">
       <c r="A132" s="30">
         <v>46423</v>
       </c>
@@ -8693,7 +8708,7 @@
       <c r="AC133" s="12"/>
       <c r="AD133" s="12"/>
     </row>
-    <row r="134" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="134" spans="1:30" ht="15.75" customHeight="1">
       <c r="A134" s="30">
         <v>46428</v>
       </c>
@@ -8745,7 +8760,7 @@
       <c r="AC134" s="12"/>
       <c r="AD134" s="12"/>
     </row>
-    <row r="135" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="135" spans="1:30" ht="15.75" customHeight="1">
       <c r="A135" s="30">
         <v>46428</v>
       </c>
@@ -8797,7 +8812,7 @@
       <c r="AC135" s="12"/>
       <c r="AD135" s="12"/>
     </row>
-    <row r="136" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="136" spans="1:30" ht="15.75" customHeight="1">
       <c r="A136" s="30">
         <v>46430</v>
       </c>
@@ -8866,7 +8881,7 @@
         <v>35</v>
       </c>
       <c r="J137" s="33" t="s">
-        <v>48</v>
+        <v>171</v>
       </c>
       <c r="K137" s="33" t="s">
         <v>23</v>
@@ -8893,7 +8908,7 @@
       <c r="AC137" s="12"/>
       <c r="AD137" s="12"/>
     </row>
-    <row r="138" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="138" spans="1:30" ht="15.75" customHeight="1">
       <c r="A138" s="30">
         <v>46438</v>
       </c>
@@ -8968,7 +8983,7 @@
         <v>35</v>
       </c>
       <c r="J139" s="33" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="K139" s="33" t="s">
         <v>23</v>
@@ -8995,7 +9010,7 @@
       <c r="AC139" s="12"/>
       <c r="AD139" s="12"/>
     </row>
-    <row r="140" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="140" spans="1:30" ht="15.75" customHeight="1">
       <c r="A140" s="30">
         <v>46443</v>
       </c>
@@ -9043,7 +9058,7 @@
       <c r="AC140" s="12"/>
       <c r="AD140" s="12"/>
     </row>
-    <row r="141" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="141" spans="1:30" ht="15.75" customHeight="1">
       <c r="A141" s="30">
         <v>46444</v>
       </c>
@@ -9055,7 +9070,7 @@
       </c>
       <c r="F141" s="34"/>
       <c r="G141" s="33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H141" s="34"/>
       <c r="I141" s="34"/>
@@ -9083,7 +9098,7 @@
       <c r="AC141" s="12"/>
       <c r="AD141" s="12"/>
     </row>
-    <row r="142" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="142" spans="1:30" ht="15.75" customHeight="1">
       <c r="A142" s="30">
         <v>46445</v>
       </c>
@@ -9095,7 +9110,7 @@
       </c>
       <c r="F142" s="34"/>
       <c r="G142" s="33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H142" s="33" t="s">
         <v>25</v>
@@ -9127,7 +9142,7 @@
       <c r="AC142" s="12"/>
       <c r="AD142" s="12"/>
     </row>
-    <row r="143" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="143" spans="1:30" ht="15.75" customHeight="1">
       <c r="A143" s="30">
         <v>46447</v>
       </c>
@@ -9139,7 +9154,7 @@
       </c>
       <c r="F143" s="34"/>
       <c r="G143" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H143" s="34" t="s">
         <v>25</v>
@@ -9171,7 +9186,7 @@
       <c r="AC143" s="12"/>
       <c r="AD143" s="12"/>
     </row>
-    <row r="144" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="144" spans="1:30" ht="15.75" customHeight="1">
       <c r="A144" s="30">
         <v>46447</v>
       </c>
@@ -9183,7 +9198,7 @@
       </c>
       <c r="F144" s="34"/>
       <c r="G144" s="33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H144" s="34" t="s">
         <v>20</v>
@@ -9215,7 +9230,7 @@
       <c r="AC144" s="12"/>
       <c r="AD144" s="12"/>
     </row>
-    <row r="145" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="145" spans="1:30" ht="15.75" customHeight="1">
       <c r="A145" s="30">
         <v>46447</v>
       </c>
@@ -9227,7 +9242,7 @@
       </c>
       <c r="F145" s="34"/>
       <c r="G145" s="33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H145" s="34"/>
       <c r="I145" s="33" t="s">
@@ -9257,7 +9272,7 @@
       <c r="AC145" s="12"/>
       <c r="AD145" s="12"/>
     </row>
-    <row r="146" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="146" spans="1:30" ht="15.75" customHeight="1">
       <c r="A146" s="30">
         <v>46448</v>
       </c>
@@ -9305,7 +9320,7 @@
       <c r="AC146" s="12"/>
       <c r="AD146" s="12"/>
     </row>
-    <row r="147" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="147" spans="1:30" ht="15.75" customHeight="1">
       <c r="A147" s="30">
         <v>46449</v>
       </c>
@@ -9357,7 +9372,7 @@
       <c r="AC147" s="12"/>
       <c r="AD147" s="12"/>
     </row>
-    <row r="148" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="148" spans="1:30" ht="15.75" customHeight="1">
       <c r="A148" s="30">
         <v>46450</v>
       </c>
@@ -9405,7 +9420,7 @@
       <c r="AC148" s="12"/>
       <c r="AD148" s="12"/>
     </row>
-    <row r="149" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="149" spans="1:30" ht="15.75" customHeight="1">
       <c r="A149" s="30">
         <v>46450</v>
       </c>
@@ -9417,7 +9432,7 @@
       </c>
       <c r="F149" s="34"/>
       <c r="G149" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H149" s="34" t="s">
         <v>25</v>
@@ -9449,7 +9464,7 @@
       <c r="AC149" s="12"/>
       <c r="AD149" s="12"/>
     </row>
-    <row r="150" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="150" spans="1:30" ht="15.75" customHeight="1">
       <c r="A150" s="30">
         <v>46450</v>
       </c>
@@ -9461,7 +9476,7 @@
       </c>
       <c r="F150" s="34"/>
       <c r="G150" s="33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H150" s="34" t="s">
         <v>25</v>
@@ -9471,7 +9486,7 @@
       </c>
       <c r="J150" s="34"/>
       <c r="K150" s="33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L150" s="34"/>
       <c r="M150" s="34" t="s">
@@ -9495,7 +9510,7 @@
       <c r="AC150" s="12"/>
       <c r="AD150" s="12"/>
     </row>
-    <row r="151" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="151" spans="1:30" ht="15.75" customHeight="1">
       <c r="A151" s="40">
         <v>46450</v>
       </c>
@@ -9547,7 +9562,7 @@
       <c r="AC151" s="12"/>
       <c r="AD151" s="12"/>
     </row>
-    <row r="152" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="152" spans="1:30" ht="15.75" customHeight="1">
       <c r="A152" s="30">
         <v>46452</v>
       </c>
@@ -9563,7 +9578,7 @@
       </c>
       <c r="F152" s="34"/>
       <c r="G152" s="33" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H152" s="34" t="s">
         <v>89</v>
@@ -9595,7 +9610,7 @@
       <c r="AC152" s="12"/>
       <c r="AD152" s="12"/>
     </row>
-    <row r="153" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="153" spans="1:30" ht="15.75" customHeight="1">
       <c r="A153" s="30">
         <v>46454</v>
       </c>
@@ -9607,7 +9622,7 @@
       </c>
       <c r="F153" s="34"/>
       <c r="G153" s="33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H153" s="34" t="s">
         <v>20</v>
@@ -9639,7 +9654,7 @@
       <c r="AC153" s="24"/>
       <c r="AD153" s="24"/>
     </row>
-    <row r="154" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="154" spans="1:30" ht="15.75" customHeight="1">
       <c r="A154" s="30">
         <v>46456</v>
       </c>
@@ -9667,7 +9682,7 @@
         <v>17</v>
       </c>
       <c r="K154" s="34" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L154" s="34"/>
       <c r="M154" s="34" t="s">
@@ -9716,7 +9731,7 @@
         <v>35</v>
       </c>
       <c r="J155" s="33" t="s">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="K155" s="33" t="s">
         <v>23</v>
@@ -9743,7 +9758,7 @@
       <c r="AC155" s="12"/>
       <c r="AD155" s="12"/>
     </row>
-    <row r="156" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="156" spans="1:30" ht="15.75" customHeight="1">
       <c r="A156" s="30">
         <v>46457</v>
       </c>
@@ -9755,7 +9770,7 @@
       </c>
       <c r="F156" s="34"/>
       <c r="G156" s="33" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H156" s="34" t="s">
         <v>46</v>
@@ -9787,7 +9802,7 @@
       <c r="AC156" s="12"/>
       <c r="AD156" s="12"/>
     </row>
-    <row r="157" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="157" spans="1:30" ht="15.75" customHeight="1">
       <c r="A157" s="30">
         <v>46458</v>
       </c>
@@ -9837,7 +9852,7 @@
       <c r="AC157" s="12"/>
       <c r="AD157" s="12"/>
     </row>
-    <row r="158" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="158" spans="1:30" ht="15.75" customHeight="1">
       <c r="A158" s="30">
         <v>46458</v>
       </c>
@@ -9889,7 +9904,7 @@
       <c r="AC158" s="12"/>
       <c r="AD158" s="12"/>
     </row>
-    <row r="159" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="159" spans="1:30" ht="15.75" customHeight="1">
       <c r="A159" s="30">
         <v>46459</v>
       </c>
@@ -9939,7 +9954,7 @@
       <c r="AC159" s="12"/>
       <c r="AD159" s="12"/>
     </row>
-    <row r="160" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="160" spans="1:30" ht="15.75" customHeight="1">
       <c r="A160" s="30">
         <v>46460</v>
       </c>
@@ -9953,7 +9968,7 @@
       </c>
       <c r="F160" s="34"/>
       <c r="G160" s="33" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H160" s="34" t="s">
         <v>15</v>
@@ -10037,7 +10052,7 @@
       <c r="AC161" s="12"/>
       <c r="AD161" s="12"/>
     </row>
-    <row r="162" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="162" spans="1:30" ht="15.75" customHeight="1">
       <c r="A162" s="30">
         <v>46463</v>
       </c>
@@ -10053,7 +10068,7 @@
       </c>
       <c r="F162" s="34"/>
       <c r="G162" s="33" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H162" s="33" t="s">
         <v>46</v>
@@ -10065,7 +10080,7 @@
         <v>48</v>
       </c>
       <c r="K162" s="33" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="L162" s="34"/>
       <c r="M162" s="34" t="s">
@@ -10089,7 +10104,7 @@
       <c r="AC162" s="12"/>
       <c r="AD162" s="12"/>
     </row>
-    <row r="163" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="163" spans="1:30" ht="15.75" customHeight="1">
       <c r="A163" s="30">
         <v>46464</v>
       </c>
@@ -10137,7 +10152,7 @@
       <c r="AC163" s="12"/>
       <c r="AD163" s="12"/>
     </row>
-    <row r="164" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="164" spans="1:30" ht="15.75" customHeight="1">
       <c r="A164" s="30">
         <v>46464</v>
       </c>
@@ -10153,7 +10168,7 @@
       </c>
       <c r="F164" s="34"/>
       <c r="G164" s="33" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H164" s="34"/>
       <c r="I164" s="34" t="s">
@@ -10185,7 +10200,7 @@
       <c r="AC164" s="12"/>
       <c r="AD164" s="12"/>
     </row>
-    <row r="165" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="165" spans="1:30" ht="15.75" customHeight="1">
       <c r="A165" s="30">
         <v>46468</v>
       </c>
@@ -10199,7 +10214,7 @@
       </c>
       <c r="F165" s="34"/>
       <c r="G165" s="33" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H165" s="34"/>
       <c r="I165" s="34"/>
@@ -10227,12 +10242,12 @@
       <c r="AC165" s="12"/>
       <c r="AD165" s="12"/>
     </row>
-    <row r="166" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="166" spans="1:30" ht="15.75" customHeight="1">
       <c r="A166" s="30">
         <v>46475</v>
       </c>
       <c r="B166" s="36" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C166" s="32">
         <v>0.60416666666666663</v>
@@ -10277,7 +10292,7 @@
       <c r="AC166" s="12"/>
       <c r="AD166" s="12"/>
     </row>
-    <row r="167" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="167" spans="1:30" ht="15.75" customHeight="1">
       <c r="A167" s="30">
         <v>46479</v>
       </c>
@@ -10325,7 +10340,7 @@
       <c r="AC167" s="12"/>
       <c r="AD167" s="12"/>
     </row>
-    <row r="168" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="168" spans="1:30" ht="15.75" customHeight="1">
       <c r="A168" s="30">
         <v>46484</v>
       </c>
@@ -10377,7 +10392,7 @@
       <c r="AC168" s="12"/>
       <c r="AD168" s="12"/>
     </row>
-    <row r="169" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="169" spans="1:30" ht="15.75" customHeight="1">
       <c r="A169" s="30">
         <v>46484</v>
       </c>
@@ -10399,13 +10414,13 @@
         <v>58</v>
       </c>
       <c r="I169" s="34" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J169" s="34" t="s">
         <v>17</v>
       </c>
       <c r="K169" s="34" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="L169" s="34"/>
       <c r="M169" s="34" t="s">
@@ -10429,7 +10444,7 @@
       <c r="AC169" s="12"/>
       <c r="AD169" s="12"/>
     </row>
-    <row r="170" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="170" spans="1:30" ht="15.75" customHeight="1">
       <c r="A170" s="30">
         <v>46484</v>
       </c>
@@ -10477,7 +10492,7 @@
       <c r="AC170" s="12"/>
       <c r="AD170" s="12"/>
     </row>
-    <row r="171" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="171" spans="1:30" ht="15.75" customHeight="1">
       <c r="A171" s="30">
         <v>46485</v>
       </c>
@@ -10489,7 +10504,7 @@
       </c>
       <c r="F171" s="34"/>
       <c r="G171" s="33" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="H171" s="34" t="s">
         <v>46</v>
@@ -10548,7 +10563,7 @@
         <v>35</v>
       </c>
       <c r="J172" s="33" t="s">
-        <v>48</v>
+        <v>195</v>
       </c>
       <c r="K172" s="33" t="s">
         <v>23</v>
@@ -10575,7 +10590,7 @@
       <c r="AC172" s="12"/>
       <c r="AD172" s="12"/>
     </row>
-    <row r="173" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="173" spans="1:30" ht="15.75" customHeight="1">
       <c r="A173" s="40">
         <v>46492</v>
       </c>
@@ -10627,7 +10642,7 @@
       <c r="AC173" s="12"/>
       <c r="AD173" s="12"/>
     </row>
-    <row r="174" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="174" spans="1:30" ht="15.75" customHeight="1">
       <c r="A174" s="30">
         <v>46493</v>
       </c>
@@ -10639,7 +10654,7 @@
       </c>
       <c r="F174" s="34"/>
       <c r="G174" s="33" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H174" s="34"/>
       <c r="I174" s="34"/>
@@ -10667,7 +10682,7 @@
       <c r="AC174" s="12"/>
       <c r="AD174" s="12"/>
     </row>
-    <row r="175" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="175" spans="1:30" ht="15.75" customHeight="1">
       <c r="A175" s="30">
         <v>46493</v>
       </c>
@@ -10679,7 +10694,7 @@
       </c>
       <c r="F175" s="34"/>
       <c r="G175" s="33" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="H175" s="34"/>
       <c r="I175" s="33" t="s">
@@ -10687,7 +10702,7 @@
       </c>
       <c r="J175" s="34"/>
       <c r="K175" s="33" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="L175" s="34"/>
       <c r="M175" s="34" t="s">
@@ -10711,7 +10726,7 @@
       <c r="AC175" s="12"/>
       <c r="AD175" s="12"/>
     </row>
-    <row r="176" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="176" spans="1:30" ht="15.75" customHeight="1">
       <c r="A176" s="30">
         <v>46494</v>
       </c>
@@ -10786,7 +10801,7 @@
         <v>35</v>
       </c>
       <c r="J177" s="33" t="s">
-        <v>48</v>
+        <v>199</v>
       </c>
       <c r="K177" s="33" t="s">
         <v>23</v>
@@ -10813,7 +10828,7 @@
       <c r="AC177" s="12"/>
       <c r="AD177" s="12"/>
     </row>
-    <row r="178" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="178" spans="1:30" ht="15.75" customHeight="1">
       <c r="A178" s="30">
         <v>46499</v>
       </c>
@@ -10825,7 +10840,7 @@
       </c>
       <c r="F178" s="34"/>
       <c r="G178" s="33" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H178" s="34"/>
       <c r="I178" s="34" t="s">
@@ -10855,7 +10870,7 @@
       <c r="AC178" s="12"/>
       <c r="AD178" s="12"/>
     </row>
-    <row r="179" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="179" spans="1:30" ht="15.75" customHeight="1">
       <c r="A179" s="30">
         <v>46499</v>
       </c>
@@ -10886,7 +10901,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="180" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="180" spans="1:30" ht="15.75" customHeight="1">
       <c r="A180" s="30">
         <v>46499</v>
       </c>
@@ -10898,7 +10913,7 @@
       </c>
       <c r="F180" s="34"/>
       <c r="G180" s="33" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H180" s="33" t="s">
         <v>46</v>
@@ -10913,7 +10928,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="181" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="181" spans="1:30" ht="15.75" customHeight="1">
       <c r="A181" s="30">
         <v>46500</v>
       </c>
@@ -10944,7 +10959,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="182" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="182" spans="1:30" ht="15.75" customHeight="1">
       <c r="A182" s="30">
         <v>46501</v>
       </c>
@@ -10956,7 +10971,7 @@
       </c>
       <c r="F182" s="34"/>
       <c r="G182" s="33" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="H182" s="33" t="s">
         <v>25</v>
@@ -10971,7 +10986,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="183" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="183" spans="1:30" ht="15.75" customHeight="1">
       <c r="A183" s="30">
         <v>46501</v>
       </c>
@@ -10987,7 +11002,7 @@
       </c>
       <c r="F183" s="34"/>
       <c r="G183" s="33" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="H183" s="34" t="s">
         <v>89</v>
@@ -11037,7 +11052,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="185" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="185" spans="1:30" ht="15.75" customHeight="1">
       <c r="A185" s="30">
         <v>46507</v>
       </c>
@@ -11049,7 +11064,7 @@
       </c>
       <c r="F185" s="34"/>
       <c r="G185" s="33" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="H185" s="34"/>
       <c r="I185" s="34"/>
@@ -11060,7 +11075,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="186" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="186" spans="1:30" ht="15.75" customHeight="1">
       <c r="A186" s="30">
         <v>46507</v>
       </c>
@@ -11072,7 +11087,7 @@
       </c>
       <c r="F186" s="34"/>
       <c r="G186" s="33" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="H186" s="33" t="s">
         <v>25</v>
@@ -11087,7 +11102,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="187" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="187" spans="1:30" ht="15.75" customHeight="1">
       <c r="A187" s="30">
         <v>46511</v>
       </c>
@@ -11118,7 +11133,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="188" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="188" spans="1:30" ht="15.75" customHeight="1">
       <c r="A188" s="30">
         <v>46512</v>
       </c>
@@ -11153,7 +11168,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="189" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="189" spans="1:30" ht="15.75" customHeight="1">
       <c r="A189" s="40">
         <v>46513</v>
       </c>
@@ -11223,7 +11238,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="191" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="191" spans="1:30" ht="15.75" customHeight="1">
       <c r="A191" s="30">
         <v>46519</v>
       </c>
@@ -11245,20 +11260,20 @@
         <v>58</v>
       </c>
       <c r="I191" s="34" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="J191" s="34" t="s">
         <v>17</v>
       </c>
       <c r="K191" s="34" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="L191" s="34"/>
       <c r="M191" s="34" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="192" spans="1:30" ht="15.75" hidden="1" customHeight="1">
+    <row r="192" spans="1:30" ht="15.75" customHeight="1">
       <c r="A192" s="30">
         <v>46519</v>
       </c>
@@ -11291,7 +11306,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="193" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="193" spans="1:13" ht="15.75" customHeight="1">
       <c r="A193" s="30">
         <v>46521</v>
       </c>
@@ -11322,7 +11337,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="194" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="194" spans="1:13" ht="15.75" customHeight="1">
       <c r="A194" s="30">
         <v>46522</v>
       </c>
@@ -11390,7 +11405,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="196" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="196" spans="1:13" ht="15.75" customHeight="1">
       <c r="A196" s="30">
         <v>46526</v>
       </c>
@@ -11402,7 +11417,7 @@
       </c>
       <c r="F196" s="34"/>
       <c r="G196" s="33" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="H196" s="34" t="s">
         <v>25</v>
@@ -11452,7 +11467,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="198" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="198" spans="1:13" ht="15.75" customHeight="1">
       <c r="A198" s="30">
         <v>46534</v>
       </c>
@@ -11477,7 +11492,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="199" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="199" spans="1:13" ht="15.75" customHeight="1">
       <c r="A199" s="30">
         <v>46535</v>
       </c>
@@ -11489,7 +11504,7 @@
       </c>
       <c r="F199" s="34"/>
       <c r="G199" s="33" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="H199" s="34"/>
       <c r="I199" s="34"/>
@@ -11500,7 +11515,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="200" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="200" spans="1:13" ht="15.75" customHeight="1">
       <c r="A200" s="30">
         <v>46539</v>
       </c>
@@ -11531,7 +11546,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="201" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="201" spans="1:13" ht="15.75" customHeight="1">
       <c r="A201" s="30">
         <v>46540</v>
       </c>
@@ -11566,7 +11581,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="202" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="202" spans="1:13" ht="15.75" customHeight="1">
       <c r="A202" s="30">
         <v>46540</v>
       </c>
@@ -11599,7 +11614,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="203" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="203" spans="1:13" ht="15.75" customHeight="1">
       <c r="A203" s="30">
         <v>46542</v>
       </c>
@@ -11630,7 +11645,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="204" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="204" spans="1:13" ht="15.75" customHeight="1">
       <c r="A204" s="30">
         <v>46542</v>
       </c>
@@ -11646,7 +11661,7 @@
       </c>
       <c r="F204" s="34"/>
       <c r="G204" s="33" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="H204" s="34" t="s">
         <v>58</v>
@@ -11658,14 +11673,14 @@
         <v>153</v>
       </c>
       <c r="K204" s="34" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L204" s="34"/>
       <c r="M204" s="34" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="205" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="205" spans="1:13" ht="15.75" customHeight="1">
       <c r="A205" s="48">
         <v>46543</v>
       </c>
@@ -11698,7 +11713,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="206" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="206" spans="1:13" ht="15.75" customHeight="1">
       <c r="A206" s="52">
         <v>46545</v>
       </c>
@@ -11733,7 +11748,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="207" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="207" spans="1:13" ht="15.75" customHeight="1">
       <c r="A207" s="48">
         <v>46549</v>
       </c>
@@ -11760,12 +11775,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="208" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="208" spans="1:13" ht="15.75" customHeight="1">
       <c r="A208" s="48">
         <v>46552</v>
       </c>
       <c r="B208" s="55" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C208" s="50">
         <v>0.35416666666666669</v>
@@ -11778,7 +11793,7 @@
       </c>
       <c r="F208" s="51"/>
       <c r="G208" s="37" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="H208" s="34" t="s">
         <v>46</v>
@@ -11793,7 +11808,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="209" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="209" spans="1:13" ht="15.75" customHeight="1">
       <c r="A209" s="48">
         <v>46554</v>
       </c>
@@ -11821,14 +11836,14 @@
         <v>17</v>
       </c>
       <c r="K209" s="51" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="L209" s="51"/>
       <c r="M209" s="34" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="210" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="210" spans="1:13" ht="15.75" customHeight="1">
       <c r="A210" s="48">
         <v>46563</v>
       </c>
@@ -11859,7 +11874,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="211" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="211" spans="1:13" ht="15.75" customHeight="1">
       <c r="A211" s="48">
         <v>46568</v>
       </c>
@@ -11871,7 +11886,7 @@
       </c>
       <c r="F211" s="51"/>
       <c r="G211" s="37" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="H211" s="34"/>
       <c r="I211" s="34" t="s">
@@ -11884,7 +11899,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="212" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="212" spans="1:13" ht="15.75" customHeight="1">
       <c r="A212" s="48">
         <v>46592</v>
       </c>
@@ -11896,7 +11911,7 @@
       </c>
       <c r="F212" s="51"/>
       <c r="G212" s="37" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="H212" s="33" t="s">
         <v>25</v>
@@ -11911,7 +11926,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="213" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="213" spans="1:13" ht="15.75" customHeight="1">
       <c r="A213" s="48">
         <v>46597</v>
       </c>
@@ -11923,7 +11938,7 @@
       </c>
       <c r="F213" s="51"/>
       <c r="G213" s="37" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="H213" s="33" t="s">
         <v>25</v>
@@ -11938,7 +11953,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="214" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="214" spans="1:13" ht="15.75" customHeight="1">
       <c r="A214" s="48">
         <v>46623</v>
       </c>
@@ -11950,7 +11965,7 @@
       </c>
       <c r="F214" s="51"/>
       <c r="G214" s="37" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="H214" s="34"/>
       <c r="I214" s="34"/>
@@ -11961,7 +11976,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="215" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="215" spans="1:13" ht="15.75" customHeight="1">
       <c r="A215" s="48">
         <v>46630</v>
       </c>
@@ -11973,7 +11988,7 @@
       </c>
       <c r="F215" s="51"/>
       <c r="G215" s="37" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="H215" s="34"/>
       <c r="I215" s="34"/>
@@ -16696,12 +16711,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:M215" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="Coach/Advisor Collaboration ▶️ 🐦"/>
-        <filter val="LL Team Meeting — School Site ▶️"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M215">
       <sortCondition ref="A1:A215"/>
     </sortState>
@@ -16779,21 +16788,21 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C2" s="16">
         <v>46203</v>
@@ -16801,16 +16810,16 @@
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
       <c r="A3" s="18" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C3" s="20">
         <v>46199</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="E3" s="18"/>
       <c r="F3" s="18"/>
@@ -16837,24 +16846,24 @@
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
       <c r="A4" s="18" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C4" s="20">
         <v>46199</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>224</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>219</v>
       </c>
       <c r="C5" s="21">
         <v>46266</v>
@@ -16862,10 +16871,10 @@
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C6" s="16">
         <v>46356</v>
@@ -16873,34 +16882,34 @@
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
       <c r="A8" s="19" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
       <c r="A9" s="19" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C10" s="21">
         <v>46120</v>
@@ -16908,20 +16917,20 @@
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1">
       <c r="A11" s="19" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="15" customHeight="1">
       <c r="A13" s="7" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -16965,7 +16974,7 @@
         <v>4</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>6</v>
@@ -17001,16 +17010,16 @@
     </row>
     <row r="2" spans="1:26">
       <c r="A2" s="10" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>46</v>
@@ -17021,16 +17030,16 @@
         <v>46456</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:26">
@@ -17038,16 +17047,16 @@
         <v>46499</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -17113,15 +17122,15 @@
         <v>10</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1">
       <c r="A2" s="11" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="15" t="s">
@@ -17138,7 +17147,7 @@
         <v>21</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="I2" s="19" t="s">
         <v>23</v>
@@ -17148,17 +17157,17 @@
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>28</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="19" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F3" s="15" t="s">
         <v>108</v>
@@ -17188,7 +17197,7 @@
         <v>21</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I4" s="19" t="s">
         <v>23</v>
@@ -17198,7 +17207,7 @@
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1">
       <c r="A5" s="11" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>39</v>
@@ -17252,7 +17261,7 @@
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1">
       <c r="A7" s="11" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="19" t="s">
@@ -17260,7 +17269,7 @@
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="19" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F7" s="19" t="s">
         <v>58</v>
@@ -17274,7 +17283,7 @@
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1">
       <c r="A8" s="11" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="15" t="s">
@@ -17301,7 +17310,7 @@
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
       <c r="A9" s="11" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="15" t="s">
@@ -17315,7 +17324,7 @@
         <v>58</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="H9" s="15"/>
       <c r="I9" s="15"/>
@@ -17324,7 +17333,7 @@
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="15" t="s">
@@ -17351,7 +17360,7 @@
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="15" t="s">
@@ -17378,7 +17387,7 @@
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1">
       <c r="A12" s="11" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="19" t="s">
@@ -17386,7 +17395,7 @@
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="19" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F12" s="19" t="s">
         <v>58</v>
@@ -17401,7 +17410,7 @@
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="15" t="s">
@@ -17428,7 +17437,7 @@
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1">
       <c r="A14" s="11" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="15" t="s">
@@ -17455,7 +17464,7 @@
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="19" t="s">
@@ -17480,7 +17489,7 @@
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="15" t="s">
@@ -17494,7 +17503,7 @@
         <v>58</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="15"/>
@@ -17503,7 +17512,7 @@
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="19" t="s">
@@ -17526,7 +17535,7 @@
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="15" t="s">
@@ -17553,7 +17562,7 @@
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="19" t="s">
@@ -17576,7 +17585,7 @@
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1">
       <c r="A20" s="11" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="15" t="s">
@@ -17603,7 +17612,7 @@
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1">
       <c r="A21" s="11" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="19" t="s">
@@ -17611,7 +17620,7 @@
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="19" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F21" s="15" t="s">
         <v>108</v>
@@ -17626,7 +17635,7 @@
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B22" s="13"/>
       <c r="C22" s="15" t="s">
@@ -17649,7 +17658,7 @@
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="15" t="s">
@@ -17676,7 +17685,7 @@
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="15" t="s">
@@ -17699,7 +17708,7 @@
     </row>
     <row r="25" spans="1:11" ht="15" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B25" s="13"/>
       <c r="C25" s="19" t="s">
@@ -17707,7 +17716,7 @@
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="19" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="F25" s="15" t="s">
         <v>108</v>
@@ -17722,7 +17731,7 @@
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1">
       <c r="A26" s="11" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="15" t="s">
@@ -17749,7 +17758,7 @@
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B27" s="13"/>
       <c r="C27" s="15" t="s">
@@ -17763,7 +17772,7 @@
         <v>58</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="H27" s="15"/>
       <c r="I27" s="15"/>
@@ -17772,7 +17781,7 @@
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="19" t="s">
@@ -17780,7 +17789,7 @@
       </c>
       <c r="D28" s="15"/>
       <c r="E28" s="19" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F28" s="15" t="s">
         <v>108</v>
@@ -17795,7 +17804,7 @@
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B29" s="13"/>
       <c r="C29" s="15" t="s">
@@ -17822,7 +17831,7 @@
     </row>
     <row r="30" spans="1:11" ht="15" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>126</v>
@@ -17832,7 +17841,7 @@
       </c>
       <c r="D30" s="15"/>
       <c r="E30" s="19" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="F30" s="19" t="s">
         <v>89</v>
@@ -17844,14 +17853,14 @@
         <v>128</v>
       </c>
       <c r="I30" s="19" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J30" s="15"/>
       <c r="K30" s="15"/>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B31" s="13"/>
       <c r="C31" s="15" t="s">
@@ -17878,7 +17887,7 @@
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B32" s="13"/>
       <c r="C32" s="19" t="s">
@@ -17901,7 +17910,7 @@
     </row>
     <row r="33" spans="1:11" ht="15" customHeight="1">
       <c r="A33" s="11" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B33" s="13"/>
       <c r="C33" s="19" t="s">
@@ -17924,7 +17933,7 @@
     </row>
     <row r="34" spans="1:11" ht="15" customHeight="1">
       <c r="A34" s="11" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B34" s="13"/>
       <c r="C34" s="19" t="s">
@@ -17932,7 +17941,7 @@
       </c>
       <c r="D34" s="15"/>
       <c r="E34" s="19" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="F34" s="15" t="s">
         <v>108</v>
@@ -17947,7 +17956,7 @@
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1">
       <c r="A35" s="11" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="15" t="s">
@@ -17974,7 +17983,7 @@
     </row>
     <row r="36" spans="1:11" ht="15" customHeight="1">
       <c r="A36" s="11" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B36" s="13"/>
       <c r="C36" s="19" t="s">
@@ -17982,7 +17991,7 @@
       </c>
       <c r="D36" s="15"/>
       <c r="E36" s="19" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F36" s="15" t="s">
         <v>108</v>
@@ -17997,7 +18006,7 @@
     </row>
     <row r="37" spans="1:11" ht="15" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B37" s="13"/>
       <c r="C37" s="19" t="s">
@@ -18020,7 +18029,7 @@
     </row>
     <row r="38" spans="1:11" ht="15" customHeight="1">
       <c r="A38" s="11" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B38" s="13"/>
       <c r="C38" s="15" t="s">
@@ -18034,18 +18043,18 @@
         <v>58</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="H38" s="15"/>
       <c r="I38" s="19" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="J38" s="15"/>
       <c r="K38" s="15"/>
     </row>
     <row r="39" spans="1:11" ht="15" customHeight="1">
       <c r="A39" s="11" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B39" s="13"/>
       <c r="C39" s="15" t="s">
@@ -18072,7 +18081,7 @@
     </row>
     <row r="40" spans="1:11" ht="15" customHeight="1">
       <c r="A40" s="11" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B40" s="13"/>
       <c r="C40" s="15" t="s">
@@ -18080,7 +18089,7 @@
       </c>
       <c r="D40" s="15"/>
       <c r="E40" s="19" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F40" s="15" t="s">
         <v>89</v>
@@ -18095,7 +18104,7 @@
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1">
       <c r="A41" s="11" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B41" s="13"/>
       <c r="C41" s="15" t="s">
@@ -18122,7 +18131,7 @@
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1">
       <c r="A42" s="11" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B42" s="13"/>
       <c r="C42" s="15" t="s">
@@ -18145,7 +18154,7 @@
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1">
       <c r="A43" s="11" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="15" t="s">
@@ -18172,7 +18181,7 @@
     </row>
     <row r="44" spans="1:11" ht="15" customHeight="1">
       <c r="A44" s="11" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B44" s="13"/>
       <c r="C44" s="15" t="s">
@@ -18180,7 +18189,7 @@
       </c>
       <c r="D44" s="15"/>
       <c r="E44" s="19" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F44" s="15" t="s">
         <v>80</v>
@@ -18195,7 +18204,7 @@
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1">
       <c r="A45" s="11" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B45" s="13"/>
       <c r="C45" s="15" t="s">
@@ -18222,7 +18231,7 @@
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1">
       <c r="A46" s="11" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B46" s="13"/>
       <c r="C46" s="15" t="s">
@@ -18236,7 +18245,7 @@
         <v>58</v>
       </c>
       <c r="G46" s="15" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="H46" s="15"/>
       <c r="I46" s="15"/>
@@ -18245,7 +18254,7 @@
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1">
       <c r="A47" s="11" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B47" s="13"/>
       <c r="C47" s="19" t="s">
@@ -18268,7 +18277,7 @@
     </row>
     <row r="48" spans="1:11" ht="15" customHeight="1">
       <c r="A48" s="11" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B48" s="13"/>
       <c r="C48" s="15" t="s">
@@ -18295,7 +18304,7 @@
     </row>
     <row r="49" spans="1:11" ht="15" customHeight="1">
       <c r="A49" s="11" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B49" s="13"/>
       <c r="C49" s="15" t="s">
@@ -18322,7 +18331,7 @@
     </row>
     <row r="50" spans="1:11" ht="15" customHeight="1">
       <c r="A50" s="11" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B50" s="13"/>
       <c r="C50" s="15" t="s">
@@ -18349,7 +18358,7 @@
     </row>
     <row r="51" spans="1:11" ht="15" customHeight="1">
       <c r="A51" s="11" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B51" s="13"/>
       <c r="C51" s="15" t="s">
@@ -18363,7 +18372,7 @@
         <v>58</v>
       </c>
       <c r="G51" s="15" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="H51" s="15"/>
       <c r="I51" s="15"/>
@@ -18372,7 +18381,7 @@
     </row>
     <row r="52" spans="1:11" ht="15" customHeight="1">
       <c r="A52" s="11" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B52" s="13"/>
       <c r="C52" s="19" t="s">
@@ -18395,7 +18404,7 @@
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="11" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B53" s="13"/>
       <c r="C53" s="15" t="s">
@@ -18422,7 +18431,7 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="11" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B54" s="13"/>
       <c r="C54" s="19" t="s">
@@ -18445,7 +18454,7 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="11" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B55" s="13"/>
       <c r="C55" s="15" t="s">
@@ -18468,7 +18477,7 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="11" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B56" s="13"/>
       <c r="C56" s="15" t="s">
@@ -18495,7 +18504,7 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="11" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B57" s="13"/>
       <c r="C57" s="15" t="s">
@@ -18503,7 +18512,7 @@
       </c>
       <c r="D57" s="15"/>
       <c r="E57" s="19" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="F57" s="15" t="s">
         <v>58</v>
@@ -18518,7 +18527,7 @@
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="11" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B58" s="13"/>
       <c r="C58" s="15" t="s">
@@ -18545,7 +18554,7 @@
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="11" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B59" s="13"/>
       <c r="C59" s="15" t="s">
@@ -18559,7 +18568,7 @@
         <v>58</v>
       </c>
       <c r="G59" s="15" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="H59" s="15"/>
       <c r="I59" s="15"/>
@@ -18568,7 +18577,7 @@
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="11" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B60" s="13"/>
       <c r="C60" s="15" t="s">
@@ -18595,7 +18604,7 @@
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="11" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B61" s="13"/>
       <c r="C61" s="15" t="s">
@@ -18622,7 +18631,7 @@
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="11" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B62" s="13"/>
       <c r="C62" s="19" t="s">
@@ -18645,7 +18654,7 @@
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="11" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B63" s="13"/>
       <c r="C63" s="15" t="s">
@@ -18672,7 +18681,7 @@
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="11" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B64" s="13"/>
       <c r="C64" s="15" t="s">
@@ -18695,7 +18704,7 @@
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="11" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B65" s="13"/>
       <c r="C65" s="19" t="s">
@@ -18718,7 +18727,7 @@
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="11" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B66" s="13"/>
       <c r="C66" s="19" t="s">
@@ -18726,7 +18735,7 @@
       </c>
       <c r="D66" s="15"/>
       <c r="E66" s="19" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F66" s="15" t="s">
         <v>89</v>
@@ -18768,7 +18777,7 @@
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="11" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B68" s="13"/>
       <c r="C68" s="15" t="s">
@@ -18782,7 +18791,7 @@
         <v>58</v>
       </c>
       <c r="G68" s="15" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="H68" s="15"/>
       <c r="I68" s="15"/>
@@ -18818,7 +18827,7 @@
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="11" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B70" s="13"/>
       <c r="C70" s="15" t="s">
@@ -18841,10 +18850,10 @@
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="11" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C71" s="15" t="s">
         <v>56</v>
@@ -18866,7 +18875,7 @@
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="11" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B72" s="13"/>
       <c r="C72" s="15" t="s">
@@ -18893,7 +18902,7 @@
     </row>
     <row r="73" spans="1:11">
       <c r="A73" s="11" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B73" s="13"/>
       <c r="C73" s="15" t="s">
@@ -18901,7 +18910,7 @@
       </c>
       <c r="D73" s="15"/>
       <c r="E73" s="19" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F73" s="15" t="s">
         <v>20</v>
@@ -18914,7 +18923,7 @@
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="11" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B74" s="13"/>
       <c r="C74" s="15" t="s">
@@ -18928,7 +18937,7 @@
         <v>58</v>
       </c>
       <c r="G74" s="15" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="H74" s="15"/>
       <c r="I74" s="15"/>
@@ -18937,7 +18946,7 @@
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="11" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B75" s="13"/>
       <c r="C75" s="15" t="s">
@@ -18964,7 +18973,7 @@
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="11" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B76" s="13"/>
       <c r="C76" s="15" t="s">
@@ -18991,7 +19000,7 @@
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="11" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B77" s="13"/>
       <c r="C77" s="19" t="s">
@@ -19014,7 +19023,7 @@
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="11" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B78" s="13"/>
       <c r="C78" s="19" t="s">
@@ -19022,7 +19031,7 @@
       </c>
       <c r="D78" s="15"/>
       <c r="E78" s="19" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F78" s="15" t="s">
         <v>89</v>
@@ -19037,7 +19046,7 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="11" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B79" s="13"/>
       <c r="C79" s="15" t="s">
@@ -19064,7 +19073,7 @@
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="11" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B80" s="13"/>
       <c r="C80" s="15" t="s">
@@ -19091,7 +19100,7 @@
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="11" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B81" s="13"/>
       <c r="C81" s="15" t="s">
@@ -19114,7 +19123,7 @@
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="22" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B82" s="23"/>
       <c r="C82" s="15" t="s">
@@ -19141,7 +19150,7 @@
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="22" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B83" s="23"/>
       <c r="C83" s="15" t="s">
@@ -19155,7 +19164,7 @@
         <v>58</v>
       </c>
       <c r="G83" s="15" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="H83" s="15"/>
       <c r="I83" s="15"/>
@@ -19164,7 +19173,7 @@
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="22" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B84" s="23"/>
       <c r="C84" s="15" t="s">
@@ -19191,7 +19200,7 @@
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="22" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B85" s="23"/>
       <c r="C85" s="15" t="s">
@@ -19218,7 +19227,7 @@
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="22" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B86" s="23"/>
       <c r="C86" s="15" t="s">
@@ -19245,7 +19254,7 @@
     </row>
     <row r="87" spans="1:11">
       <c r="A87" s="22" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B87" s="23"/>
       <c r="C87" s="15" t="s">
@@ -19268,7 +19277,7 @@
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="22" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B88" s="23"/>
       <c r="C88" s="15" t="s">
@@ -19282,7 +19291,7 @@
         <v>58</v>
       </c>
       <c r="G88" s="15" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="H88" s="15"/>
       <c r="I88" s="15"/>

--- a/26-27_Admin_Calendar_Events_CTE-LL_Version.xlsx
+++ b/26-27_Admin_Calendar_Events_CTE-LL_Version.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lausd.sharepoint.com/teams/CTE-LLLeadership/Shared Documents/Calendaring/CTELL_Calendar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="111" documentId="8_{AFEB7EE0-A3A0-BE46-B68A-F48D580478B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{620FA9F9-7316-4513-BFA0-926929FBA686}"/>
+  <xr:revisionPtr revIDLastSave="127" documentId="8_{AFEB7EE0-A3A0-BE46-B68A-F48D580478B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{282661BD-A045-4CC6-8898-A2D82E73BCAF}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
     <author>tc={07f742e6-da81-4690-924b-edd49951831d}</author>
     <author>tc={80e866d6-bfaf-4296-9eae-a24011716c28}</author>
     <author>tc={572f9da1-db36-4ac3-a4e5-e9c38653e985}</author>
-    <author>tc={dca28f16-b9ac-4996-a6ef-40aa311ba7aa}</author>
+    <author>tc={19DDB89B-3A12-4552-B614-77B383CFE27B}</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0" xr:uid="{E7906286-BBDE-433D-B420-E6B087CD316B}">
@@ -342,7 +342,7 @@
 Assigned to rekha.prakash@lausd.net</t>
       </text>
     </comment>
-    <comment ref="J162" authorId="8" shapeId="0" xr:uid="{DCA28F16-B9AC-4996-A6EF-40AA311BA7AA}">
+    <comment ref="J177" authorId="8" shapeId="0" xr:uid="{19DDB89B-3A12-4552-B614-77B383CFE27B}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -956,43 +956,43 @@
     <t>Educating for Careers Conference</t>
   </si>
   <si>
+    <t>CTE-Linked Learning Showcase &amp; Advisory Mtg 🏫</t>
+  </si>
+  <si>
+    <t>Spring Recess</t>
+  </si>
+  <si>
+    <t>Tuesday, 3/30/27</t>
+  </si>
+  <si>
+    <t>FRANK, JUSTIN</t>
+  </si>
+  <si>
+    <t>Justin</t>
+  </si>
+  <si>
+    <t>4th Annual ABOTA @ LA Superior Court</t>
+  </si>
+  <si>
+    <t>Roosevelt HS</t>
+  </si>
+  <si>
+    <t>Final Procurement Purchases 💰</t>
+  </si>
+  <si>
+    <t>ELAC CTE Day</t>
+  </si>
+  <si>
+    <t>CTE student field trip to ELAC. date needs to be confirmed</t>
+  </si>
+  <si>
+    <t>MCLC</t>
+  </si>
+  <si>
     <t>Pathway Connect HSMT PatCare 🐦</t>
   </si>
   <si>
     <t>HSMT Patient Care teachers only</t>
-  </si>
-  <si>
-    <t>CTE-Linked Learning Showcase &amp; Advisory Mtg 🏫</t>
-  </si>
-  <si>
-    <t>Spring Recess</t>
-  </si>
-  <si>
-    <t>Tuesday, 3/30/27</t>
-  </si>
-  <si>
-    <t>FRANK, JUSTIN</t>
-  </si>
-  <si>
-    <t>Justin</t>
-  </si>
-  <si>
-    <t>4th Annual ABOTA @ LA Superior Court</t>
-  </si>
-  <si>
-    <t>Roosevelt HS</t>
-  </si>
-  <si>
-    <t>Final Procurement Purchases 💰</t>
-  </si>
-  <si>
-    <t>ELAC CTE Day</t>
-  </si>
-  <si>
-    <t>CTE student field trip to ELAC. date needs to be confirmed</t>
-  </si>
-  <si>
-    <t>MCLC</t>
   </si>
   <si>
     <t>Perkins Q3 Budget Revision 💰</t>
@@ -1736,22 +1736,22 @@
 
 <file path=xl/documenttasks/documenttask1.xml><?xml version="1.0" encoding="utf-8"?>
 <Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks">
-  <Task id="{83E88D0C-66B8-489C-8DAF-1F90D21C911A}">
+  <Task id="{10A84903-9D47-45EE-B3BE-3F7F1C0F086F}">
     <Anchor>
-      <Comment id="{DCA28F16-B9AC-4996-A6EF-40AA311BA7AA}"/>
+      <Comment id="{19DDB89B-3A12-4552-B614-77B383CFE27B}"/>
     </Anchor>
     <History>
       <Event time="2026-08-24T19:19:35.0" id="{9CDAE529-52F2-49B2-8CF4-8235EE7170A0}">
         <Attribution userId="placeholder@email.com" userName="NANCY LE" userProvider="google-sheets"/>
         <Anchor>
-          <Comment id="{DCA28F16-B9AC-4996-A6EF-40AA311BA7AA}"/>
+          <Comment id="{19DDB89B-3A12-4552-B614-77B383CFE27B}"/>
         </Anchor>
         <Create/>
       </Event>
       <Event time="2026-08-24T19:19:35.0" id="{7A386294-E5D7-4A79-B98E-BAE604E3DD97}">
         <Attribution userId="placeholder@email.com" userName="NANCY LE" userProvider="google-sheets"/>
         <Anchor>
-          <Comment id="{DCA28F16-B9AC-4996-A6EF-40AA311BA7AA}"/>
+          <Comment id="{19DDB89B-3A12-4552-B614-77B383CFE27B}"/>
         </Anchor>
         <Assign userId="rekha.prakash@lausd.net" userName="rekha.prakash@lausd.net" userProvider="google-sheets"/>
       </Event>
@@ -2171,11 +2171,11 @@
       <mention mentionpersonId="{D5E65F0F-B0E9-CF42-A55F-18641707047D}" mentionId="{F6AF3A79-49FE-4E10-9DEB-F6F24CB735C6}" startIndex="23" length="24"/>
     </mentions>
   </threadedComment>
-  <threadedComment ref="J162" dT="2026-08-24T19:19:35.00" personId="{EA5698C8-7C4A-4A39-873A-050A87D08922}" id="{DCA28F16-B9AC-4996-A6EF-40AA311BA7AA}">
+  <threadedComment ref="J177" dT="2026-08-24T19:19:35.00" personId="{EA5698C8-7C4A-4A39-873A-050A87D08922}" id="{19DDB89B-3A12-4552-B614-77B383CFE27B}">
     <text>Please update if known @rekha.prakash@lausd.net
 Assigned to rekha.prakash@lausd.net</text>
     <mentions>
-      <mention mentionpersonId="{D5E65F0F-B0E9-CF42-A55F-18641707047D}" mentionId="{1DE1824C-3BA7-4108-9EE9-AB3BDA4F671F}" startIndex="23" length="24"/>
+      <mention mentionpersonId="{D5E65F0F-B0E9-CF42-A55F-18641707047D}" mentionId="{D72AFB46-9823-42DB-AE66-E21FF7D7598B}" startIndex="23" length="24"/>
     </mentions>
   </threadedComment>
 </ThreadedComments>
@@ -10054,7 +10054,7 @@
     </row>
     <row r="162" spans="1:30" ht="15.75" customHeight="1">
       <c r="A162" s="30">
-        <v>46463</v>
+        <v>46464</v>
       </c>
       <c r="B162" s="31"/>
       <c r="C162" s="35">
@@ -10063,25 +10063,21 @@
       <c r="D162" s="35">
         <v>0.64583333333333337</v>
       </c>
-      <c r="E162" s="33" t="s">
+      <c r="E162" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F162" s="34"/>
       <c r="G162" s="33" t="s">
-        <v>187</v>
-      </c>
-      <c r="H162" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="I162" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J162" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="K162" s="33" t="s">
-        <v>188</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="H162" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="I162" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="J162" s="34"/>
+      <c r="K162" s="34"/>
       <c r="L162" s="34"/>
       <c r="M162" s="34" t="s">
         <v>32</v>
@@ -10109,28 +10105,28 @@
         <v>46464</v>
       </c>
       <c r="B163" s="31"/>
-      <c r="C163" s="35">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D163" s="35">
-        <v>0.64583333333333337</v>
+      <c r="C163" s="32">
+        <v>0.375</v>
+      </c>
+      <c r="D163" s="32">
+        <v>0.625</v>
       </c>
       <c r="E163" s="34" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="F163" s="34"/>
       <c r="G163" s="33" t="s">
-        <v>102</v>
-      </c>
-      <c r="H163" s="34" t="s">
-        <v>41</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="H163" s="34"/>
       <c r="I163" s="34" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="J163" s="34"/>
-      <c r="K163" s="34"/>
-      <c r="L163" s="34"/>
+      <c r="K163" s="33"/>
+      <c r="L163" s="34" t="s">
+        <v>32</v>
+      </c>
       <c r="M163" s="34" t="s">
         <v>32</v>
       </c>
@@ -10154,31 +10150,25 @@
     </row>
     <row r="164" spans="1:30" ht="15.75" customHeight="1">
       <c r="A164" s="30">
-        <v>46464</v>
-      </c>
-      <c r="B164" s="31"/>
-      <c r="C164" s="32">
-        <v>0.375</v>
-      </c>
-      <c r="D164" s="32">
-        <v>0.625</v>
-      </c>
+        <v>46468</v>
+      </c>
+      <c r="B164" s="31">
+        <v>46472</v>
+      </c>
+      <c r="C164" s="32"/>
+      <c r="D164" s="32"/>
       <c r="E164" s="34" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F164" s="34"/>
       <c r="G164" s="33" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H164" s="34"/>
-      <c r="I164" s="34" t="s">
-        <v>51</v>
-      </c>
+      <c r="I164" s="34"/>
       <c r="J164" s="34"/>
       <c r="K164" s="33"/>
-      <c r="L164" s="34" t="s">
-        <v>32</v>
-      </c>
+      <c r="L164" s="34"/>
       <c r="M164" s="34" t="s">
         <v>32</v>
       </c>
@@ -10202,24 +10192,32 @@
     </row>
     <row r="165" spans="1:30" ht="15.75" customHeight="1">
       <c r="A165" s="30">
-        <v>46468</v>
-      </c>
-      <c r="B165" s="31">
-        <v>46472</v>
-      </c>
-      <c r="C165" s="32"/>
-      <c r="D165" s="32"/>
+        <v>46475</v>
+      </c>
+      <c r="B165" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="C165" s="32">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D165" s="32">
+        <v>0.6875</v>
+      </c>
       <c r="E165" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F165" s="34"/>
       <c r="G165" s="33" t="s">
-        <v>190</v>
-      </c>
-      <c r="H165" s="34"/>
-      <c r="I165" s="34"/>
+        <v>145</v>
+      </c>
+      <c r="H165" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="I165" s="34" t="s">
+        <v>97</v>
+      </c>
       <c r="J165" s="34"/>
-      <c r="K165" s="33"/>
+      <c r="K165" s="34"/>
       <c r="L165" s="34"/>
       <c r="M165" s="34" t="s">
         <v>32</v>
@@ -10244,35 +10242,33 @@
     </row>
     <row r="166" spans="1:30" ht="15.75" customHeight="1">
       <c r="A166" s="30">
-        <v>46475</v>
-      </c>
-      <c r="B166" s="36" t="s">
-        <v>191</v>
-      </c>
+        <v>46479</v>
+      </c>
+      <c r="B166" s="31"/>
       <c r="C166" s="32">
-        <v>0.60416666666666663</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D166" s="32">
-        <v>0.6875</v>
+        <v>0.4375</v>
       </c>
       <c r="E166" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F166" s="34"/>
       <c r="G166" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="H166" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="I166" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="J166" s="34"/>
-      <c r="K166" s="34"/>
+        <v>49</v>
+      </c>
+      <c r="H166" s="34"/>
+      <c r="I166" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="J166" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K166" s="33"/>
       <c r="L166" s="34"/>
       <c r="M166" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N166" s="12"/>
       <c r="O166" s="12"/>
@@ -10294,30 +10290,34 @@
     </row>
     <row r="167" spans="1:30" ht="15.75" customHeight="1">
       <c r="A167" s="30">
-        <v>46479</v>
+        <v>46484</v>
       </c>
       <c r="B167" s="31"/>
       <c r="C167" s="32">
         <v>0.35416666666666669</v>
       </c>
       <c r="D167" s="32">
-        <v>0.4375</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="E167" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F167" s="34"/>
       <c r="G167" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="H167" s="34"/>
+        <v>19</v>
+      </c>
+      <c r="H167" s="33" t="s">
+        <v>20</v>
+      </c>
       <c r="I167" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="J167" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K167" s="33"/>
+        <v>21</v>
+      </c>
+      <c r="J167" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="K167" s="33" t="s">
+        <v>23</v>
+      </c>
       <c r="L167" s="34"/>
       <c r="M167" s="34" t="s">
         <v>18</v>
@@ -10346,29 +10346,29 @@
       </c>
       <c r="B168" s="31"/>
       <c r="C168" s="32">
-        <v>0.35416666666666669</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D168" s="32">
-        <v>0.52083333333333337</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="E168" s="34" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="F168" s="34"/>
       <c r="G168" s="33" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="H168" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="I168" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="J168" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="K168" s="33" t="s">
-        <v>23</v>
+        <v>58</v>
+      </c>
+      <c r="I168" s="34" t="s">
+        <v>190</v>
+      </c>
+      <c r="J168" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K168" s="34" t="s">
+        <v>191</v>
       </c>
       <c r="L168" s="34"/>
       <c r="M168" s="34" t="s">
@@ -10396,36 +10396,32 @@
       <c r="A169" s="30">
         <v>46484</v>
       </c>
-      <c r="B169" s="31"/>
+      <c r="B169" s="47"/>
       <c r="C169" s="32">
-        <v>0.52083333333333337</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D169" s="32">
-        <v>0.54166666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="E169" s="34" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F169" s="34"/>
       <c r="G169" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="H169" s="33" t="s">
-        <v>58</v>
+        <v>14</v>
+      </c>
+      <c r="H169" s="34" t="s">
+        <v>15</v>
       </c>
       <c r="I169" s="34" t="s">
-        <v>192</v>
+        <v>16</v>
       </c>
       <c r="J169" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K169" s="34" t="s">
-        <v>193</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="K169" s="34"/>
       <c r="L169" s="34"/>
-      <c r="M169" s="34" t="s">
-        <v>18</v>
-      </c>
+      <c r="M169" s="34"/>
       <c r="N169" s="12"/>
       <c r="O169" s="12"/>
       <c r="P169" s="12"/>
@@ -10446,34 +10442,32 @@
     </row>
     <row r="170" spans="1:30" ht="15.75" customHeight="1">
       <c r="A170" s="30">
-        <v>46484</v>
-      </c>
-      <c r="B170" s="47"/>
-      <c r="C170" s="32">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D170" s="32">
-        <v>0.5</v>
-      </c>
-      <c r="E170" s="34" t="s">
-        <v>13</v>
+        <v>46485</v>
+      </c>
+      <c r="B170" s="31"/>
+      <c r="C170" s="35"/>
+      <c r="D170" s="35"/>
+      <c r="E170" s="33" t="s">
+        <v>56</v>
       </c>
       <c r="F170" s="34"/>
       <c r="G170" s="33" t="s">
-        <v>14</v>
+        <v>192</v>
       </c>
       <c r="H170" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="I170" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="J170" s="34" t="s">
-        <v>147</v>
-      </c>
-      <c r="K170" s="34"/>
+        <v>46</v>
+      </c>
+      <c r="I170" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="J170" s="34"/>
+      <c r="K170" s="33" t="s">
+        <v>130</v>
+      </c>
       <c r="L170" s="34"/>
-      <c r="M170" s="34"/>
+      <c r="M170" s="34" t="s">
+        <v>32</v>
+      </c>
       <c r="N170" s="12"/>
       <c r="O170" s="12"/>
       <c r="P170" s="12"/>
@@ -10494,31 +10488,37 @@
     </row>
     <row r="171" spans="1:30" ht="15.75" customHeight="1">
       <c r="A171" s="30">
-        <v>46485</v>
+        <v>46491</v>
       </c>
       <c r="B171" s="31"/>
-      <c r="C171" s="35"/>
-      <c r="D171" s="35"/>
-      <c r="E171" s="33" t="s">
-        <v>56</v>
+      <c r="C171" s="32">
+        <v>0.34375</v>
+      </c>
+      <c r="D171" s="32">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E171" s="34" t="s">
+        <v>13</v>
       </c>
       <c r="F171" s="34"/>
       <c r="G171" s="33" t="s">
-        <v>194</v>
-      </c>
-      <c r="H171" s="34" t="s">
-        <v>46</v>
+        <v>53</v>
+      </c>
+      <c r="H171" s="33" t="s">
+        <v>54</v>
       </c>
       <c r="I171" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="J171" s="34"/>
+        <v>35</v>
+      </c>
+      <c r="J171" s="33" t="s">
+        <v>193</v>
+      </c>
       <c r="K171" s="33" t="s">
-        <v>130</v>
+        <v>23</v>
       </c>
       <c r="L171" s="34"/>
       <c r="M171" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N171" s="12"/>
       <c r="O171" s="12"/>
@@ -10539,36 +10539,36 @@
       <c r="AD171" s="12"/>
     </row>
     <row r="172" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A172" s="30">
-        <v>46491</v>
-      </c>
-      <c r="B172" s="31"/>
-      <c r="C172" s="32">
-        <v>0.34375</v>
-      </c>
-      <c r="D172" s="32">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="E172" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="F172" s="34"/>
-      <c r="G172" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="H172" s="33" t="s">
-        <v>54</v>
+      <c r="A172" s="40">
+        <v>46492</v>
+      </c>
+      <c r="B172" s="41"/>
+      <c r="C172" s="42">
+        <v>0.625</v>
+      </c>
+      <c r="D172" s="42">
+        <v>0.6875</v>
+      </c>
+      <c r="E172" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F172" s="41"/>
+      <c r="G172" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="H172" s="34" t="s">
+        <v>50</v>
       </c>
       <c r="I172" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="J172" s="33" t="s">
-        <v>195</v>
-      </c>
-      <c r="K172" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="L172" s="34"/>
+      <c r="J172" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="K172" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="L172" s="43"/>
       <c r="M172" s="34" t="s">
         <v>18</v>
       </c>
@@ -10591,36 +10591,24 @@
       <c r="AD172" s="12"/>
     </row>
     <row r="173" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A173" s="40">
-        <v>46492</v>
-      </c>
-      <c r="B173" s="41"/>
-      <c r="C173" s="42">
-        <v>0.625</v>
-      </c>
-      <c r="D173" s="42">
-        <v>0.6875</v>
-      </c>
-      <c r="E173" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="F173" s="41"/>
-      <c r="G173" s="41" t="s">
-        <v>75</v>
-      </c>
-      <c r="H173" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="I173" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="J173" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="K173" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="L173" s="43"/>
+      <c r="A173" s="30">
+        <v>46493</v>
+      </c>
+      <c r="B173" s="31"/>
+      <c r="C173" s="32"/>
+      <c r="D173" s="32"/>
+      <c r="E173" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="F173" s="34"/>
+      <c r="G173" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="H173" s="34"/>
+      <c r="I173" s="34"/>
+      <c r="J173" s="34"/>
+      <c r="K173" s="34"/>
+      <c r="L173" s="34"/>
       <c r="M173" s="34" t="s">
         <v>18</v>
       </c>
@@ -10654,15 +10642,19 @@
       </c>
       <c r="F174" s="34"/>
       <c r="G174" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="H174" s="34"/>
+      <c r="I174" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="J174" s="34"/>
+      <c r="K174" s="33" t="s">
         <v>196</v>
       </c>
-      <c r="H174" s="34"/>
-      <c r="I174" s="34"/>
-      <c r="J174" s="34"/>
-      <c r="K174" s="34"/>
       <c r="L174" s="34"/>
       <c r="M174" s="34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N174" s="12"/>
       <c r="O174" s="12"/>
@@ -10684,26 +10676,32 @@
     </row>
     <row r="175" spans="1:30" ht="15.75" customHeight="1">
       <c r="A175" s="30">
-        <v>46493</v>
+        <v>46494</v>
       </c>
       <c r="B175" s="31"/>
-      <c r="C175" s="32"/>
-      <c r="D175" s="32"/>
-      <c r="E175" s="34" t="s">
-        <v>56</v>
+      <c r="C175" s="35">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D175" s="35">
+        <v>0.5</v>
+      </c>
+      <c r="E175" s="33" t="s">
+        <v>13</v>
       </c>
       <c r="F175" s="34"/>
       <c r="G175" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="H175" s="34"/>
+        <v>65</v>
+      </c>
+      <c r="H175" s="33" t="s">
+        <v>46</v>
+      </c>
       <c r="I175" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="J175" s="34"/>
-      <c r="K175" s="33" t="s">
-        <v>198</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="J175" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="K175" s="34"/>
       <c r="L175" s="34"/>
       <c r="M175" s="34" t="s">
         <v>32</v>
@@ -10728,35 +10726,37 @@
     </row>
     <row r="176" spans="1:30" ht="15.75" customHeight="1">
       <c r="A176" s="30">
-        <v>46494</v>
+        <v>46498</v>
       </c>
       <c r="B176" s="31"/>
-      <c r="C176" s="35">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D176" s="35">
-        <v>0.5</v>
-      </c>
-      <c r="E176" s="33" t="s">
+      <c r="C176" s="32">
+        <v>0.34375</v>
+      </c>
+      <c r="D176" s="32">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E176" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F176" s="34"/>
       <c r="G176" s="33" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="H176" s="33" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I176" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J176" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="K176" s="34"/>
+        <v>35</v>
+      </c>
+      <c r="J176" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="K176" s="33" t="s">
+        <v>23</v>
+      </c>
       <c r="L176" s="34"/>
       <c r="M176" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N176" s="12"/>
       <c r="O176" s="12"/>
@@ -10781,30 +10781,30 @@
         <v>46498</v>
       </c>
       <c r="B177" s="31"/>
-      <c r="C177" s="32">
-        <v>0.34375</v>
-      </c>
-      <c r="D177" s="32">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="E177" s="34" t="s">
+      <c r="C177" s="35">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D177" s="35">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="E177" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F177" s="34"/>
       <c r="G177" s="33" t="s">
-        <v>53</v>
+        <v>198</v>
       </c>
       <c r="H177" s="33" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I177" s="33" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="J177" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="K177" s="33" t="s">
         <v>199</v>
-      </c>
-      <c r="K177" s="33" t="s">
-        <v>23</v>
       </c>
       <c r="L177" s="34"/>
       <c r="M177" s="34" t="s">
@@ -16721,7 +16721,7 @@
   <customSheetViews>
     <customSheetView guid="{8F656852-D603-4744-997A-DE0F92A7585E}" filter="1" showAutoFilter="1">
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-      <autoFilter ref="A1:M198" xr:uid="{0A9EEFBD-86C1-45FF-AD2A-54B605172D14}">
+      <autoFilter ref="A1:M198" xr:uid="{3AA3E11F-63A0-4736-95FE-EED3347D6423}">
         <filterColumn colId="6">
           <filters>
             <filter val="GSPP Action Planning Implementation Pathways Region E Day 1  🌁"/>
@@ -16737,7 +16737,7 @@
     </customSheetView>
   </customSheetViews>
   <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" sqref="I2:I37 I182:I215 I162:I180 I39:I160" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I37 I182:I215 I39:I160 I162:I180" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"BARRENECHEA, ED,DABAGYAN, ESTHER,ELIAS, MICHELLE,GERTNER, BEN,KASAMANYAN, HOVIK,LE, NANCY,PRICE, TOMOKO,PRAKASH, REKHA,SERRANO, NANCY"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M205:M215 L2:M204" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -18853,7 +18853,7 @@
         <v>321</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C71" s="15" t="s">
         <v>56</v>
@@ -19328,17 +19328,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f51bf047-e00d-4111-9acd-3b648a8df45c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb5933e1-39c5-43d4-bb0e-9e063605db7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FC47CB1A92F76B4FA38F66E0A126B066" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c0dc230b441f24b1df5c0a570d224bc1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb5933e1-39c5-43d4-bb0e-9e063605db7e" xmlns:ns3="f51bf047-e00d-4111-9acd-3b648a8df45c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d343ed676125dbafcd5314f1cfe67f7c" ns2:_="" ns3:_="">
     <xsd:import namespace="bb5933e1-39c5-43d4-bb0e-9e063605db7e"/>
@@ -19567,14 +19556,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f51bf047-e00d-4111-9acd-3b648a8df45c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb5933e1-39c5-43d4-bb0e-9e063605db7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE723B2C-1BFC-4804-B7F3-9EA38C1D43D6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B318E1E-A80F-4091-9E4D-E3248AE98C97}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DDBE47C-C6A7-41E9-8322-5F40C8EF948C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DDBE47C-C6A7-41E9-8322-5F40C8EF948C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B318E1E-A80F-4091-9E4D-E3248AE98C97}"/>
 </file>
--- a/26-27_Admin_Calendar_Events_CTE-LL_Version.xlsx
+++ b/26-27_Admin_Calendar_Events_CTE-LL_Version.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lausd.sharepoint.com/teams/CTE-LLLeadership/Shared Documents/Calendaring/CTELL_Calendar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="141" documentId="8_{AFEB7EE0-A3A0-BE46-B68A-F48D580478B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4814403-C221-9041-9E37-61538F50F135}"/>
+  <xr:revisionPtr revIDLastSave="146" documentId="8_{AFEB7EE0-A3A0-BE46-B68A-F48D580478B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A81D601-7D86-394C-9DA8-4D70533D327F}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -776,9 +776,6 @@
     <t>Friday, 10/23/26</t>
   </si>
   <si>
-    <t>Linke Learning Conference ▶️</t>
-  </si>
-  <si>
     <t>Indian Wells Resort Hotel, Palm Springs, CA</t>
   </si>
   <si>
@@ -1406,6 +1403,9 @@
   </si>
   <si>
     <t>LAMC 3rd CTE Symposium (CANCELED)</t>
+  </si>
+  <si>
+    <t>Linked Learning Conference ▶️</t>
   </si>
 </sst>
 </file>
@@ -5813,8 +5813,8 @@
         <v>13</v>
       </c>
       <c r="F74" s="34"/>
-      <c r="G74" s="33" t="s">
-        <v>127</v>
+      <c r="G74" s="19" t="s">
+        <v>336</v>
       </c>
       <c r="H74" s="33" t="s">
         <v>89</v>
@@ -5823,7 +5823,7 @@
         <v>35</v>
       </c>
       <c r="J74" s="34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K74" s="33"/>
       <c r="L74" s="34"/>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="F75" s="34"/>
       <c r="G75" s="33" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H75" s="34"/>
       <c r="I75" s="33" t="s">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="J75" s="34"/>
       <c r="K75" s="33" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L75" s="34"/>
       <c r="M75" s="34" t="s">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="F76" s="34"/>
       <c r="G76" s="33" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H76" s="34"/>
       <c r="I76" s="34" t="s">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="F78" s="34"/>
       <c r="G78" s="33" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H78" s="33" t="s">
         <v>25</v>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="J78" s="34"/>
       <c r="K78" s="33" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L78" s="34"/>
       <c r="M78" s="34" t="s">
@@ -6096,11 +6096,11 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="E80" s="33" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F80" s="34"/>
       <c r="G80" s="19" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H80" s="33" t="s">
         <v>41</v>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="F81" s="34"/>
       <c r="G81" s="33" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H81" s="34" t="s">
         <v>46</v>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="F82" s="34"/>
       <c r="G82" s="33" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H82" s="34"/>
       <c r="I82" s="34"/>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="F84" s="34"/>
       <c r="G84" s="33" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H84" s="33" t="s">
         <v>25</v>
@@ -6368,11 +6368,11 @@
       <c r="C86" s="35"/>
       <c r="D86" s="35"/>
       <c r="E86" s="33" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F86" s="34"/>
       <c r="G86" s="19" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H86" s="34"/>
       <c r="I86" s="33" t="s">
@@ -6581,7 +6581,7 @@
         <v>97</v>
       </c>
       <c r="J90" s="34" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K90" s="46" t="s">
         <v>110</v>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="F91" s="34"/>
       <c r="G91" s="33" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H91" s="34" t="s">
         <v>89</v>
@@ -6684,7 +6684,7 @@
         <v>17</v>
       </c>
       <c r="K92" s="33" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L92" s="34"/>
       <c r="M92" s="34" t="s">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="F96" s="34"/>
       <c r="G96" s="33" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H96" s="33" t="s">
         <v>46</v>
@@ -6933,7 +6933,7 @@
         <v>35</v>
       </c>
       <c r="J97" s="34" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K97" s="34"/>
       <c r="L97" s="34"/>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="F98" s="34"/>
       <c r="G98" s="33" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H98" s="34" t="s">
         <v>25</v>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="F99" s="34"/>
       <c r="G99" s="33" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H99" s="34" t="s">
         <v>58</v>
@@ -7230,7 +7230,7 @@
         <v>17</v>
       </c>
       <c r="K103" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L103" s="34"/>
       <c r="M103" s="34" t="s">
@@ -7279,7 +7279,7 @@
         <v>16</v>
       </c>
       <c r="J104" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K104" s="34"/>
       <c r="L104" s="34"/>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F105" s="34"/>
       <c r="G105" s="33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H105" s="33" t="s">
         <v>38</v>
@@ -7360,7 +7360,7 @@
       </c>
       <c r="F106" s="34"/>
       <c r="G106" s="33" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H106" s="34" t="s">
         <v>46</v>
@@ -7467,10 +7467,10 @@
         <v>35</v>
       </c>
       <c r="J108" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="K108" s="33" t="s">
         <v>148</v>
-      </c>
-      <c r="K108" s="33" t="s">
-        <v>149</v>
       </c>
       <c r="L108" s="34"/>
       <c r="M108" s="34" t="s">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="F109" s="34"/>
       <c r="G109" s="33" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H109" s="34" t="s">
         <v>58</v>
@@ -7519,10 +7519,10 @@
         <v>63</v>
       </c>
       <c r="J109" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="K109" s="34" t="s">
         <v>151</v>
-      </c>
-      <c r="K109" s="34" t="s">
-        <v>152</v>
       </c>
       <c r="L109" s="34"/>
       <c r="M109" s="34" t="s">
@@ -7825,7 +7825,7 @@
         <v>35</v>
       </c>
       <c r="J115" s="33" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K115" s="33" t="s">
         <v>23</v>
@@ -7880,7 +7880,7 @@
         <v>17</v>
       </c>
       <c r="K116" s="34" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L116" s="34"/>
       <c r="M116" s="34" t="s">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="F118" s="34"/>
       <c r="G118" s="33" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H118" s="33" t="s">
         <v>89</v>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="F119" s="34"/>
       <c r="G119" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H119" s="34"/>
       <c r="I119" s="34" t="s">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="F120" s="34"/>
       <c r="G120" s="33" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H120" s="33" t="s">
         <v>25</v>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="J120" s="34"/>
       <c r="K120" s="33" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L120" s="34"/>
       <c r="M120" s="34" t="s">
@@ -8115,7 +8115,7 @@
         <v>35</v>
       </c>
       <c r="J121" s="33" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K121" s="33" t="s">
         <v>23</v>
@@ -8202,7 +8202,7 @@
       </c>
       <c r="F123" s="34"/>
       <c r="G123" s="33" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H123" s="33" t="s">
         <v>25</v>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="F124" s="34"/>
       <c r="G124" s="33" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H124" s="33" t="s">
         <v>25</v>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="F125" s="34"/>
       <c r="G125" s="33" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H125" s="34"/>
       <c r="I125" s="34"/>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="F126" s="34"/>
       <c r="G126" s="33" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H126" s="34" t="s">
         <v>58</v>
@@ -8584,7 +8584,7 @@
       </c>
       <c r="F131" s="34"/>
       <c r="G131" s="33" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H131" s="34" t="s">
         <v>58</v>
@@ -8593,10 +8593,10 @@
         <v>35</v>
       </c>
       <c r="J131" s="34" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K131" s="34" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L131" s="34"/>
       <c r="M131" s="34" t="s">
@@ -8645,7 +8645,7 @@
         <v>35</v>
       </c>
       <c r="J132" s="33" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K132" s="33" t="s">
         <v>23</v>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="F133" s="34"/>
       <c r="G133" s="33" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H133" s="33" t="s">
         <v>46</v>
@@ -8700,7 +8700,7 @@
         <v>48</v>
       </c>
       <c r="K133" s="33" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L133" s="34"/>
       <c r="M133" s="34" t="s">
@@ -8752,7 +8752,7 @@
         <v>17</v>
       </c>
       <c r="K134" s="34" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L134" s="34"/>
       <c r="M134" s="34" t="s">
@@ -8845,7 +8845,7 @@
         <v>35</v>
       </c>
       <c r="J136" s="33" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K136" s="33" t="s">
         <v>23</v>
@@ -8947,7 +8947,7 @@
         <v>35</v>
       </c>
       <c r="J138" s="33" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K138" s="33" t="s">
         <v>23</v>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="F140" s="34"/>
       <c r="G140" s="33" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H140" s="34"/>
       <c r="I140" s="34"/>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="F141" s="34"/>
       <c r="G141" s="33" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H141" s="33" t="s">
         <v>25</v>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="F142" s="34"/>
       <c r="G142" s="33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H142" s="34" t="s">
         <v>25</v>
@@ -9162,7 +9162,7 @@
       </c>
       <c r="F143" s="34"/>
       <c r="G143" s="33" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H143" s="34" t="s">
         <v>20</v>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="F144" s="34"/>
       <c r="G144" s="33" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H144" s="34"/>
       <c r="I144" s="33" t="s">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="F145" s="34"/>
       <c r="G145" s="33" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H145" s="34" t="s">
         <v>58</v>
@@ -9396,7 +9396,7 @@
       </c>
       <c r="F148" s="34"/>
       <c r="G148" s="33" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H148" s="34" t="s">
         <v>25</v>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="F149" s="34"/>
       <c r="G149" s="33" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H149" s="34" t="s">
         <v>25</v>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="J149" s="34"/>
       <c r="K149" s="33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L149" s="34"/>
       <c r="M149" s="34" t="s">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="F151" s="34"/>
       <c r="G151" s="33" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H151" s="34" t="s">
         <v>89</v>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="F152" s="34"/>
       <c r="G152" s="33" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H152" s="34" t="s">
         <v>20</v>
@@ -9646,7 +9646,7 @@
         <v>17</v>
       </c>
       <c r="K153" s="34" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L153" s="34"/>
       <c r="M153" s="34" t="s">
@@ -9695,7 +9695,7 @@
         <v>35</v>
       </c>
       <c r="J154" s="33" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K154" s="33" t="s">
         <v>23</v>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="F155" s="34"/>
       <c r="G155" s="33" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H155" s="34" t="s">
         <v>46</v>
@@ -9932,7 +9932,7 @@
       </c>
       <c r="F159" s="34"/>
       <c r="G159" s="33" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H159" s="34" t="s">
         <v>15</v>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="F162" s="34"/>
       <c r="G162" s="33" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H162" s="34"/>
       <c r="I162" s="34" t="s">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="F163" s="34"/>
       <c r="G163" s="33" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H163" s="34"/>
       <c r="I163" s="34"/>
@@ -10159,7 +10159,7 @@
         <v>46475</v>
       </c>
       <c r="B164" s="36" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C164" s="32">
         <v>0.60416666666666663</v>
@@ -10172,7 +10172,7 @@
       </c>
       <c r="F164" s="34"/>
       <c r="G164" s="33" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H164" s="34" t="s">
         <v>58</v>
@@ -10326,13 +10326,13 @@
         <v>58</v>
       </c>
       <c r="I167" s="34" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J167" s="34" t="s">
         <v>17</v>
       </c>
       <c r="K167" s="34" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L167" s="34"/>
       <c r="M167" s="34" t="s">
@@ -10381,7 +10381,7 @@
         <v>16</v>
       </c>
       <c r="J168" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K168" s="34"/>
       <c r="L168" s="34"/>
@@ -10416,7 +10416,7 @@
       </c>
       <c r="F169" s="34"/>
       <c r="G169" s="33" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H169" s="34" t="s">
         <v>46</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="J169" s="34"/>
       <c r="K169" s="33" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L169" s="34"/>
       <c r="M169" s="34" t="s">
@@ -10475,7 +10475,7 @@
         <v>35</v>
       </c>
       <c r="J170" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K170" s="33" t="s">
         <v>23</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="F172" s="34"/>
       <c r="G172" s="33" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H172" s="34"/>
       <c r="I172" s="34"/>
@@ -10606,7 +10606,7 @@
       </c>
       <c r="F173" s="34"/>
       <c r="G173" s="33" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H173" s="34"/>
       <c r="I173" s="33" t="s">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="J173" s="34"/>
       <c r="K173" s="33" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L173" s="34"/>
       <c r="M173" s="34" t="s">
@@ -10713,7 +10713,7 @@
         <v>35</v>
       </c>
       <c r="J175" s="33" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K175" s="33" t="s">
         <v>23</v>
@@ -10756,7 +10756,7 @@
       </c>
       <c r="F176" s="34"/>
       <c r="G176" s="33" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H176" s="33" t="s">
         <v>46</v>
@@ -10768,7 +10768,7 @@
         <v>48</v>
       </c>
       <c r="K176" s="33" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L176" s="34"/>
       <c r="M176" s="34" t="s">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="F177" s="34"/>
       <c r="G177" s="33" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H177" s="34"/>
       <c r="I177" s="34" t="s">
@@ -10867,17 +10867,21 @@
     </row>
     <row r="179" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A179" s="30">
-        <v>46499</v>
+        <v>46498</v>
       </c>
       <c r="B179" s="31"/>
-      <c r="C179" s="35"/>
-      <c r="D179" s="35"/>
+      <c r="C179" s="35">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D179" s="35">
+        <v>0.64583333333333337</v>
+      </c>
       <c r="E179" s="33" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F179" s="34"/>
       <c r="G179" s="33" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H179" s="33" t="s">
         <v>46</v>
@@ -10935,7 +10939,7 @@
       </c>
       <c r="F181" s="34"/>
       <c r="G181" s="33" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H181" s="33" t="s">
         <v>25</v>
@@ -10966,7 +10970,7 @@
       </c>
       <c r="F182" s="34"/>
       <c r="G182" s="33" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H182" s="34" t="s">
         <v>89</v>
@@ -11028,7 +11032,7 @@
       </c>
       <c r="F184" s="34"/>
       <c r="G184" s="33" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H184" s="34"/>
       <c r="I184" s="34"/>
@@ -11051,7 +11055,7 @@
       </c>
       <c r="F185" s="34"/>
       <c r="G185" s="33" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H185" s="33" t="s">
         <v>25</v>
@@ -11082,7 +11086,7 @@
       </c>
       <c r="F186" s="34"/>
       <c r="G186" s="33" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H186" s="34" t="s">
         <v>58</v>
@@ -11224,13 +11228,13 @@
         <v>58</v>
       </c>
       <c r="I190" s="34" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J190" s="34" t="s">
         <v>17</v>
       </c>
       <c r="K190" s="34" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L190" s="34"/>
       <c r="M190" s="34" t="s">
@@ -11262,7 +11266,7 @@
         <v>16</v>
       </c>
       <c r="J191" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K191" s="34"/>
       <c r="L191" s="34"/>
@@ -11381,7 +11385,7 @@
       </c>
       <c r="F195" s="34"/>
       <c r="G195" s="33" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H195" s="34" t="s">
         <v>25</v>
@@ -11421,7 +11425,7 @@
         <v>35</v>
       </c>
       <c r="J196" s="33" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K196" s="33" t="s">
         <v>23</v>
@@ -11443,7 +11447,7 @@
       </c>
       <c r="F197" s="34"/>
       <c r="G197" s="33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H197" s="34"/>
       <c r="I197" s="33" t="s">
@@ -11468,7 +11472,7 @@
       </c>
       <c r="F198" s="34"/>
       <c r="G198" s="33" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H198" s="34"/>
       <c r="I198" s="34"/>
@@ -11495,7 +11499,7 @@
       </c>
       <c r="F199" s="34"/>
       <c r="G199" s="33" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H199" s="34" t="s">
         <v>58</v>
@@ -11625,7 +11629,7 @@
       </c>
       <c r="F203" s="34"/>
       <c r="G203" s="33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H203" s="34" t="s">
         <v>58</v>
@@ -11634,10 +11638,10 @@
         <v>16</v>
       </c>
       <c r="J203" s="34" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K203" s="34" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L203" s="34"/>
       <c r="M203" s="34" t="s">
@@ -11744,7 +11748,7 @@
         <v>46552</v>
       </c>
       <c r="B207" s="55" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C207" s="50">
         <v>0.35416666666666669</v>
@@ -11757,7 +11761,7 @@
       </c>
       <c r="F207" s="51"/>
       <c r="G207" s="37" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H207" s="34" t="s">
         <v>46</v>
@@ -11800,7 +11804,7 @@
         <v>17</v>
       </c>
       <c r="K208" s="51" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L208" s="51"/>
       <c r="M208" s="34" t="s">
@@ -11850,7 +11854,7 @@
       </c>
       <c r="F210" s="51"/>
       <c r="G210" s="37" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H210" s="34"/>
       <c r="I210" s="34" t="s">
@@ -11875,7 +11879,7 @@
       </c>
       <c r="F211" s="51"/>
       <c r="G211" s="37" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H211" s="33" t="s">
         <v>25</v>
@@ -11902,7 +11906,7 @@
       </c>
       <c r="F212" s="51"/>
       <c r="G212" s="37" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H212" s="33" t="s">
         <v>25</v>
@@ -11929,7 +11933,7 @@
       </c>
       <c r="F213" s="51"/>
       <c r="G213" s="37" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H213" s="34"/>
       <c r="I213" s="34"/>
@@ -11952,7 +11956,7 @@
       </c>
       <c r="F214" s="51"/>
       <c r="G214" s="37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H214" s="34"/>
       <c r="I214" s="34"/>
@@ -16685,7 +16689,7 @@
   <customSheetViews>
     <customSheetView guid="{8F656852-D603-4744-997A-DE0F92A7585E}" filter="1" showAutoFilter="1">
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-      <autoFilter ref="A1:M198" xr:uid="{FEC57C60-0883-6343-A154-46059B9BDC89}">
+      <autoFilter ref="A1:M198" xr:uid="{5B42E301-AFBF-4844-8441-330416FFB861}">
         <filterColumn colId="6">
           <filters>
             <filter val="GSPP Action Planning Implementation Pathways Region E Day 1  🌁"/>
@@ -16752,21 +16756,21 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>221</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>222</v>
       </c>
       <c r="C2" s="16">
         <v>46203</v>
@@ -16774,16 +16778,16 @@
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>223</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>224</v>
       </c>
       <c r="C3" s="20">
         <v>46199</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E3" s="18"/>
       <c r="F3" s="18"/>
@@ -16810,24 +16814,24 @@
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="18" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C4" s="20">
         <v>46199</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C5" s="21">
         <v>46266</v>
@@ -16835,10 +16839,10 @@
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C6" s="16">
         <v>46356</v>
@@ -16846,34 +16850,34 @@
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>232</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>233</v>
       </c>
       <c r="C10" s="21">
         <v>46120</v>
@@ -16881,20 +16885,20 @@
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -16938,7 +16942,7 @@
         <v>4</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>6</v>
@@ -16974,16 +16978,16 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="C2" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>239</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>240</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>46</v>
@@ -16994,16 +16998,16 @@
         <v>46456</v>
       </c>
       <c r="B3" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="D3" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="D3" s="12" t="s">
+      <c r="E3" s="12" t="s">
         <v>242</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.2">
@@ -17011,16 +17015,16 @@
         <v>46499</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D4" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>244</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -17086,15 +17090,15 @@
         <v>10</v>
       </c>
       <c r="J1" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="K1" s="9" t="s">
         <v>246</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="15" t="s">
@@ -17111,7 +17115,7 @@
         <v>21</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I2" s="19" t="s">
         <v>23</v>
@@ -17121,17 +17125,17 @@
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>250</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>251</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>28</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="19" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F3" s="15" t="s">
         <v>108</v>
@@ -17161,7 +17165,7 @@
         <v>21</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I4" s="19" t="s">
         <v>23</v>
@@ -17171,7 +17175,7 @@
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>39</v>
@@ -17225,7 +17229,7 @@
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="19" t="s">
@@ -17233,7 +17237,7 @@
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F7" s="19" t="s">
         <v>58</v>
@@ -17247,7 +17251,7 @@
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="15" t="s">
@@ -17274,7 +17278,7 @@
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="15" t="s">
@@ -17288,7 +17292,7 @@
         <v>58</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H9" s="15"/>
       <c r="I9" s="15"/>
@@ -17297,7 +17301,7 @@
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="15" t="s">
@@ -17324,7 +17328,7 @@
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="15" t="s">
@@ -17351,7 +17355,7 @@
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="19" t="s">
@@ -17359,7 +17363,7 @@
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="19" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F12" s="19" t="s">
         <v>58</v>
@@ -17374,7 +17378,7 @@
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="15" t="s">
@@ -17401,7 +17405,7 @@
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="15" t="s">
@@ -17428,7 +17432,7 @@
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="19" t="s">
@@ -17453,7 +17457,7 @@
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="15" t="s">
@@ -17467,7 +17471,7 @@
         <v>58</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="15"/>
@@ -17476,7 +17480,7 @@
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="19" t="s">
@@ -17499,7 +17503,7 @@
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="15" t="s">
@@ -17516,7 +17520,7 @@
         <v>35</v>
       </c>
       <c r="H18" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I18" s="19" t="s">
         <v>23</v>
@@ -17526,7 +17530,7 @@
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="19" t="s">
@@ -17549,7 +17553,7 @@
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="15" t="s">
@@ -17576,7 +17580,7 @@
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="19" t="s">
@@ -17584,7 +17588,7 @@
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F21" s="15" t="s">
         <v>108</v>
@@ -17599,7 +17603,7 @@
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B22" s="13"/>
       <c r="C22" s="15" t="s">
@@ -17622,7 +17626,7 @@
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="15" t="s">
@@ -17649,7 +17653,7 @@
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="15" t="s">
@@ -17672,7 +17676,7 @@
     </row>
     <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B25" s="13"/>
       <c r="C25" s="19" t="s">
@@ -17680,7 +17684,7 @@
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="19" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F25" s="15" t="s">
         <v>108</v>
@@ -17695,7 +17699,7 @@
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="15" t="s">
@@ -17722,7 +17726,7 @@
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B27" s="13"/>
       <c r="C27" s="15" t="s">
@@ -17736,7 +17740,7 @@
         <v>58</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H27" s="15"/>
       <c r="I27" s="15"/>
@@ -17745,7 +17749,7 @@
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="19" t="s">
@@ -17753,7 +17757,7 @@
       </c>
       <c r="D28" s="15"/>
       <c r="E28" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F28" s="15" t="s">
         <v>108</v>
@@ -17768,7 +17772,7 @@
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B29" s="13"/>
       <c r="C29" s="15" t="s">
@@ -17795,7 +17799,7 @@
     </row>
     <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>126</v>
@@ -17805,7 +17809,7 @@
       </c>
       <c r="D30" s="15"/>
       <c r="E30" s="19" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F30" s="19" t="s">
         <v>89</v>
@@ -17814,17 +17818,17 @@
         <v>35</v>
       </c>
       <c r="H30" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I30" s="19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J30" s="15"/>
       <c r="K30" s="15"/>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B31" s="13"/>
       <c r="C31" s="15" t="s">
@@ -17841,7 +17845,7 @@
         <v>35</v>
       </c>
       <c r="H31" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I31" s="19" t="s">
         <v>23</v>
@@ -17851,7 +17855,7 @@
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="11" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B32" s="13"/>
       <c r="C32" s="19" t="s">
@@ -17874,7 +17878,7 @@
     </row>
     <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B33" s="13"/>
       <c r="C33" s="19" t="s">
@@ -17897,7 +17901,7 @@
     </row>
     <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B34" s="13"/>
       <c r="C34" s="19" t="s">
@@ -17905,7 +17909,7 @@
       </c>
       <c r="D34" s="15"/>
       <c r="E34" s="19" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F34" s="15" t="s">
         <v>108</v>
@@ -17920,7 +17924,7 @@
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="15" t="s">
@@ -17947,7 +17951,7 @@
     </row>
     <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="11" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B36" s="13"/>
       <c r="C36" s="19" t="s">
@@ -17955,7 +17959,7 @@
       </c>
       <c r="D36" s="15"/>
       <c r="E36" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F36" s="15" t="s">
         <v>108</v>
@@ -17970,7 +17974,7 @@
     </row>
     <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="11" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B37" s="13"/>
       <c r="C37" s="19" t="s">
@@ -17978,7 +17982,7 @@
       </c>
       <c r="D37" s="15"/>
       <c r="E37" s="19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F37" s="15" t="s">
         <v>89</v>
@@ -17993,7 +17997,7 @@
     </row>
     <row r="38" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B38" s="13"/>
       <c r="C38" s="15" t="s">
@@ -18007,18 +18011,18 @@
         <v>58</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H38" s="15"/>
       <c r="I38" s="19" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J38" s="15"/>
       <c r="K38" s="15"/>
     </row>
     <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B39" s="13"/>
       <c r="C39" s="15" t="s">
@@ -18045,7 +18049,7 @@
     </row>
     <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B40" s="13"/>
       <c r="C40" s="15" t="s">
@@ -18053,7 +18057,7 @@
       </c>
       <c r="D40" s="15"/>
       <c r="E40" s="19" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F40" s="15" t="s">
         <v>89</v>
@@ -18068,7 +18072,7 @@
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B41" s="13"/>
       <c r="C41" s="15" t="s">
@@ -18095,7 +18099,7 @@
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B42" s="13"/>
       <c r="C42" s="15" t="s">
@@ -18103,7 +18107,7 @@
       </c>
       <c r="D42" s="15"/>
       <c r="E42" s="19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F42" s="15" t="s">
         <v>58</v>
@@ -18118,7 +18122,7 @@
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="15" t="s">
@@ -18145,7 +18149,7 @@
     </row>
     <row r="44" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B44" s="13"/>
       <c r="C44" s="15" t="s">
@@ -18153,7 +18157,7 @@
       </c>
       <c r="D44" s="15"/>
       <c r="E44" s="19" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F44" s="15" t="s">
         <v>80</v>
@@ -18168,7 +18172,7 @@
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B45" s="13"/>
       <c r="C45" s="15" t="s">
@@ -18195,7 +18199,7 @@
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B46" s="13"/>
       <c r="C46" s="15" t="s">
@@ -18209,7 +18213,7 @@
         <v>58</v>
       </c>
       <c r="G46" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H46" s="15"/>
       <c r="I46" s="15"/>
@@ -18218,7 +18222,7 @@
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B47" s="13"/>
       <c r="C47" s="19" t="s">
@@ -18226,7 +18230,7 @@
       </c>
       <c r="D47" s="15"/>
       <c r="E47" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F47" s="19" t="s">
         <v>38</v>
@@ -18241,7 +18245,7 @@
     </row>
     <row r="48" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B48" s="13"/>
       <c r="C48" s="15" t="s">
@@ -18258,7 +18262,7 @@
         <v>35</v>
       </c>
       <c r="H48" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I48" s="19" t="s">
         <v>23</v>
@@ -18268,7 +18272,7 @@
     </row>
     <row r="49" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B49" s="13"/>
       <c r="C49" s="15" t="s">
@@ -18295,7 +18299,7 @@
     </row>
     <row r="50" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B50" s="13"/>
       <c r="C50" s="15" t="s">
@@ -18322,7 +18326,7 @@
     </row>
     <row r="51" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B51" s="13"/>
       <c r="C51" s="15" t="s">
@@ -18336,7 +18340,7 @@
         <v>58</v>
       </c>
       <c r="G51" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H51" s="15"/>
       <c r="I51" s="15"/>
@@ -18345,7 +18349,7 @@
     </row>
     <row r="52" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B52" s="13"/>
       <c r="C52" s="19" t="s">
@@ -18353,7 +18357,7 @@
       </c>
       <c r="D52" s="15"/>
       <c r="E52" s="19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F52" s="19" t="s">
         <v>89</v>
@@ -18368,7 +18372,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A53" s="11" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B53" s="13"/>
       <c r="C53" s="15" t="s">
@@ -18395,7 +18399,7 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A54" s="11" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B54" s="13"/>
       <c r="C54" s="19" t="s">
@@ -18418,7 +18422,7 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A55" s="11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B55" s="13"/>
       <c r="C55" s="15" t="s">
@@ -18426,7 +18430,7 @@
       </c>
       <c r="D55" s="15"/>
       <c r="E55" s="19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F55" s="15" t="s">
         <v>58</v>
@@ -18441,7 +18445,7 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A56" s="11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B56" s="13"/>
       <c r="C56" s="15" t="s">
@@ -18468,7 +18472,7 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A57" s="11" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B57" s="13"/>
       <c r="C57" s="15" t="s">
@@ -18476,7 +18480,7 @@
       </c>
       <c r="D57" s="15"/>
       <c r="E57" s="19" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F57" s="15" t="s">
         <v>58</v>
@@ -18491,7 +18495,7 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A58" s="11" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B58" s="13"/>
       <c r="C58" s="15" t="s">
@@ -18518,7 +18522,7 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A59" s="11" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B59" s="13"/>
       <c r="C59" s="15" t="s">
@@ -18532,7 +18536,7 @@
         <v>58</v>
       </c>
       <c r="G59" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H59" s="15"/>
       <c r="I59" s="15"/>
@@ -18541,7 +18545,7 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A60" s="11" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B60" s="13"/>
       <c r="C60" s="15" t="s">
@@ -18568,7 +18572,7 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A61" s="11" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B61" s="13"/>
       <c r="C61" s="15" t="s">
@@ -18585,7 +18589,7 @@
         <v>35</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I61" s="19" t="s">
         <v>23</v>
@@ -18595,7 +18599,7 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A62" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B62" s="13"/>
       <c r="C62" s="19" t="s">
@@ -18618,7 +18622,7 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A63" s="11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B63" s="13"/>
       <c r="C63" s="15" t="s">
@@ -18645,7 +18649,7 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A64" s="11" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B64" s="13"/>
       <c r="C64" s="15" t="s">
@@ -18653,7 +18657,7 @@
       </c>
       <c r="D64" s="15"/>
       <c r="E64" s="19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F64" s="15" t="s">
         <v>58</v>
@@ -18668,7 +18672,7 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A65" s="11" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B65" s="13"/>
       <c r="C65" s="19" t="s">
@@ -18691,7 +18695,7 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A66" s="11" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B66" s="13"/>
       <c r="C66" s="19" t="s">
@@ -18699,7 +18703,7 @@
       </c>
       <c r="D66" s="15"/>
       <c r="E66" s="19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F66" s="15" t="s">
         <v>89</v>
@@ -18741,7 +18745,7 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A68" s="11" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B68" s="13"/>
       <c r="C68" s="15" t="s">
@@ -18755,7 +18759,7 @@
         <v>58</v>
       </c>
       <c r="G68" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H68" s="15"/>
       <c r="I68" s="15"/>
@@ -18781,7 +18785,7 @@
         <v>35</v>
       </c>
       <c r="H69" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I69" s="19" t="s">
         <v>23</v>
@@ -18791,7 +18795,7 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A70" s="11" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B70" s="13"/>
       <c r="C70" s="15" t="s">
@@ -18814,17 +18818,17 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A71" s="11" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C71" s="15" t="s">
         <v>56</v>
       </c>
       <c r="D71" s="15"/>
       <c r="E71" s="19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F71" s="15" t="s">
         <v>58</v>
@@ -18839,7 +18843,7 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A72" s="11" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B72" s="13"/>
       <c r="C72" s="15" t="s">
@@ -18866,7 +18870,7 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A73" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B73" s="13"/>
       <c r="C73" s="15" t="s">
@@ -18874,7 +18878,7 @@
       </c>
       <c r="D73" s="15"/>
       <c r="E73" s="19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F73" s="15" t="s">
         <v>20</v>
@@ -18887,7 +18891,7 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A74" s="11" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B74" s="13"/>
       <c r="C74" s="15" t="s">
@@ -18901,7 +18905,7 @@
         <v>58</v>
       </c>
       <c r="G74" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H74" s="15"/>
       <c r="I74" s="15"/>
@@ -18910,7 +18914,7 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A75" s="11" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B75" s="13"/>
       <c r="C75" s="15" t="s">
@@ -18937,7 +18941,7 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A76" s="11" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B76" s="13"/>
       <c r="C76" s="15" t="s">
@@ -18964,7 +18968,7 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A77" s="11" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B77" s="13"/>
       <c r="C77" s="19" t="s">
@@ -18987,7 +18991,7 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A78" s="11" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B78" s="13"/>
       <c r="C78" s="19" t="s">
@@ -18995,7 +18999,7 @@
       </c>
       <c r="D78" s="15"/>
       <c r="E78" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F78" s="15" t="s">
         <v>89</v>
@@ -19010,7 +19014,7 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A79" s="11" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B79" s="13"/>
       <c r="C79" s="15" t="s">
@@ -19037,7 +19041,7 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A80" s="11" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B80" s="13"/>
       <c r="C80" s="15" t="s">
@@ -19064,7 +19068,7 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A81" s="11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B81" s="13"/>
       <c r="C81" s="15" t="s">
@@ -19072,7 +19076,7 @@
       </c>
       <c r="D81" s="15"/>
       <c r="E81" s="19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F81" s="15" t="s">
         <v>58</v>
@@ -19087,7 +19091,7 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A82" s="22" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B82" s="23"/>
       <c r="C82" s="15" t="s">
@@ -19114,7 +19118,7 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A83" s="22" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B83" s="23"/>
       <c r="C83" s="15" t="s">
@@ -19128,7 +19132,7 @@
         <v>58</v>
       </c>
       <c r="G83" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H83" s="15"/>
       <c r="I83" s="15"/>
@@ -19137,7 +19141,7 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A84" s="22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B84" s="23"/>
       <c r="C84" s="15" t="s">
@@ -19164,7 +19168,7 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A85" s="22" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B85" s="23"/>
       <c r="C85" s="15" t="s">
@@ -19181,7 +19185,7 @@
         <v>35</v>
       </c>
       <c r="H85" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I85" s="19" t="s">
         <v>23</v>
@@ -19191,7 +19195,7 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A86" s="22" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B86" s="23"/>
       <c r="C86" s="15" t="s">
@@ -19218,7 +19222,7 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A87" s="22" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B87" s="23"/>
       <c r="C87" s="15" t="s">
@@ -19226,7 +19230,7 @@
       </c>
       <c r="D87" s="15"/>
       <c r="E87" s="19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F87" s="15" t="s">
         <v>58</v>
@@ -19241,7 +19245,7 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A88" s="22" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B88" s="23"/>
       <c r="C88" s="15" t="s">
@@ -19255,7 +19259,7 @@
         <v>58</v>
       </c>
       <c r="G88" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H88" s="15"/>
       <c r="I88" s="15"/>
@@ -19283,14 +19287,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f51bf047-e00d-4111-9acd-3b648a8df45c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb5933e1-39c5-43d4-bb0e-9e063605db7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19523,27 +19525,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f51bf047-e00d-4111-9acd-3b648a8df45c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb5933e1-39c5-43d4-bb0e-9e063605db7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B318E1E-A80F-4091-9E4D-E3248AE98C97}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE723B2C-1BFC-4804-B7F3-9EA38C1D43D6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="bb5933e1-39c5-43d4-bb0e-9e063605db7e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="f51bf047-e00d-4111-9acd-3b648a8df45c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -19568,9 +19563,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE723B2C-1BFC-4804-B7F3-9EA38C1D43D6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B318E1E-A80F-4091-9E4D-E3248AE98C97}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="f51bf047-e00d-4111-9acd-3b648a8df45c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="bb5933e1-39c5-43d4-bb0e-9e063605db7e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/26-27_Admin_Calendar_Events_CTE-LL_Version.xlsx
+++ b/26-27_Admin_Calendar_Events_CTE-LL_Version.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lausd.sharepoint.com/teams/CTE-LLLeadership/Shared Documents/Calendaring/CTELL_Calendar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="146" documentId="8_{AFEB7EE0-A3A0-BE46-B68A-F48D580478B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A81D601-7D86-394C-9DA8-4D70533D327F}"/>
+  <xr:revisionPtr revIDLastSave="148" documentId="8_{AFEB7EE0-A3A0-BE46-B68A-F48D580478B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73500B6F-8E7F-0243-BC0C-124909E6375C}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -392,7 +392,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1819" uniqueCount="339">
   <si>
     <t>Date</t>
   </si>
@@ -1406,6 +1406,12 @@
   </si>
   <si>
     <t>Linked Learning Conference ▶️</t>
+  </si>
+  <si>
+    <t>Educators of Tomorrow Hiring Event 📗</t>
+  </si>
+  <si>
+    <t>Cal State University, Los Angeles</t>
   </si>
 </sst>
 </file>
@@ -10880,8 +10886,8 @@
         <v>13</v>
       </c>
       <c r="F179" s="34"/>
-      <c r="G179" s="33" t="s">
-        <v>198</v>
+      <c r="G179" s="19" t="s">
+        <v>337</v>
       </c>
       <c r="H179" s="33" t="s">
         <v>46</v>
@@ -10889,7 +10895,9 @@
       <c r="I179" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="J179" s="34"/>
+      <c r="J179" s="15" t="s">
+        <v>338</v>
+      </c>
       <c r="K179" s="34"/>
       <c r="L179" s="34"/>
       <c r="M179" s="34" t="s">

--- a/26-27_Admin_Calendar_Events_CTE-LL_Version.xlsx
+++ b/26-27_Admin_Calendar_Events_CTE-LL_Version.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11023"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lausd.sharepoint.com/teams/CTE-LLLeadership/Shared Documents/Calendaring/CTELL_Calendar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="148" documentId="8_{AFEB7EE0-A3A0-BE46-B68A-F48D580478B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73500B6F-8E7F-0243-BC0C-124909E6375C}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="8_{AFEB7EE0-A3A0-BE46-B68A-F48D580478B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2A40512-1739-5C4F-B2DF-AC6DFB7BB5B7}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,8 +19,8 @@
     <sheet name="LinkedLearning" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'26-27_Events'!$A$1:$M$214</definedName>
-    <definedName name="Z_8F656852_D603_4744_997A_DE0F92A7585E_.wvu.FilterData" localSheetId="0" hidden="1">'26-27_Events'!$A$1:$M$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'26-27_Events'!$A$1:$M$215</definedName>
+    <definedName name="Z_8F656852_D603_4744_997A_DE0F92A7585E_.wvu.FilterData" localSheetId="0" hidden="1">'26-27_Events'!$A$1:$M$204</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <customWorkbookViews>
@@ -320,7 +320,7 @@
 Assigned to rekha.prakash@lausd.net</t>
       </text>
     </comment>
-    <comment ref="J96" authorId="6" shapeId="0" xr:uid="{80E866D6-BFAF-4296-9EAE-A24011716C28}">
+    <comment ref="J97" authorId="6" shapeId="0" xr:uid="{80E866D6-BFAF-4296-9EAE-A24011716C28}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -331,7 +331,7 @@
 Assigned to rekha.prakash@lausd.net</t>
       </text>
     </comment>
-    <comment ref="J133" authorId="7" shapeId="0" xr:uid="{572F9DA1-DB36-4AC3-A4E5-E9C38653E985}">
+    <comment ref="J134" authorId="7" shapeId="0" xr:uid="{572F9DA1-DB36-4AC3-A4E5-E9C38653E985}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -342,7 +342,7 @@
 Assigned to rekha.prakash@lausd.net</t>
       </text>
     </comment>
-    <comment ref="J176" authorId="8" shapeId="0" xr:uid="{19DDB89B-3A12-4552-B614-77B383CFE27B}">
+    <comment ref="J177" authorId="8" shapeId="0" xr:uid="{19DDB89B-3A12-4552-B614-77B383CFE27B}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -392,7 +392,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1819" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1825" uniqueCount="340">
   <si>
     <t>Date</t>
   </si>
@@ -1412,6 +1412,9 @@
   </si>
   <si>
     <t>Cal State University, Los Angeles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSPP Counselor PD 🌁 </t>
   </si>
 </sst>
 </file>
@@ -2171,21 +2174,21 @@
       <mention mentionpersonId="{D5E65F0F-B0E9-CF42-A55F-18641707047D}" mentionId="{9CB472DA-D422-4FA8-A5BA-5E793DAE0CEE}" startIndex="23" length="24"/>
     </mentions>
   </threadedComment>
-  <threadedComment ref="J96" dT="2026-08-24T19:19:27.00" personId="{EA5698C8-7C4A-4A39-873A-050A87D08922}" id="{80E866D6-BFAF-4296-9EAE-A24011716C28}">
+  <threadedComment ref="J97" dT="2026-08-24T19:19:27.00" personId="{EA5698C8-7C4A-4A39-873A-050A87D08922}" id="{80E866D6-BFAF-4296-9EAE-A24011716C28}">
     <text>Please update if known @rekha.prakash@lausd.net
 Assigned to rekha.prakash@lausd.net</text>
     <mentions>
       <mention mentionpersonId="{D5E65F0F-B0E9-CF42-A55F-18641707047D}" mentionId="{691AD2DE-CA99-4F22-B8D0-B42BB58CC296}" startIndex="23" length="24"/>
     </mentions>
   </threadedComment>
-  <threadedComment ref="J133" dT="2026-08-24T19:19:31.00" personId="{EA5698C8-7C4A-4A39-873A-050A87D08922}" id="{572F9DA1-DB36-4AC3-A4E5-E9C38653E985}">
+  <threadedComment ref="J134" dT="2026-08-24T19:19:31.00" personId="{EA5698C8-7C4A-4A39-873A-050A87D08922}" id="{572F9DA1-DB36-4AC3-A4E5-E9C38653E985}">
     <text>Please update if known @rekha.prakash@lausd.net
 Assigned to rekha.prakash@lausd.net</text>
     <mentions>
       <mention mentionpersonId="{D5E65F0F-B0E9-CF42-A55F-18641707047D}" mentionId="{F6AF3A79-49FE-4E10-9DEB-F6F24CB735C6}" startIndex="23" length="24"/>
     </mentions>
   </threadedComment>
-  <threadedComment ref="J176" dT="2026-08-24T19:19:35.00" personId="{EA5698C8-7C4A-4A39-873A-050A87D08922}" id="{19DDB89B-3A12-4552-B614-77B383CFE27B}">
+  <threadedComment ref="J177" dT="2026-08-24T19:19:35.00" personId="{EA5698C8-7C4A-4A39-873A-050A87D08922}" id="{19DDB89B-3A12-4552-B614-77B383CFE27B}">
     <text>Please update if known @rekha.prakash@lausd.net
 Assigned to rekha.prakash@lausd.net</text>
     <mentions>
@@ -2200,7 +2203,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD999"/>
+  <dimension ref="A1:AD1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="18.5" style="29" customWidth="1"/>
@@ -6237,7 +6240,7 @@
         <v>13</v>
       </c>
       <c r="F83" s="34"/>
-      <c r="G83" s="33" t="s">
+      <c r="G83" s="19" t="s">
         <v>62</v>
       </c>
       <c r="H83" s="34" t="s">
@@ -6410,37 +6413,35 @@
     </row>
     <row r="87" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="30">
-        <v>46330</v>
+        <v>46329</v>
       </c>
       <c r="B87" s="31"/>
-      <c r="C87" s="32">
+      <c r="C87" s="35">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D87" s="32">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="E87" s="34" t="s">
+      <c r="D87" s="35">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="E87" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F87" s="34"/>
-      <c r="G87" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="H87" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="I87" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="J87" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="K87" s="33" t="s">
-        <v>23</v>
-      </c>
+      <c r="G87" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="H87" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="I87" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="J87" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="K87" s="34"/>
       <c r="L87" s="34"/>
       <c r="M87" s="34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N87" s="12"/>
       <c r="O87" s="12"/>
@@ -6469,25 +6470,27 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D88" s="32">
-        <v>0.5</v>
-      </c>
-      <c r="E88" s="33" t="s">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E88" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F88" s="34"/>
       <c r="G88" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="H88" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="I88" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="J88" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K88" s="34"/>
+        <v>19</v>
+      </c>
+      <c r="H88" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="I88" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="J88" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="K88" s="33" t="s">
+        <v>23</v>
+      </c>
       <c r="L88" s="34"/>
       <c r="M88" s="34" t="s">
         <v>18</v>
@@ -6511,36 +6514,34 @@
       <c r="AD88" s="12"/>
     </row>
     <row r="89" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="40">
-        <v>46331</v>
-      </c>
-      <c r="B89" s="41"/>
-      <c r="C89" s="42">
-        <v>0.625</v>
-      </c>
-      <c r="D89" s="42">
-        <v>0.6875</v>
-      </c>
-      <c r="E89" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="F89" s="41"/>
-      <c r="G89" s="41" t="s">
-        <v>75</v>
+      <c r="A89" s="30">
+        <v>46330</v>
+      </c>
+      <c r="B89" s="31"/>
+      <c r="C89" s="32">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D89" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="E89" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F89" s="34"/>
+      <c r="G89" s="33" t="s">
+        <v>14</v>
       </c>
       <c r="H89" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="I89" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="J89" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="K89" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="L89" s="43"/>
+        <v>15</v>
+      </c>
+      <c r="I89" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="J89" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K89" s="34"/>
+      <c r="L89" s="34"/>
       <c r="M89" s="34" t="s">
         <v>18</v>
       </c>
@@ -6563,38 +6564,38 @@
       <c r="AD89" s="12"/>
     </row>
     <row r="90" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="30">
-        <v>46333</v>
-      </c>
-      <c r="B90" s="31"/>
-      <c r="C90" s="35">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D90" s="35">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="E90" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="F90" s="34"/>
-      <c r="G90" s="33" t="s">
-        <v>107</v>
+      <c r="A90" s="40">
+        <v>46331</v>
+      </c>
+      <c r="B90" s="41"/>
+      <c r="C90" s="42">
+        <v>0.625</v>
+      </c>
+      <c r="D90" s="42">
+        <v>0.6875</v>
+      </c>
+      <c r="E90" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90" s="41"/>
+      <c r="G90" s="41" t="s">
+        <v>75</v>
       </c>
       <c r="H90" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="I90" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="J90" s="34" t="s">
-        <v>136</v>
-      </c>
-      <c r="K90" s="46" t="s">
-        <v>110</v>
-      </c>
-      <c r="L90" s="34"/>
+        <v>50</v>
+      </c>
+      <c r="I90" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="J90" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="K90" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="L90" s="43"/>
       <c r="M90" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N90" s="12"/>
       <c r="O90" s="12"/>
@@ -6630,16 +6631,20 @@
       </c>
       <c r="F91" s="34"/>
       <c r="G91" s="33" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="H91" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="I91" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="I91" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="J91" s="34"/>
-      <c r="K91" s="34"/>
+      <c r="J91" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="K91" s="46" t="s">
+        <v>110</v>
+      </c>
       <c r="L91" s="34"/>
       <c r="M91" s="34" t="s">
         <v>32</v>
@@ -6664,37 +6669,33 @@
     </row>
     <row r="92" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="30">
-        <v>46338</v>
+        <v>46333</v>
       </c>
       <c r="B92" s="31"/>
-      <c r="C92" s="32">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D92" s="32">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="E92" s="34" t="s">
+      <c r="C92" s="35">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D92" s="35">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="E92" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F92" s="34"/>
       <c r="G92" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="H92" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="I92" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="J92" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K92" s="33" t="s">
-        <v>138</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="H92" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="I92" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="J92" s="34"/>
+      <c r="K92" s="34"/>
       <c r="L92" s="34"/>
       <c r="M92" s="34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N92" s="12"/>
       <c r="O92" s="12"/>
@@ -6716,30 +6717,34 @@
     </row>
     <row r="93" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="30">
-        <v>46339</v>
+        <v>46338</v>
       </c>
       <c r="B93" s="31"/>
       <c r="C93" s="32">
-        <v>0.35416666666666669</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D93" s="32">
-        <v>0.4375</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="E93" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F93" s="34"/>
       <c r="G93" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="H93" s="34"/>
-      <c r="I93" s="33" t="s">
-        <v>51</v>
+        <v>91</v>
+      </c>
+      <c r="H93" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="I93" s="34" t="s">
+        <v>30</v>
       </c>
       <c r="J93" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="K93" s="33"/>
+      <c r="K93" s="33" t="s">
+        <v>138</v>
+      </c>
       <c r="L93" s="34"/>
       <c r="M93" s="34" t="s">
         <v>18</v>
@@ -6764,35 +6769,33 @@
     </row>
     <row r="94" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="30">
-        <v>46340</v>
+        <v>46339</v>
       </c>
       <c r="B94" s="31"/>
-      <c r="C94" s="35">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D94" s="35">
-        <v>0.5</v>
-      </c>
-      <c r="E94" s="33" t="s">
+      <c r="C94" s="32">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D94" s="32">
+        <v>0.4375</v>
+      </c>
+      <c r="E94" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F94" s="34"/>
       <c r="G94" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="H94" s="33" t="s">
-        <v>46</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="H94" s="34"/>
       <c r="I94" s="33" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="J94" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="K94" s="34"/>
+        <v>17</v>
+      </c>
+      <c r="K94" s="33"/>
       <c r="L94" s="34"/>
       <c r="M94" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N94" s="12"/>
       <c r="O94" s="12"/>
@@ -6814,37 +6817,35 @@
     </row>
     <row r="95" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="30">
-        <v>46344</v>
+        <v>46340</v>
       </c>
       <c r="B95" s="31"/>
-      <c r="C95" s="32">
-        <v>0.34375</v>
-      </c>
-      <c r="D95" s="32">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="E95" s="34" t="s">
+      <c r="C95" s="35">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D95" s="35">
+        <v>0.5</v>
+      </c>
+      <c r="E95" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F95" s="34"/>
       <c r="G95" s="33" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="H95" s="33" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I95" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="J95" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="K95" s="33" t="s">
-        <v>23</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="J95" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="K95" s="34"/>
       <c r="L95" s="34"/>
       <c r="M95" s="34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N95" s="12"/>
       <c r="O95" s="12"/>
@@ -6869,32 +6870,34 @@
         <v>46344</v>
       </c>
       <c r="B96" s="31"/>
-      <c r="C96" s="35">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D96" s="35">
-        <v>0.64583333333333337</v>
+      <c r="C96" s="32">
+        <v>0.34375</v>
+      </c>
+      <c r="D96" s="32">
+        <v>0.52083333333333337</v>
       </c>
       <c r="E96" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F96" s="34"/>
       <c r="G96" s="33" t="s">
-        <v>139</v>
+        <v>53</v>
       </c>
       <c r="H96" s="33" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I96" s="33" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="J96" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="K96" s="33"/>
+      <c r="K96" s="33" t="s">
+        <v>23</v>
+      </c>
       <c r="L96" s="34"/>
       <c r="M96" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N96" s="12"/>
       <c r="O96" s="12"/>
@@ -6916,7 +6919,7 @@
     </row>
     <row r="97" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="30">
-        <v>46345</v>
+        <v>46344</v>
       </c>
       <c r="B97" s="31"/>
       <c r="C97" s="35">
@@ -6930,18 +6933,18 @@
       </c>
       <c r="F97" s="34"/>
       <c r="G97" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="H97" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="I97" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="J97" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="K97" s="34"/>
+        <v>139</v>
+      </c>
+      <c r="H97" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="I97" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="J97" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="K97" s="33"/>
       <c r="L97" s="34"/>
       <c r="M97" s="34" t="s">
         <v>32</v>
@@ -6966,25 +6969,31 @@
     </row>
     <row r="98" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="30">
-        <v>46356</v>
+        <v>46345</v>
       </c>
       <c r="B98" s="31"/>
-      <c r="C98" s="32"/>
-      <c r="D98" s="32"/>
+      <c r="C98" s="35">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D98" s="35">
+        <v>0.64583333333333337</v>
+      </c>
       <c r="E98" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F98" s="34"/>
       <c r="G98" s="33" t="s">
-        <v>141</v>
+        <v>88</v>
       </c>
       <c r="H98" s="34" t="s">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="I98" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="J98" s="34"/>
+        <v>35</v>
+      </c>
+      <c r="J98" s="34" t="s">
+        <v>140</v>
+      </c>
       <c r="K98" s="34"/>
       <c r="L98" s="34"/>
       <c r="M98" s="34" t="s">
@@ -7010,27 +7019,23 @@
     </row>
     <row r="99" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="30">
-        <v>46357</v>
+        <v>46356</v>
       </c>
       <c r="B99" s="31"/>
-      <c r="C99" s="32">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D99" s="32">
-        <v>0.6875</v>
-      </c>
+      <c r="C99" s="32"/>
+      <c r="D99" s="32"/>
       <c r="E99" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F99" s="34"/>
       <c r="G99" s="33" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H99" s="34" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="I99" s="34" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="J99" s="34"/>
       <c r="K99" s="34"/>
@@ -7058,37 +7063,33 @@
     </row>
     <row r="100" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="30">
-        <v>46358</v>
+        <v>46357</v>
       </c>
       <c r="B100" s="31"/>
       <c r="C100" s="32">
-        <v>0.35416666666666669</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D100" s="32">
-        <v>0.52083333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="E100" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F100" s="34"/>
       <c r="G100" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="H100" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="I100" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="J100" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="K100" s="33" t="s">
-        <v>23</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="H100" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="I100" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="J100" s="34"/>
+      <c r="K100" s="34"/>
       <c r="L100" s="34"/>
       <c r="M100" s="34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N100" s="12"/>
       <c r="O100" s="12"/>
@@ -7110,30 +7111,34 @@
     </row>
     <row r="101" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="30">
-        <v>46360</v>
+        <v>46358</v>
       </c>
       <c r="B101" s="31"/>
       <c r="C101" s="32">
         <v>0.35416666666666669</v>
       </c>
       <c r="D101" s="32">
-        <v>0.4375</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="E101" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F101" s="34"/>
       <c r="G101" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="H101" s="34"/>
+        <v>19</v>
+      </c>
+      <c r="H101" s="33" t="s">
+        <v>20</v>
+      </c>
       <c r="I101" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="J101" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K101" s="33"/>
+        <v>21</v>
+      </c>
+      <c r="J101" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="K101" s="33" t="s">
+        <v>23</v>
+      </c>
       <c r="L101" s="34"/>
       <c r="M101" s="34" t="s">
         <v>18</v>
@@ -7158,34 +7163,30 @@
     </row>
     <row r="102" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="30">
-        <v>46365</v>
+        <v>46360</v>
       </c>
       <c r="B102" s="31"/>
       <c r="C102" s="32">
-        <v>0.34375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D102" s="32">
-        <v>0.52083333333333337</v>
+        <v>0.4375</v>
       </c>
       <c r="E102" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F102" s="34"/>
       <c r="G102" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="H102" s="33" t="s">
-        <v>54</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="H102" s="34"/>
       <c r="I102" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="J102" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="K102" s="33" t="s">
-        <v>23</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="J102" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K102" s="33"/>
       <c r="L102" s="34"/>
       <c r="M102" s="34" t="s">
         <v>18</v>
@@ -7214,29 +7215,29 @@
       </c>
       <c r="B103" s="31"/>
       <c r="C103" s="32">
+        <v>0.34375</v>
+      </c>
+      <c r="D103" s="32">
         <v>0.52083333333333337</v>
-      </c>
-      <c r="D103" s="32">
-        <v>0.54166666666666663</v>
       </c>
       <c r="E103" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F103" s="34"/>
       <c r="G103" s="33" t="s">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="H103" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="I103" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="I103" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="J103" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K103" s="34" t="s">
-        <v>143</v>
+      <c r="J103" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="K103" s="33" t="s">
+        <v>23</v>
       </c>
       <c r="L103" s="34"/>
       <c r="M103" s="34" t="s">
@@ -7266,28 +7267,30 @@
       </c>
       <c r="B104" s="31"/>
       <c r="C104" s="32">
-        <v>0.35416666666666669</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D104" s="32">
-        <v>0.5</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="E104" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F104" s="34"/>
       <c r="G104" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="H104" s="34" t="s">
-        <v>15</v>
+        <v>91</v>
+      </c>
+      <c r="H104" s="33" t="s">
+        <v>58</v>
       </c>
       <c r="I104" s="34" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="J104" s="34" t="s">
-        <v>144</v>
-      </c>
-      <c r="K104" s="34"/>
+        <v>17</v>
+      </c>
+      <c r="K104" s="34" t="s">
+        <v>143</v>
+      </c>
       <c r="L104" s="34"/>
       <c r="M104" s="34" t="s">
         <v>18</v>
@@ -7312,29 +7315,35 @@
     </row>
     <row r="105" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="30">
-        <v>46366</v>
+        <v>46365</v>
       </c>
       <c r="B105" s="31"/>
-      <c r="C105" s="35"/>
-      <c r="D105" s="35"/>
-      <c r="E105" s="33" t="s">
+      <c r="C105" s="32">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D105" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="E105" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F105" s="34"/>
       <c r="G105" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="H105" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="I105" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="J105" s="34"/>
+        <v>14</v>
+      </c>
+      <c r="H105" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="I105" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="J105" s="34" t="s">
+        <v>144</v>
+      </c>
       <c r="K105" s="34"/>
       <c r="L105" s="34"/>
       <c r="M105" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N105" s="12"/>
       <c r="O105" s="12"/>
@@ -7356,22 +7365,22 @@
     </row>
     <row r="106" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="30">
-        <v>46367</v>
+        <v>46366</v>
       </c>
       <c r="B106" s="31"/>
-      <c r="C106" s="32"/>
-      <c r="D106" s="32"/>
-      <c r="E106" s="34" t="s">
-        <v>56</v>
+      <c r="C106" s="35"/>
+      <c r="D106" s="35"/>
+      <c r="E106" s="33" t="s">
+        <v>13</v>
       </c>
       <c r="F106" s="34"/>
       <c r="G106" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="H106" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="I106" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="H106" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="I106" s="33" t="s">
         <v>63</v>
       </c>
       <c r="J106" s="34"/>
@@ -7400,31 +7409,25 @@
     </row>
     <row r="107" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="30">
-        <v>46368</v>
+        <v>46367</v>
       </c>
       <c r="B107" s="31"/>
-      <c r="C107" s="35">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D107" s="35">
-        <v>0.5</v>
-      </c>
-      <c r="E107" s="33" t="s">
-        <v>13</v>
+      <c r="C107" s="32"/>
+      <c r="D107" s="32"/>
+      <c r="E107" s="34" t="s">
+        <v>56</v>
       </c>
       <c r="F107" s="34"/>
       <c r="G107" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="H107" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="H107" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="I107" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J107" s="34" t="s">
-        <v>66</v>
-      </c>
+      <c r="I107" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="J107" s="34"/>
       <c r="K107" s="34"/>
       <c r="L107" s="34"/>
       <c r="M107" s="34" t="s">
@@ -7450,37 +7453,35 @@
     </row>
     <row r="108" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="30">
-        <v>46372</v>
+        <v>46368</v>
       </c>
       <c r="B108" s="31"/>
-      <c r="C108" s="32">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D108" s="32">
+      <c r="C108" s="35">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D108" s="35">
         <v>0.5</v>
       </c>
-      <c r="E108" s="34" t="s">
-        <v>28</v>
+      <c r="E108" s="33" t="s">
+        <v>13</v>
       </c>
       <c r="F108" s="34"/>
       <c r="G108" s="33" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="H108" s="33" t="s">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="I108" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="J108" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="K108" s="33" t="s">
-        <v>148</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="J108" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="K108" s="34"/>
       <c r="L108" s="34"/>
       <c r="M108" s="34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N108" s="12"/>
       <c r="O108" s="12"/>
@@ -7506,29 +7507,29 @@
       </c>
       <c r="B109" s="31"/>
       <c r="C109" s="32">
-        <v>0.45833333333333331</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D109" s="32">
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="E109" s="34" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F109" s="34"/>
       <c r="G109" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="H109" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="I109" s="34" t="s">
-        <v>63</v>
-      </c>
-      <c r="J109" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="K109" s="34" t="s">
-        <v>151</v>
+        <v>99</v>
+      </c>
+      <c r="H109" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="I109" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="J109" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="K109" s="33" t="s">
+        <v>148</v>
       </c>
       <c r="L109" s="34"/>
       <c r="M109" s="34" t="s">
@@ -7553,36 +7554,36 @@
       <c r="AD109" s="12"/>
     </row>
     <row r="110" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="40">
-        <v>46373</v>
-      </c>
-      <c r="B110" s="41"/>
-      <c r="C110" s="42">
-        <v>0.625</v>
-      </c>
-      <c r="D110" s="42">
-        <v>0.6875</v>
-      </c>
-      <c r="E110" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="F110" s="41"/>
-      <c r="G110" s="41" t="s">
-        <v>75</v>
+      <c r="A110" s="30">
+        <v>46372</v>
+      </c>
+      <c r="B110" s="31"/>
+      <c r="C110" s="32">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D110" s="32">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E110" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F110" s="34"/>
+      <c r="G110" s="33" t="s">
+        <v>149</v>
       </c>
       <c r="H110" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="I110" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="J110" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="K110" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="L110" s="43"/>
+        <v>58</v>
+      </c>
+      <c r="I110" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="J110" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="K110" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="L110" s="34"/>
       <c r="M110" s="34" t="s">
         <v>18</v>
       </c>
@@ -7605,36 +7606,36 @@
       <c r="AD110" s="12"/>
     </row>
     <row r="111" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="30">
-        <v>46400</v>
-      </c>
-      <c r="B111" s="31"/>
-      <c r="C111" s="32">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D111" s="32">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="E111" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="F111" s="34"/>
-      <c r="G111" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="H111" s="33" t="s">
-        <v>20</v>
+      <c r="A111" s="40">
+        <v>46373</v>
+      </c>
+      <c r="B111" s="41"/>
+      <c r="C111" s="42">
+        <v>0.625</v>
+      </c>
+      <c r="D111" s="42">
+        <v>0.6875</v>
+      </c>
+      <c r="E111" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F111" s="41"/>
+      <c r="G111" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="H111" s="34" t="s">
+        <v>50</v>
       </c>
       <c r="I111" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="J111" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="K111" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="L111" s="34"/>
+        <v>35</v>
+      </c>
+      <c r="J111" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="K111" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="L111" s="43"/>
       <c r="M111" s="34" t="s">
         <v>18</v>
       </c>
@@ -7665,25 +7666,27 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D112" s="32">
-        <v>0.5</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="E112" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F112" s="34"/>
       <c r="G112" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="H112" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="I112" s="34" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="H112" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="I112" s="33" t="s">
+        <v>21</v>
       </c>
       <c r="J112" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="K112" s="33"/>
+        <v>72</v>
+      </c>
+      <c r="K112" s="33" t="s">
+        <v>23</v>
+      </c>
       <c r="L112" s="34"/>
       <c r="M112" s="34" t="s">
         <v>18</v>
@@ -7707,36 +7710,34 @@
       <c r="AD112" s="12"/>
     </row>
     <row r="113" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="40">
-        <v>46401</v>
-      </c>
-      <c r="B113" s="41"/>
-      <c r="C113" s="42">
-        <v>0.625</v>
-      </c>
-      <c r="D113" s="42">
-        <v>0.6875</v>
-      </c>
-      <c r="E113" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="F113" s="41"/>
-      <c r="G113" s="41" t="s">
-        <v>75</v>
+      <c r="A113" s="30">
+        <v>46400</v>
+      </c>
+      <c r="B113" s="31"/>
+      <c r="C113" s="32">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D113" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="E113" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F113" s="34"/>
+      <c r="G113" s="33" t="s">
+        <v>14</v>
       </c>
       <c r="H113" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="I113" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="J113" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="K113" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="L113" s="43"/>
+        <v>15</v>
+      </c>
+      <c r="I113" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="J113" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="K113" s="33"/>
+      <c r="L113" s="34"/>
       <c r="M113" s="34" t="s">
         <v>18</v>
       </c>
@@ -7759,32 +7760,36 @@
       <c r="AD113" s="12"/>
     </row>
     <row r="114" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="30">
-        <v>46402</v>
-      </c>
-      <c r="B114" s="31"/>
-      <c r="C114" s="32">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D114" s="32">
-        <v>0.4375</v>
-      </c>
-      <c r="E114" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="F114" s="34"/>
-      <c r="G114" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="H114" s="34"/>
+      <c r="A114" s="40">
+        <v>46401</v>
+      </c>
+      <c r="B114" s="41"/>
+      <c r="C114" s="42">
+        <v>0.625</v>
+      </c>
+      <c r="D114" s="42">
+        <v>0.6875</v>
+      </c>
+      <c r="E114" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F114" s="41"/>
+      <c r="G114" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="H114" s="34" t="s">
+        <v>50</v>
+      </c>
       <c r="I114" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="J114" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K114" s="33"/>
-      <c r="L114" s="34"/>
+        <v>35</v>
+      </c>
+      <c r="J114" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="K114" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="L114" s="43"/>
       <c r="M114" s="34" t="s">
         <v>18</v>
       </c>
@@ -7808,34 +7813,30 @@
     </row>
     <row r="115" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="30">
-        <v>46407</v>
+        <v>46402</v>
       </c>
       <c r="B115" s="31"/>
       <c r="C115" s="32">
-        <v>0.34375</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D115" s="32">
-        <v>0.52083333333333337</v>
+        <v>0.4375</v>
       </c>
       <c r="E115" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F115" s="34"/>
       <c r="G115" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="H115" s="33" t="s">
-        <v>54</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="H115" s="34"/>
       <c r="I115" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="J115" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="K115" s="33" t="s">
-        <v>23</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="J115" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K115" s="33"/>
       <c r="L115" s="34"/>
       <c r="M115" s="34" t="s">
         <v>18</v>
@@ -7864,29 +7865,29 @@
       </c>
       <c r="B116" s="31"/>
       <c r="C116" s="32">
+        <v>0.34375</v>
+      </c>
+      <c r="D116" s="32">
         <v>0.52083333333333337</v>
       </c>
-      <c r="D116" s="32">
-        <v>0.54166666666666663</v>
-      </c>
       <c r="E116" s="34" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F116" s="34"/>
       <c r="G116" s="33" t="s">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="H116" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="I116" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="J116" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K116" s="34" t="s">
-        <v>153</v>
+        <v>54</v>
+      </c>
+      <c r="I116" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="J116" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="K116" s="33" t="s">
+        <v>23</v>
       </c>
       <c r="L116" s="34"/>
       <c r="M116" s="34" t="s">
@@ -7912,35 +7913,37 @@
     </row>
     <row r="117" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="30">
-        <v>46410</v>
+        <v>46407</v>
       </c>
       <c r="B117" s="31"/>
-      <c r="C117" s="35">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D117" s="35">
-        <v>0.5</v>
-      </c>
-      <c r="E117" s="33" t="s">
-        <v>13</v>
+      <c r="C117" s="32">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D117" s="32">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="E117" s="34" t="s">
+        <v>56</v>
       </c>
       <c r="F117" s="34"/>
       <c r="G117" s="33" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="H117" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="I117" s="33" t="s">
-        <v>16</v>
+        <v>58</v>
+      </c>
+      <c r="I117" s="34" t="s">
+        <v>51</v>
       </c>
       <c r="J117" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="K117" s="34"/>
+        <v>17</v>
+      </c>
+      <c r="K117" s="34" t="s">
+        <v>153</v>
+      </c>
       <c r="L117" s="34"/>
       <c r="M117" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N117" s="12"/>
       <c r="O117" s="12"/>
@@ -7966,25 +7969,27 @@
       </c>
       <c r="B118" s="31"/>
       <c r="C118" s="35">
-        <v>0.35416666666666669</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D118" s="35">
-        <v>0.64583333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="E118" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F118" s="34"/>
       <c r="G118" s="33" t="s">
-        <v>154</v>
+        <v>65</v>
       </c>
       <c r="H118" s="33" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="I118" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="J118" s="34"/>
+        <v>16</v>
+      </c>
+      <c r="J118" s="34" t="s">
+        <v>66</v>
+      </c>
       <c r="K118" s="34"/>
       <c r="L118" s="34"/>
       <c r="M118" s="34" t="s">
@@ -8010,27 +8015,33 @@
     </row>
     <row r="119" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="30">
-        <v>46411</v>
+        <v>46410</v>
       </c>
       <c r="B119" s="31"/>
-      <c r="C119" s="32"/>
-      <c r="D119" s="32"/>
-      <c r="E119" s="34" t="s">
+      <c r="C119" s="35">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D119" s="35">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="E119" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F119" s="34"/>
       <c r="G119" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="H119" s="34"/>
-      <c r="I119" s="34" t="s">
-        <v>26</v>
+        <v>154</v>
+      </c>
+      <c r="H119" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="I119" s="33" t="s">
+        <v>97</v>
       </c>
       <c r="J119" s="34"/>
       <c r="K119" s="34"/>
       <c r="L119" s="34"/>
       <c r="M119" s="34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N119" s="12"/>
       <c r="O119" s="12"/>
@@ -8058,22 +8069,18 @@
       <c r="C120" s="32"/>
       <c r="D120" s="32"/>
       <c r="E120" s="34" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F120" s="34"/>
       <c r="G120" s="33" t="s">
-        <v>156</v>
-      </c>
-      <c r="H120" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="I120" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H120" s="34"/>
+      <c r="I120" s="34" t="s">
         <v>26</v>
       </c>
       <c r="J120" s="34"/>
-      <c r="K120" s="33" t="s">
-        <v>157</v>
-      </c>
+      <c r="K120" s="34"/>
       <c r="L120" s="34"/>
       <c r="M120" s="34" t="s">
         <v>18</v>
@@ -8098,33 +8105,27 @@
     </row>
     <row r="121" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="30">
-        <v>46414</v>
+        <v>46411</v>
       </c>
       <c r="B121" s="31"/>
-      <c r="C121" s="32">
-        <v>0.34375</v>
-      </c>
-      <c r="D121" s="32">
-        <v>0.52083333333333337</v>
-      </c>
+      <c r="C121" s="32"/>
+      <c r="D121" s="32"/>
       <c r="E121" s="34" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="F121" s="34"/>
       <c r="G121" s="33" t="s">
-        <v>53</v>
+        <v>156</v>
       </c>
       <c r="H121" s="33" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="I121" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="J121" s="33" t="s">
-        <v>158</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="J121" s="34"/>
       <c r="K121" s="33" t="s">
-        <v>23</v>
+        <v>157</v>
       </c>
       <c r="L121" s="34"/>
       <c r="M121" s="34" t="s">
@@ -8150,33 +8151,37 @@
     </row>
     <row r="122" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="30">
-        <v>46415</v>
+        <v>46414</v>
       </c>
       <c r="B122" s="31"/>
-      <c r="C122" s="35">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D122" s="35">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="E122" s="33" t="s">
+      <c r="C122" s="32">
+        <v>0.34375</v>
+      </c>
+      <c r="D122" s="32">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E122" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F122" s="34"/>
       <c r="G122" s="33" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="H122" s="33" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="I122" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="J122" s="34"/>
-      <c r="K122" s="34"/>
+      <c r="J122" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="K122" s="33" t="s">
+        <v>23</v>
+      </c>
       <c r="L122" s="34"/>
       <c r="M122" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N122" s="12"/>
       <c r="O122" s="12"/>
@@ -8198,29 +8203,33 @@
     </row>
     <row r="123" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="30">
-        <v>46416</v>
+        <v>46415</v>
       </c>
       <c r="B123" s="31"/>
-      <c r="C123" s="35"/>
-      <c r="D123" s="35"/>
+      <c r="C123" s="35">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D123" s="35">
+        <v>0.64583333333333337</v>
+      </c>
       <c r="E123" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F123" s="34"/>
       <c r="G123" s="33" t="s">
-        <v>159</v>
+        <v>102</v>
       </c>
       <c r="H123" s="33" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="I123" s="33" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="J123" s="34"/>
-      <c r="K123" s="33"/>
+      <c r="K123" s="34"/>
       <c r="L123" s="34"/>
       <c r="M123" s="34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N123" s="12"/>
       <c r="O123" s="12"/>
@@ -8242,7 +8251,7 @@
     </row>
     <row r="124" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="30">
-        <v>46417</v>
+        <v>46416</v>
       </c>
       <c r="B124" s="31"/>
       <c r="C124" s="35"/>
@@ -8252,7 +8261,7 @@
       </c>
       <c r="F124" s="34"/>
       <c r="G124" s="33" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H124" s="33" t="s">
         <v>25</v>
@@ -8261,7 +8270,7 @@
         <v>26</v>
       </c>
       <c r="J124" s="34"/>
-      <c r="K124" s="34"/>
+      <c r="K124" s="33"/>
       <c r="L124" s="34"/>
       <c r="M124" s="34" t="s">
         <v>18</v>
@@ -8286,20 +8295,24 @@
     </row>
     <row r="125" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="30">
-        <v>46418</v>
+        <v>46417</v>
       </c>
       <c r="B125" s="31"/>
-      <c r="C125" s="32"/>
-      <c r="D125" s="32"/>
-      <c r="E125" s="34" t="s">
+      <c r="C125" s="35"/>
+      <c r="D125" s="35"/>
+      <c r="E125" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F125" s="34"/>
       <c r="G125" s="33" t="s">
-        <v>161</v>
-      </c>
-      <c r="H125" s="34"/>
-      <c r="I125" s="34"/>
+        <v>160</v>
+      </c>
+      <c r="H125" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="I125" s="33" t="s">
+        <v>26</v>
+      </c>
       <c r="J125" s="34"/>
       <c r="K125" s="34"/>
       <c r="L125" s="34"/>
@@ -8326,33 +8339,25 @@
     </row>
     <row r="126" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="30">
-        <v>46420</v>
+        <v>46418</v>
       </c>
       <c r="B126" s="31"/>
-      <c r="C126" s="32">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D126" s="32">
-        <v>0.6875</v>
-      </c>
+      <c r="C126" s="32"/>
+      <c r="D126" s="32"/>
       <c r="E126" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F126" s="34"/>
       <c r="G126" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="H126" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="I126" s="34" t="s">
-        <v>97</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="H126" s="34"/>
+      <c r="I126" s="34"/>
       <c r="J126" s="34"/>
       <c r="K126" s="34"/>
       <c r="L126" s="34"/>
       <c r="M126" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N126" s="12"/>
       <c r="O126" s="12"/>
@@ -8374,37 +8379,33 @@
     </row>
     <row r="127" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="30">
-        <v>46421</v>
+        <v>46420</v>
       </c>
       <c r="B127" s="31"/>
       <c r="C127" s="32">
-        <v>0.35416666666666669</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D127" s="32">
-        <v>0.52083333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="E127" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F127" s="34"/>
       <c r="G127" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="H127" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="I127" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="J127" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="K127" s="33" t="s">
-        <v>23</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="H127" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="I127" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="J127" s="34"/>
+      <c r="K127" s="34"/>
       <c r="L127" s="34"/>
       <c r="M127" s="34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N127" s="12"/>
       <c r="O127" s="12"/>
@@ -8433,25 +8434,27 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D128" s="32">
-        <v>0.5</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="E128" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F128" s="34"/>
       <c r="G128" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="H128" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="I128" s="34" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="H128" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="I128" s="33" t="s">
+        <v>21</v>
       </c>
       <c r="J128" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="K128" s="33"/>
+        <v>72</v>
+      </c>
+      <c r="K128" s="33" t="s">
+        <v>23</v>
+      </c>
       <c r="L128" s="34"/>
       <c r="M128" s="34" t="s">
         <v>18</v>
@@ -8475,36 +8478,34 @@
       <c r="AD128" s="12"/>
     </row>
     <row r="129" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="40">
-        <v>46422</v>
-      </c>
-      <c r="B129" s="41"/>
-      <c r="C129" s="42">
-        <v>0.625</v>
-      </c>
-      <c r="D129" s="42">
-        <v>0.6875</v>
-      </c>
-      <c r="E129" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="F129" s="41"/>
-      <c r="G129" s="41" t="s">
-        <v>75</v>
+      <c r="A129" s="30">
+        <v>46421</v>
+      </c>
+      <c r="B129" s="31"/>
+      <c r="C129" s="32">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D129" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="E129" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F129" s="34"/>
+      <c r="G129" s="33" t="s">
+        <v>14</v>
       </c>
       <c r="H129" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="I129" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="J129" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="K129" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="L129" s="43"/>
+        <v>15</v>
+      </c>
+      <c r="I129" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="J129" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="K129" s="33"/>
+      <c r="L129" s="34"/>
       <c r="M129" s="34" t="s">
         <v>18</v>
       </c>
@@ -8527,32 +8528,36 @@
       <c r="AD129" s="12"/>
     </row>
     <row r="130" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="30">
-        <v>46423</v>
-      </c>
-      <c r="B130" s="31"/>
-      <c r="C130" s="32">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D130" s="32">
-        <v>0.4375</v>
-      </c>
-      <c r="E130" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="F130" s="34"/>
-      <c r="G130" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="H130" s="34"/>
+      <c r="A130" s="40">
+        <v>46422</v>
+      </c>
+      <c r="B130" s="41"/>
+      <c r="C130" s="42">
+        <v>0.625</v>
+      </c>
+      <c r="D130" s="42">
+        <v>0.6875</v>
+      </c>
+      <c r="E130" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F130" s="41"/>
+      <c r="G130" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="H130" s="34" t="s">
+        <v>50</v>
+      </c>
       <c r="I130" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="J130" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K130" s="33"/>
-      <c r="L130" s="34"/>
+        <v>35</v>
+      </c>
+      <c r="J130" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="K130" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="L130" s="43"/>
       <c r="M130" s="34" t="s">
         <v>18</v>
       </c>
@@ -8580,30 +8585,26 @@
       </c>
       <c r="B131" s="31"/>
       <c r="C131" s="32">
-        <v>0.45833333333333331</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D131" s="32">
-        <v>0.66666666666666663</v>
+        <v>0.4375</v>
       </c>
       <c r="E131" s="34" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F131" s="34"/>
       <c r="G131" s="33" t="s">
-        <v>162</v>
-      </c>
-      <c r="H131" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="I131" s="34" t="s">
-        <v>35</v>
+        <v>49</v>
+      </c>
+      <c r="H131" s="34"/>
+      <c r="I131" s="33" t="s">
+        <v>51</v>
       </c>
       <c r="J131" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="K131" s="34" t="s">
-        <v>163</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="K131" s="33"/>
       <c r="L131" s="34"/>
       <c r="M131" s="34" t="s">
         <v>18</v>
@@ -8628,33 +8629,33 @@
     </row>
     <row r="132" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="30">
-        <v>46428</v>
+        <v>46423</v>
       </c>
       <c r="B132" s="31"/>
       <c r="C132" s="32">
-        <v>0.34375</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D132" s="32">
-        <v>0.52083333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E132" s="34" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="F132" s="34"/>
       <c r="G132" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="H132" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="I132" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="H132" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="I132" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="J132" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="K132" s="33" t="s">
-        <v>23</v>
+      <c r="J132" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="K132" s="34" t="s">
+        <v>163</v>
       </c>
       <c r="L132" s="34"/>
       <c r="M132" s="34" t="s">
@@ -8683,34 +8684,34 @@
         <v>46428</v>
       </c>
       <c r="B133" s="31"/>
-      <c r="C133" s="35">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D133" s="35">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="E133" s="33" t="s">
+      <c r="C133" s="32">
+        <v>0.34375</v>
+      </c>
+      <c r="D133" s="32">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E133" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F133" s="34"/>
       <c r="G133" s="33" t="s">
-        <v>165</v>
+        <v>53</v>
       </c>
       <c r="H133" s="33" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I133" s="33" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="J133" s="33" t="s">
-        <v>48</v>
+        <v>164</v>
       </c>
       <c r="K133" s="33" t="s">
-        <v>166</v>
+        <v>23</v>
       </c>
       <c r="L133" s="34"/>
       <c r="M133" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N133" s="12"/>
       <c r="O133" s="12"/>
@@ -8735,34 +8736,34 @@
         <v>46428</v>
       </c>
       <c r="B134" s="31"/>
-      <c r="C134" s="32">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D134" s="32">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="E134" s="34" t="s">
-        <v>56</v>
+      <c r="C134" s="35">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D134" s="35">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="E134" s="33" t="s">
+        <v>13</v>
       </c>
       <c r="F134" s="34"/>
       <c r="G134" s="33" t="s">
-        <v>91</v>
+        <v>165</v>
       </c>
       <c r="H134" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="I134" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="J134" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K134" s="34" t="s">
-        <v>167</v>
+        <v>46</v>
+      </c>
+      <c r="I134" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="J134" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="K134" s="33" t="s">
+        <v>166</v>
       </c>
       <c r="L134" s="34"/>
       <c r="M134" s="34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N134" s="12"/>
       <c r="O134" s="12"/>
@@ -8784,26 +8785,34 @@
     </row>
     <row r="135" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="30">
-        <v>46430</v>
+        <v>46428</v>
       </c>
       <c r="B135" s="31"/>
-      <c r="C135" s="35"/>
-      <c r="D135" s="35"/>
-      <c r="E135" s="33" t="s">
-        <v>13</v>
+      <c r="C135" s="32">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D135" s="32">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="E135" s="34" t="s">
+        <v>56</v>
       </c>
       <c r="F135" s="34"/>
       <c r="G135" s="33" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="H135" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="I135" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="J135" s="34"/>
-      <c r="K135" s="34"/>
+        <v>58</v>
+      </c>
+      <c r="I135" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="J135" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K135" s="34" t="s">
+        <v>167</v>
+      </c>
       <c r="L135" s="34"/>
       <c r="M135" s="34" t="s">
         <v>18</v>
@@ -8828,34 +8837,26 @@
     </row>
     <row r="136" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="30">
-        <v>46435</v>
+        <v>46430</v>
       </c>
       <c r="B136" s="31"/>
-      <c r="C136" s="32">
-        <v>0.34375</v>
-      </c>
-      <c r="D136" s="32">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="E136" s="34" t="s">
+      <c r="C136" s="35"/>
+      <c r="D136" s="35"/>
+      <c r="E136" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F136" s="34"/>
       <c r="G136" s="33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H136" s="33" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="I136" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="J136" s="33" t="s">
-        <v>168</v>
-      </c>
-      <c r="K136" s="33" t="s">
-        <v>23</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="J136" s="34"/>
+      <c r="K136" s="34"/>
       <c r="L136" s="34"/>
       <c r="M136" s="34" t="s">
         <v>18</v>
@@ -8880,35 +8881,37 @@
     </row>
     <row r="137" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="30">
-        <v>46438</v>
+        <v>46435</v>
       </c>
       <c r="B137" s="31"/>
-      <c r="C137" s="35">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D137" s="35">
-        <v>0.5</v>
-      </c>
-      <c r="E137" s="33" t="s">
+      <c r="C137" s="32">
+        <v>0.34375</v>
+      </c>
+      <c r="D137" s="32">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E137" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F137" s="34"/>
       <c r="G137" s="33" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="H137" s="33" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I137" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J137" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="K137" s="34"/>
+        <v>35</v>
+      </c>
+      <c r="J137" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="K137" s="33" t="s">
+        <v>23</v>
+      </c>
       <c r="L137" s="34"/>
       <c r="M137" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N137" s="12"/>
       <c r="O137" s="12"/>
@@ -8930,37 +8933,35 @@
     </row>
     <row r="138" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="30">
-        <v>46442</v>
+        <v>46438</v>
       </c>
       <c r="B138" s="31"/>
-      <c r="C138" s="32">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D138" s="32">
+      <c r="C138" s="35">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D138" s="35">
         <v>0.5</v>
       </c>
-      <c r="E138" s="34" t="s">
+      <c r="E138" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F138" s="34"/>
       <c r="G138" s="33" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="H138" s="33" t="s">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="I138" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="J138" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="K138" s="33" t="s">
-        <v>23</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="J138" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="K138" s="34"/>
       <c r="L138" s="34"/>
       <c r="M138" s="34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N138" s="12"/>
       <c r="O138" s="12"/>
@@ -8982,33 +8983,37 @@
     </row>
     <row r="139" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="30">
-        <v>46443</v>
+        <v>46442</v>
       </c>
       <c r="B139" s="31"/>
-      <c r="C139" s="35">
+      <c r="C139" s="32">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D139" s="35">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="E139" s="33" t="s">
+      <c r="D139" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="E139" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F139" s="34"/>
       <c r="G139" s="33" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H139" s="33" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="I139" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="J139" s="34"/>
-      <c r="K139" s="34"/>
+      <c r="J139" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="K139" s="33" t="s">
+        <v>23</v>
+      </c>
       <c r="L139" s="34"/>
       <c r="M139" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N139" s="12"/>
       <c r="O139" s="12"/>
@@ -9030,20 +9035,28 @@
     </row>
     <row r="140" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="30">
-        <v>46444</v>
+        <v>46443</v>
       </c>
       <c r="B140" s="31"/>
-      <c r="C140" s="32"/>
-      <c r="D140" s="32"/>
-      <c r="E140" s="34" t="s">
+      <c r="C140" s="35">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D140" s="35">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="E140" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F140" s="34"/>
       <c r="G140" s="33" t="s">
-        <v>170</v>
-      </c>
-      <c r="H140" s="34"/>
-      <c r="I140" s="34"/>
+        <v>102</v>
+      </c>
+      <c r="H140" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="I140" s="33" t="s">
+        <v>35</v>
+      </c>
       <c r="J140" s="34"/>
       <c r="K140" s="34"/>
       <c r="L140" s="34"/>
@@ -9070,29 +9083,25 @@
     </row>
     <row r="141" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="30">
-        <v>46445</v>
+        <v>46444</v>
       </c>
       <c r="B141" s="31"/>
-      <c r="C141" s="35"/>
-      <c r="D141" s="35"/>
-      <c r="E141" s="33" t="s">
+      <c r="C141" s="32"/>
+      <c r="D141" s="32"/>
+      <c r="E141" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F141" s="34"/>
       <c r="G141" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="H141" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="I141" s="33" t="s">
-        <v>26</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="H141" s="34"/>
+      <c r="I141" s="34"/>
       <c r="J141" s="34"/>
       <c r="K141" s="34"/>
       <c r="L141" s="34"/>
       <c r="M141" s="34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N141" s="12"/>
       <c r="O141" s="12"/>
@@ -9114,23 +9123,23 @@
     </row>
     <row r="142" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="30">
-        <v>46447</v>
+        <v>46445</v>
       </c>
       <c r="B142" s="31"/>
-      <c r="C142" s="32"/>
-      <c r="D142" s="32"/>
-      <c r="E142" s="34" t="s">
+      <c r="C142" s="35"/>
+      <c r="D142" s="35"/>
+      <c r="E142" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F142" s="34"/>
       <c r="G142" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="H142" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="H142" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="I142" s="34" t="s">
-        <v>30</v>
+      <c r="I142" s="33" t="s">
+        <v>26</v>
       </c>
       <c r="J142" s="34"/>
       <c r="K142" s="34"/>
@@ -9168,13 +9177,13 @@
       </c>
       <c r="F143" s="34"/>
       <c r="G143" s="33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H143" s="34" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I143" s="34" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J143" s="34"/>
       <c r="K143" s="34"/>
@@ -9208,21 +9217,23 @@
       <c r="C144" s="32"/>
       <c r="D144" s="32"/>
       <c r="E144" s="34" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F144" s="34"/>
       <c r="G144" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="H144" s="34"/>
-      <c r="I144" s="33" t="s">
-        <v>63</v>
+        <v>173</v>
+      </c>
+      <c r="H144" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="I144" s="34" t="s">
+        <v>26</v>
       </c>
       <c r="J144" s="34"/>
       <c r="K144" s="34"/>
       <c r="L144" s="34"/>
       <c r="M144" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N144" s="12"/>
       <c r="O144" s="12"/>
@@ -9244,27 +9255,21 @@
     </row>
     <row r="145" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="30">
-        <v>46448</v>
+        <v>46447</v>
       </c>
       <c r="B145" s="31"/>
-      <c r="C145" s="32">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D145" s="32">
-        <v>0.6875</v>
-      </c>
+      <c r="C145" s="32"/>
+      <c r="D145" s="32"/>
       <c r="E145" s="34" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="F145" s="34"/>
       <c r="G145" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="H145" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="I145" s="34" t="s">
-        <v>97</v>
+        <v>174</v>
+      </c>
+      <c r="H145" s="34"/>
+      <c r="I145" s="33" t="s">
+        <v>63</v>
       </c>
       <c r="J145" s="34"/>
       <c r="K145" s="34"/>
@@ -9292,37 +9297,33 @@
     </row>
     <row r="146" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="30">
-        <v>46449</v>
+        <v>46448</v>
       </c>
       <c r="B146" s="31"/>
       <c r="C146" s="32">
-        <v>0.35416666666666669</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D146" s="32">
-        <v>0.52083333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="E146" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F146" s="34"/>
       <c r="G146" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="H146" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="I146" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="J146" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="K146" s="33" t="s">
-        <v>23</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="H146" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="I146" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="J146" s="34"/>
+      <c r="K146" s="34"/>
       <c r="L146" s="34"/>
       <c r="M146" s="34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N146" s="12"/>
       <c r="O146" s="12"/>
@@ -9344,33 +9345,37 @@
     </row>
     <row r="147" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="30">
-        <v>46450</v>
+        <v>46449</v>
       </c>
       <c r="B147" s="31"/>
-      <c r="C147" s="35">
+      <c r="C147" s="32">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D147" s="35">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="E147" s="33" t="s">
+      <c r="D147" s="32">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E147" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F147" s="34"/>
       <c r="G147" s="33" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="H147" s="33" t="s">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="I147" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="J147" s="34"/>
-      <c r="K147" s="34"/>
+        <v>21</v>
+      </c>
+      <c r="J147" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="K147" s="33" t="s">
+        <v>23</v>
+      </c>
       <c r="L147" s="34"/>
       <c r="M147" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N147" s="12"/>
       <c r="O147" s="12"/>
@@ -9395,20 +9400,24 @@
         <v>46450</v>
       </c>
       <c r="B148" s="31"/>
-      <c r="C148" s="32"/>
-      <c r="D148" s="32"/>
-      <c r="E148" s="34" t="s">
+      <c r="C148" s="35">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D148" s="35">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="E148" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F148" s="34"/>
       <c r="G148" s="33" t="s">
-        <v>175</v>
-      </c>
-      <c r="H148" s="34" t="s">
-        <v>25</v>
+        <v>88</v>
+      </c>
+      <c r="H148" s="33" t="s">
+        <v>89</v>
       </c>
       <c r="I148" s="33" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="J148" s="34"/>
       <c r="K148" s="34"/>
@@ -9439,14 +9448,14 @@
         <v>46450</v>
       </c>
       <c r="B149" s="31"/>
-      <c r="C149" s="35"/>
-      <c r="D149" s="35"/>
-      <c r="E149" s="33" t="s">
+      <c r="C149" s="32"/>
+      <c r="D149" s="32"/>
+      <c r="E149" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F149" s="34"/>
       <c r="G149" s="33" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H149" s="34" t="s">
         <v>25</v>
@@ -9455,9 +9464,7 @@
         <v>63</v>
       </c>
       <c r="J149" s="34"/>
-      <c r="K149" s="33" t="s">
-        <v>177</v>
-      </c>
+      <c r="K149" s="34"/>
       <c r="L149" s="34"/>
       <c r="M149" s="34" t="s">
         <v>32</v>
@@ -9481,38 +9488,32 @@
       <c r="AD149" s="12"/>
     </row>
     <row r="150" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A150" s="40">
+      <c r="A150" s="30">
         <v>46450</v>
       </c>
-      <c r="B150" s="41"/>
-      <c r="C150" s="42">
-        <v>0.625</v>
-      </c>
-      <c r="D150" s="42">
-        <v>0.6875</v>
-      </c>
-      <c r="E150" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="F150" s="41"/>
-      <c r="G150" s="41" t="s">
-        <v>75</v>
+      <c r="B150" s="31"/>
+      <c r="C150" s="35"/>
+      <c r="D150" s="35"/>
+      <c r="E150" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F150" s="34"/>
+      <c r="G150" s="33" t="s">
+        <v>176</v>
       </c>
       <c r="H150" s="34" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I150" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="J150" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="K150" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="L150" s="43"/>
+        <v>63</v>
+      </c>
+      <c r="J150" s="34"/>
+      <c r="K150" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="L150" s="34"/>
       <c r="M150" s="34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N150" s="12"/>
       <c r="O150" s="12"/>
@@ -9533,34 +9534,38 @@
       <c r="AD150" s="12"/>
     </row>
     <row r="151" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="30">
-        <v>46452</v>
-      </c>
-      <c r="B151" s="31"/>
-      <c r="C151" s="35">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D151" s="35">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="E151" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="F151" s="34"/>
-      <c r="G151" s="33" t="s">
-        <v>178</v>
+      <c r="A151" s="40">
+        <v>46450</v>
+      </c>
+      <c r="B151" s="41"/>
+      <c r="C151" s="42">
+        <v>0.625</v>
+      </c>
+      <c r="D151" s="42">
+        <v>0.6875</v>
+      </c>
+      <c r="E151" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F151" s="41"/>
+      <c r="G151" s="41" t="s">
+        <v>75</v>
       </c>
       <c r="H151" s="34" t="s">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="I151" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="J151" s="34"/>
-      <c r="K151" s="34"/>
-      <c r="L151" s="34"/>
+        <v>35</v>
+      </c>
+      <c r="J151" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="K151" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="L151" s="43"/>
       <c r="M151" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N151" s="12"/>
       <c r="O151" s="12"/>
@@ -9582,99 +9587,95 @@
     </row>
     <row r="152" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="30">
-        <v>46454</v>
+        <v>46452</v>
       </c>
       <c r="B152" s="31"/>
-      <c r="C152" s="32"/>
-      <c r="D152" s="32"/>
-      <c r="E152" s="34" t="s">
+      <c r="C152" s="35">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D152" s="35">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="E152" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F152" s="34"/>
       <c r="G152" s="33" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H152" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="I152" s="34" t="s">
-        <v>16</v>
+        <v>89</v>
+      </c>
+      <c r="I152" s="33" t="s">
+        <v>97</v>
       </c>
       <c r="J152" s="34"/>
       <c r="K152" s="34"/>
       <c r="L152" s="34"/>
       <c r="M152" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="N152" s="24"/>
-      <c r="O152" s="24"/>
-      <c r="P152" s="24"/>
-      <c r="Q152" s="24"/>
-      <c r="R152" s="24"/>
-      <c r="S152" s="24"/>
-      <c r="T152" s="24"/>
-      <c r="U152" s="24"/>
-      <c r="V152" s="24"/>
-      <c r="W152" s="24"/>
-      <c r="X152" s="24"/>
-      <c r="Y152" s="24"/>
-      <c r="Z152" s="24"/>
-      <c r="AA152" s="24"/>
-      <c r="AB152" s="24"/>
-      <c r="AC152" s="24"/>
-      <c r="AD152" s="24"/>
+        <v>32</v>
+      </c>
+      <c r="N152" s="12"/>
+      <c r="O152" s="12"/>
+      <c r="P152" s="12"/>
+      <c r="Q152" s="12"/>
+      <c r="R152" s="12"/>
+      <c r="S152" s="12"/>
+      <c r="T152" s="12"/>
+      <c r="U152" s="12"/>
+      <c r="V152" s="12"/>
+      <c r="W152" s="12"/>
+      <c r="X152" s="12"/>
+      <c r="Y152" s="12"/>
+      <c r="Z152" s="12"/>
+      <c r="AA152" s="12"/>
+      <c r="AB152" s="12"/>
+      <c r="AC152" s="12"/>
+      <c r="AD152" s="12"/>
     </row>
     <row r="153" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="30">
-        <v>46456</v>
+        <v>46454</v>
       </c>
       <c r="B153" s="31"/>
-      <c r="C153" s="32">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D153" s="32">
-        <v>0.54166666666666663</v>
-      </c>
+      <c r="C153" s="32"/>
+      <c r="D153" s="32"/>
       <c r="E153" s="34" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F153" s="34"/>
       <c r="G153" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="H153" s="33" t="s">
-        <v>58</v>
+        <v>179</v>
+      </c>
+      <c r="H153" s="34" t="s">
+        <v>20</v>
       </c>
       <c r="I153" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="J153" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K153" s="34" t="s">
-        <v>180</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="J153" s="34"/>
+      <c r="K153" s="34"/>
       <c r="L153" s="34"/>
       <c r="M153" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="N153" s="12"/>
-      <c r="O153" s="12"/>
-      <c r="P153" s="12"/>
-      <c r="Q153" s="12"/>
-      <c r="R153" s="12"/>
-      <c r="S153" s="12"/>
-      <c r="T153" s="12"/>
-      <c r="U153" s="12"/>
-      <c r="V153" s="12"/>
-      <c r="W153" s="12"/>
-      <c r="X153" s="12"/>
-      <c r="Y153" s="12"/>
-      <c r="Z153" s="12"/>
-      <c r="AA153" s="12"/>
-      <c r="AB153" s="12"/>
-      <c r="AC153" s="12"/>
-      <c r="AD153" s="12"/>
+      <c r="N153" s="24"/>
+      <c r="O153" s="24"/>
+      <c r="P153" s="24"/>
+      <c r="Q153" s="24"/>
+      <c r="R153" s="24"/>
+      <c r="S153" s="24"/>
+      <c r="T153" s="24"/>
+      <c r="U153" s="24"/>
+      <c r="V153" s="24"/>
+      <c r="W153" s="24"/>
+      <c r="X153" s="24"/>
+      <c r="Y153" s="24"/>
+      <c r="Z153" s="24"/>
+      <c r="AA153" s="24"/>
+      <c r="AB153" s="24"/>
+      <c r="AC153" s="24"/>
+      <c r="AD153" s="24"/>
     </row>
     <row r="154" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="30">
@@ -9682,29 +9683,29 @@
       </c>
       <c r="B154" s="31"/>
       <c r="C154" s="32">
-        <v>0.35416666666666669</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D154" s="32">
-        <v>0.5</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="E154" s="34" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="F154" s="34"/>
       <c r="G154" s="33" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="H154" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="I154" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="J154" s="33" t="s">
-        <v>181</v>
-      </c>
-      <c r="K154" s="33" t="s">
-        <v>23</v>
+        <v>58</v>
+      </c>
+      <c r="I154" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J154" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K154" s="34" t="s">
+        <v>180</v>
       </c>
       <c r="L154" s="34"/>
       <c r="M154" s="34" t="s">
@@ -9730,29 +9731,37 @@
     </row>
     <row r="155" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="30">
-        <v>46457</v>
+        <v>46456</v>
       </c>
       <c r="B155" s="31"/>
-      <c r="C155" s="32"/>
-      <c r="D155" s="32"/>
+      <c r="C155" s="32">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D155" s="32">
+        <v>0.5</v>
+      </c>
       <c r="E155" s="34" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F155" s="34"/>
       <c r="G155" s="33" t="s">
-        <v>182</v>
-      </c>
-      <c r="H155" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="I155" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="J155" s="34"/>
-      <c r="K155" s="34"/>
+        <v>99</v>
+      </c>
+      <c r="H155" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="I155" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="J155" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="K155" s="33" t="s">
+        <v>23</v>
+      </c>
       <c r="L155" s="34"/>
       <c r="M155" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N155" s="12"/>
       <c r="O155" s="12"/>
@@ -9774,35 +9783,29 @@
     </row>
     <row r="156" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="30">
-        <v>46458</v>
+        <v>46457</v>
       </c>
       <c r="B156" s="31"/>
-      <c r="C156" s="32">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D156" s="32">
-        <v>0.5</v>
-      </c>
+      <c r="C156" s="32"/>
+      <c r="D156" s="32"/>
       <c r="E156" s="34" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="F156" s="34"/>
       <c r="G156" s="33" t="s">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="H156" s="34" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="I156" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="J156" s="33" t="s">
-        <v>48</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="J156" s="34"/>
       <c r="K156" s="34"/>
       <c r="L156" s="34"/>
       <c r="M156" s="34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N156" s="12"/>
       <c r="O156" s="12"/>
@@ -9831,27 +9834,25 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D157" s="32">
-        <v>0.4375</v>
+        <v>0.5</v>
       </c>
       <c r="E157" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F157" s="34"/>
       <c r="G157" s="33" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="H157" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="I157" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="J157" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K157" s="33" t="s">
-        <v>82</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I157" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="J157" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="K157" s="34"/>
       <c r="L157" s="34"/>
       <c r="M157" s="34" t="s">
         <v>18</v>
@@ -9876,35 +9877,37 @@
     </row>
     <row r="158" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="30">
-        <v>46459</v>
+        <v>46458</v>
       </c>
       <c r="B158" s="31"/>
-      <c r="C158" s="35">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D158" s="35">
-        <v>0.5</v>
-      </c>
-      <c r="E158" s="33" t="s">
+      <c r="C158" s="32">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D158" s="32">
+        <v>0.4375</v>
+      </c>
+      <c r="E158" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F158" s="34"/>
       <c r="G158" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="H158" s="33" t="s">
-        <v>46</v>
+        <v>49</v>
+      </c>
+      <c r="H158" s="34" t="s">
+        <v>25</v>
       </c>
       <c r="I158" s="33" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="J158" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="K158" s="34"/>
+        <v>17</v>
+      </c>
+      <c r="K158" s="33" t="s">
+        <v>82</v>
+      </c>
       <c r="L158" s="34"/>
       <c r="M158" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N158" s="12"/>
       <c r="O158" s="12"/>
@@ -9926,27 +9929,31 @@
     </row>
     <row r="159" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="30">
-        <v>46460</v>
-      </c>
-      <c r="B159" s="36">
-        <v>46462</v>
-      </c>
-      <c r="C159" s="32"/>
-      <c r="D159" s="32"/>
-      <c r="E159" s="34" t="s">
+        <v>46459</v>
+      </c>
+      <c r="B159" s="31"/>
+      <c r="C159" s="35">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D159" s="35">
+        <v>0.5</v>
+      </c>
+      <c r="E159" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F159" s="34"/>
       <c r="G159" s="33" t="s">
-        <v>183</v>
-      </c>
-      <c r="H159" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="I159" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="H159" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="I159" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="J159" s="34"/>
+      <c r="J159" s="34" t="s">
+        <v>66</v>
+      </c>
       <c r="K159" s="34"/>
       <c r="L159" s="34"/>
       <c r="M159" s="34" t="s">
@@ -9972,37 +9979,31 @@
     </row>
     <row r="160" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="30">
-        <v>46463</v>
-      </c>
-      <c r="B160" s="31"/>
-      <c r="C160" s="32">
-        <v>0.34375</v>
-      </c>
-      <c r="D160" s="32">
-        <v>0.52083333333333337</v>
-      </c>
+        <v>46460</v>
+      </c>
+      <c r="B160" s="36">
+        <v>46462</v>
+      </c>
+      <c r="C160" s="32"/>
+      <c r="D160" s="32"/>
       <c r="E160" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F160" s="34"/>
       <c r="G160" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="H160" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="I160" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="J160" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="K160" s="33" t="s">
-        <v>23</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="H160" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="I160" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="J160" s="34"/>
+      <c r="K160" s="34"/>
       <c r="L160" s="34"/>
       <c r="M160" s="34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N160" s="12"/>
       <c r="O160" s="12"/>
@@ -10024,33 +10025,37 @@
     </row>
     <row r="161" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="30">
-        <v>46464</v>
+        <v>46463</v>
       </c>
       <c r="B161" s="31"/>
-      <c r="C161" s="35">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D161" s="35">
-        <v>0.64583333333333337</v>
+      <c r="C161" s="32">
+        <v>0.34375</v>
+      </c>
+      <c r="D161" s="32">
+        <v>0.52083333333333337</v>
       </c>
       <c r="E161" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F161" s="34"/>
       <c r="G161" s="33" t="s">
-        <v>102</v>
-      </c>
-      <c r="H161" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="I161" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="H161" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="I161" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="J161" s="34"/>
-      <c r="K161" s="34"/>
+      <c r="J161" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="K161" s="33" t="s">
+        <v>23</v>
+      </c>
       <c r="L161" s="34"/>
       <c r="M161" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N161" s="12"/>
       <c r="O161" s="12"/>
@@ -10075,28 +10080,28 @@
         <v>46464</v>
       </c>
       <c r="B162" s="31"/>
-      <c r="C162" s="32">
-        <v>0.375</v>
-      </c>
-      <c r="D162" s="32">
-        <v>0.625</v>
+      <c r="C162" s="35">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D162" s="35">
+        <v>0.64583333333333337</v>
       </c>
       <c r="E162" s="34" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F162" s="34"/>
       <c r="G162" s="33" t="s">
-        <v>184</v>
-      </c>
-      <c r="H162" s="34"/>
+        <v>102</v>
+      </c>
+      <c r="H162" s="34" t="s">
+        <v>41</v>
+      </c>
       <c r="I162" s="34" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="J162" s="34"/>
-      <c r="K162" s="33"/>
-      <c r="L162" s="34" t="s">
-        <v>32</v>
-      </c>
+      <c r="K162" s="34"/>
+      <c r="L162" s="34"/>
       <c r="M162" s="34" t="s">
         <v>32</v>
       </c>
@@ -10120,25 +10125,31 @@
     </row>
     <row r="163" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="30">
-        <v>46468</v>
-      </c>
-      <c r="B163" s="31">
-        <v>46472</v>
-      </c>
-      <c r="C163" s="32"/>
-      <c r="D163" s="32"/>
+        <v>46464</v>
+      </c>
+      <c r="B163" s="31"/>
+      <c r="C163" s="32">
+        <v>0.375</v>
+      </c>
+      <c r="D163" s="32">
+        <v>0.625</v>
+      </c>
       <c r="E163" s="34" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="F163" s="34"/>
       <c r="G163" s="33" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H163" s="34"/>
-      <c r="I163" s="34"/>
+      <c r="I163" s="34" t="s">
+        <v>51</v>
+      </c>
       <c r="J163" s="34"/>
       <c r="K163" s="33"/>
-      <c r="L163" s="34"/>
+      <c r="L163" s="34" t="s">
+        <v>32</v>
+      </c>
       <c r="M163" s="34" t="s">
         <v>32</v>
       </c>
@@ -10162,32 +10173,24 @@
     </row>
     <row r="164" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="30">
-        <v>46475</v>
-      </c>
-      <c r="B164" s="36" t="s">
-        <v>186</v>
-      </c>
-      <c r="C164" s="32">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D164" s="32">
-        <v>0.6875</v>
-      </c>
+        <v>46468</v>
+      </c>
+      <c r="B164" s="31">
+        <v>46472</v>
+      </c>
+      <c r="C164" s="32"/>
+      <c r="D164" s="32"/>
       <c r="E164" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F164" s="34"/>
       <c r="G164" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="H164" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="I164" s="34" t="s">
-        <v>97</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="H164" s="34"/>
+      <c r="I164" s="34"/>
       <c r="J164" s="34"/>
-      <c r="K164" s="34"/>
+      <c r="K164" s="33"/>
       <c r="L164" s="34"/>
       <c r="M164" s="34" t="s">
         <v>32</v>
@@ -10212,33 +10215,35 @@
     </row>
     <row r="165" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="30">
-        <v>46479</v>
-      </c>
-      <c r="B165" s="31"/>
+        <v>46475</v>
+      </c>
+      <c r="B165" s="36" t="s">
+        <v>186</v>
+      </c>
       <c r="C165" s="32">
-        <v>0.35416666666666669</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D165" s="32">
-        <v>0.4375</v>
+        <v>0.6875</v>
       </c>
       <c r="E165" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F165" s="34"/>
       <c r="G165" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="H165" s="34"/>
-      <c r="I165" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="J165" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K165" s="33"/>
+        <v>142</v>
+      </c>
+      <c r="H165" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="I165" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="J165" s="34"/>
+      <c r="K165" s="34"/>
       <c r="L165" s="34"/>
       <c r="M165" s="34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N165" s="12"/>
       <c r="O165" s="12"/>
@@ -10260,34 +10265,30 @@
     </row>
     <row r="166" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="30">
-        <v>46484</v>
+        <v>46479</v>
       </c>
       <c r="B166" s="31"/>
       <c r="C166" s="32">
         <v>0.35416666666666669</v>
       </c>
       <c r="D166" s="32">
-        <v>0.52083333333333337</v>
+        <v>0.4375</v>
       </c>
       <c r="E166" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F166" s="34"/>
       <c r="G166" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="H166" s="33" t="s">
-        <v>20</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="H166" s="34"/>
       <c r="I166" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="J166" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="K166" s="33" t="s">
-        <v>23</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="J166" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K166" s="33"/>
       <c r="L166" s="34"/>
       <c r="M166" s="34" t="s">
         <v>18</v>
@@ -10316,29 +10317,29 @@
       </c>
       <c r="B167" s="31"/>
       <c r="C167" s="32">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D167" s="32">
         <v>0.52083333333333337</v>
       </c>
-      <c r="D167" s="32">
-        <v>0.54166666666666663</v>
-      </c>
       <c r="E167" s="34" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F167" s="34"/>
       <c r="G167" s="33" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="H167" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="I167" s="34" t="s">
-        <v>187</v>
-      </c>
-      <c r="J167" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K167" s="34" t="s">
-        <v>188</v>
+        <v>20</v>
+      </c>
+      <c r="I167" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="J167" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="K167" s="33" t="s">
+        <v>23</v>
       </c>
       <c r="L167" s="34"/>
       <c r="M167" s="34" t="s">
@@ -10366,32 +10367,36 @@
       <c r="A168" s="30">
         <v>46484</v>
       </c>
-      <c r="B168" s="47"/>
+      <c r="B168" s="31"/>
       <c r="C168" s="32">
-        <v>0.35416666666666669</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D168" s="32">
-        <v>0.5</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="E168" s="34" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="F168" s="34"/>
       <c r="G168" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="H168" s="34" t="s">
-        <v>15</v>
+        <v>91</v>
+      </c>
+      <c r="H168" s="33" t="s">
+        <v>58</v>
       </c>
       <c r="I168" s="34" t="s">
-        <v>16</v>
+        <v>187</v>
       </c>
       <c r="J168" s="34" t="s">
-        <v>144</v>
-      </c>
-      <c r="K168" s="34"/>
+        <v>17</v>
+      </c>
+      <c r="K168" s="34" t="s">
+        <v>188</v>
+      </c>
       <c r="L168" s="34"/>
-      <c r="M168" s="34"/>
+      <c r="M168" s="34" t="s">
+        <v>18</v>
+      </c>
       <c r="N168" s="12"/>
       <c r="O168" s="12"/>
       <c r="P168" s="12"/>
@@ -10412,32 +10417,34 @@
     </row>
     <row r="169" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="30">
-        <v>46485</v>
-      </c>
-      <c r="B169" s="31"/>
-      <c r="C169" s="35"/>
-      <c r="D169" s="35"/>
-      <c r="E169" s="33" t="s">
-        <v>56</v>
+        <v>46484</v>
+      </c>
+      <c r="B169" s="47"/>
+      <c r="C169" s="32">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D169" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="E169" s="34" t="s">
+        <v>13</v>
       </c>
       <c r="F169" s="34"/>
       <c r="G169" s="33" t="s">
-        <v>189</v>
+        <v>14</v>
       </c>
       <c r="H169" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="I169" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="J169" s="34"/>
-      <c r="K169" s="33" t="s">
-        <v>129</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I169" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="J169" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="K169" s="34"/>
       <c r="L169" s="34"/>
-      <c r="M169" s="34" t="s">
-        <v>32</v>
-      </c>
+      <c r="M169" s="34"/>
       <c r="N169" s="12"/>
       <c r="O169" s="12"/>
       <c r="P169" s="12"/>
@@ -10458,37 +10465,31 @@
     </row>
     <row r="170" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="30">
-        <v>46491</v>
+        <v>46485</v>
       </c>
       <c r="B170" s="31"/>
-      <c r="C170" s="32">
-        <v>0.34375</v>
-      </c>
-      <c r="D170" s="32">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="E170" s="34" t="s">
-        <v>13</v>
+      <c r="C170" s="35"/>
+      <c r="D170" s="35"/>
+      <c r="E170" s="33" t="s">
+        <v>56</v>
       </c>
       <c r="F170" s="34"/>
       <c r="G170" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="H170" s="33" t="s">
-        <v>54</v>
+        <v>189</v>
+      </c>
+      <c r="H170" s="34" t="s">
+        <v>46</v>
       </c>
       <c r="I170" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="J170" s="33" t="s">
-        <v>190</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="J170" s="34"/>
       <c r="K170" s="33" t="s">
-        <v>23</v>
+        <v>129</v>
       </c>
       <c r="L170" s="34"/>
       <c r="M170" s="34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N170" s="12"/>
       <c r="O170" s="12"/>
@@ -10509,36 +10510,36 @@
       <c r="AD170" s="12"/>
     </row>
     <row r="171" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="40">
-        <v>46492</v>
-      </c>
-      <c r="B171" s="41"/>
-      <c r="C171" s="42">
-        <v>0.625</v>
-      </c>
-      <c r="D171" s="42">
-        <v>0.6875</v>
-      </c>
-      <c r="E171" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="F171" s="41"/>
-      <c r="G171" s="41" t="s">
-        <v>75</v>
-      </c>
-      <c r="H171" s="34" t="s">
-        <v>50</v>
+      <c r="A171" s="30">
+        <v>46491</v>
+      </c>
+      <c r="B171" s="31"/>
+      <c r="C171" s="32">
+        <v>0.34375</v>
+      </c>
+      <c r="D171" s="32">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E171" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F171" s="34"/>
+      <c r="G171" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="H171" s="33" t="s">
+        <v>54</v>
       </c>
       <c r="I171" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="J171" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="K171" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="L171" s="43"/>
+      <c r="J171" s="33" t="s">
+        <v>190</v>
+      </c>
+      <c r="K171" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="L171" s="34"/>
       <c r="M171" s="34" t="s">
         <v>18</v>
       </c>
@@ -10561,24 +10562,36 @@
       <c r="AD171" s="12"/>
     </row>
     <row r="172" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="30">
-        <v>46493</v>
-      </c>
-      <c r="B172" s="31"/>
-      <c r="C172" s="32"/>
-      <c r="D172" s="32"/>
-      <c r="E172" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="F172" s="34"/>
-      <c r="G172" s="33" t="s">
-        <v>191</v>
-      </c>
-      <c r="H172" s="34"/>
-      <c r="I172" s="34"/>
-      <c r="J172" s="34"/>
-      <c r="K172" s="34"/>
-      <c r="L172" s="34"/>
+      <c r="A172" s="40">
+        <v>46492</v>
+      </c>
+      <c r="B172" s="41"/>
+      <c r="C172" s="42">
+        <v>0.625</v>
+      </c>
+      <c r="D172" s="42">
+        <v>0.6875</v>
+      </c>
+      <c r="E172" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F172" s="41"/>
+      <c r="G172" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="H172" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="I172" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="J172" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="K172" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="L172" s="43"/>
       <c r="M172" s="34" t="s">
         <v>18</v>
       </c>
@@ -10612,19 +10625,15 @@
       </c>
       <c r="F173" s="34"/>
       <c r="G173" s="33" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H173" s="34"/>
-      <c r="I173" s="33" t="s">
-        <v>63</v>
-      </c>
+      <c r="I173" s="34"/>
       <c r="J173" s="34"/>
-      <c r="K173" s="33" t="s">
-        <v>193</v>
-      </c>
+      <c r="K173" s="34"/>
       <c r="L173" s="34"/>
       <c r="M173" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="N173" s="12"/>
       <c r="O173" s="12"/>
@@ -10646,32 +10655,26 @@
     </row>
     <row r="174" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="30">
-        <v>46494</v>
+        <v>46493</v>
       </c>
       <c r="B174" s="31"/>
-      <c r="C174" s="35">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D174" s="35">
-        <v>0.5</v>
-      </c>
-      <c r="E174" s="33" t="s">
-        <v>13</v>
+      <c r="C174" s="32"/>
+      <c r="D174" s="32"/>
+      <c r="E174" s="34" t="s">
+        <v>56</v>
       </c>
       <c r="F174" s="34"/>
       <c r="G174" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="H174" s="33" t="s">
-        <v>46</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="H174" s="34"/>
       <c r="I174" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J174" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="K174" s="34"/>
+        <v>63</v>
+      </c>
+      <c r="J174" s="34"/>
+      <c r="K174" s="33" t="s">
+        <v>193</v>
+      </c>
       <c r="L174" s="34"/>
       <c r="M174" s="34" t="s">
         <v>32</v>
@@ -10696,37 +10699,35 @@
     </row>
     <row r="175" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="30">
-        <v>46498</v>
+        <v>46494</v>
       </c>
       <c r="B175" s="31"/>
-      <c r="C175" s="32">
-        <v>0.34375</v>
-      </c>
-      <c r="D175" s="32">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="E175" s="34" t="s">
+      <c r="C175" s="35">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D175" s="35">
+        <v>0.5</v>
+      </c>
+      <c r="E175" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F175" s="34"/>
       <c r="G175" s="33" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="H175" s="33" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I175" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="J175" s="33" t="s">
-        <v>194</v>
-      </c>
-      <c r="K175" s="33" t="s">
-        <v>23</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="J175" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="K175" s="34"/>
       <c r="L175" s="34"/>
       <c r="M175" s="34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N175" s="12"/>
       <c r="O175" s="12"/>
@@ -10751,30 +10752,30 @@
         <v>46498</v>
       </c>
       <c r="B176" s="31"/>
-      <c r="C176" s="35">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D176" s="35">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="E176" s="33" t="s">
+      <c r="C176" s="32">
+        <v>0.34375</v>
+      </c>
+      <c r="D176" s="32">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E176" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F176" s="34"/>
       <c r="G176" s="33" t="s">
-        <v>195</v>
+        <v>53</v>
       </c>
       <c r="H176" s="33" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I176" s="33" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="J176" s="33" t="s">
-        <v>48</v>
+        <v>194</v>
       </c>
       <c r="K176" s="33" t="s">
-        <v>196</v>
+        <v>23</v>
       </c>
       <c r="L176" s="34"/>
       <c r="M176" s="34" t="s">
@@ -10800,24 +10801,34 @@
     </row>
     <row r="177" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="30">
-        <v>46499</v>
+        <v>46498</v>
       </c>
       <c r="B177" s="31"/>
-      <c r="C177" s="32"/>
-      <c r="D177" s="32"/>
-      <c r="E177" s="34" t="s">
+      <c r="C177" s="35">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D177" s="35">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="E177" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F177" s="34"/>
       <c r="G177" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="H177" s="34"/>
-      <c r="I177" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="J177" s="34"/>
-      <c r="K177" s="34"/>
+        <v>195</v>
+      </c>
+      <c r="H177" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="I177" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="J177" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="K177" s="33" t="s">
+        <v>196</v>
+      </c>
       <c r="L177" s="34"/>
       <c r="M177" s="34" t="s">
         <v>18</v>
@@ -10840,40 +10851,51 @@
       <c r="AC177" s="12"/>
       <c r="AD177" s="12"/>
     </row>
-    <row r="178" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="30">
         <v>46499</v>
       </c>
       <c r="B178" s="31"/>
-      <c r="C178" s="35">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D178" s="35">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="E178" s="33" t="s">
+      <c r="C178" s="32"/>
+      <c r="D178" s="32"/>
+      <c r="E178" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F178" s="34"/>
       <c r="G178" s="33" t="s">
-        <v>102</v>
-      </c>
-      <c r="H178" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="I178" s="33" t="s">
-        <v>35</v>
+        <v>197</v>
+      </c>
+      <c r="H178" s="34"/>
+      <c r="I178" s="34" t="s">
+        <v>26</v>
       </c>
       <c r="J178" s="34"/>
       <c r="K178" s="34"/>
       <c r="L178" s="34"/>
       <c r="M178" s="34" t="s">
-        <v>32</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="N178" s="12"/>
+      <c r="O178" s="12"/>
+      <c r="P178" s="12"/>
+      <c r="Q178" s="12"/>
+      <c r="R178" s="12"/>
+      <c r="S178" s="12"/>
+      <c r="T178" s="12"/>
+      <c r="U178" s="12"/>
+      <c r="V178" s="12"/>
+      <c r="W178" s="12"/>
+      <c r="X178" s="12"/>
+      <c r="Y178" s="12"/>
+      <c r="Z178" s="12"/>
+      <c r="AA178" s="12"/>
+      <c r="AB178" s="12"/>
+      <c r="AC178" s="12"/>
+      <c r="AD178" s="12"/>
     </row>
     <row r="179" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A179" s="30">
-        <v>46498</v>
+        <v>46499</v>
       </c>
       <c r="B179" s="31"/>
       <c r="C179" s="35">
@@ -10886,18 +10908,16 @@
         <v>13</v>
       </c>
       <c r="F179" s="34"/>
-      <c r="G179" s="19" t="s">
-        <v>337</v>
+      <c r="G179" s="33" t="s">
+        <v>102</v>
       </c>
       <c r="H179" s="33" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I179" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="J179" s="15" t="s">
-        <v>338</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="J179" s="34"/>
       <c r="K179" s="34"/>
       <c r="L179" s="34"/>
       <c r="M179" s="34" t="s">
@@ -10906,56 +10926,62 @@
     </row>
     <row r="180" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A180" s="30">
-        <v>46500</v>
+        <v>46498</v>
       </c>
       <c r="B180" s="31"/>
-      <c r="C180" s="32">
+      <c r="C180" s="35">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D180" s="32">
-        <v>0.4375</v>
-      </c>
-      <c r="E180" s="34" t="s">
+      <c r="D180" s="35">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="E180" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F180" s="34"/>
-      <c r="G180" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="H180" s="34"/>
+      <c r="G180" s="19" t="s">
+        <v>337</v>
+      </c>
+      <c r="H180" s="33" t="s">
+        <v>46</v>
+      </c>
       <c r="I180" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="J180" s="34" t="s">
-        <v>17</v>
+        <v>97</v>
+      </c>
+      <c r="J180" s="15" t="s">
+        <v>338</v>
       </c>
       <c r="K180" s="34"/>
       <c r="L180" s="34"/>
       <c r="M180" s="34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="181" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A181" s="30">
-        <v>46501</v>
+        <v>46500</v>
       </c>
       <c r="B181" s="31"/>
-      <c r="C181" s="32"/>
-      <c r="D181" s="32"/>
+      <c r="C181" s="32">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D181" s="32">
+        <v>0.4375</v>
+      </c>
       <c r="E181" s="34" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F181" s="34"/>
       <c r="G181" s="33" t="s">
-        <v>199</v>
-      </c>
-      <c r="H181" s="33" t="s">
-        <v>25</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="H181" s="34"/>
       <c r="I181" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="J181" s="34"/>
+        <v>51</v>
+      </c>
+      <c r="J181" s="34" t="s">
+        <v>17</v>
+      </c>
       <c r="K181" s="34"/>
       <c r="L181" s="34"/>
       <c r="M181" s="34" t="s">
@@ -10967,85 +10993,89 @@
         <v>46501</v>
       </c>
       <c r="B182" s="31"/>
-      <c r="C182" s="35">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D182" s="35">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="E182" s="33" t="s">
-        <v>13</v>
+      <c r="C182" s="32"/>
+      <c r="D182" s="32"/>
+      <c r="E182" s="34" t="s">
+        <v>56</v>
       </c>
       <c r="F182" s="34"/>
       <c r="G182" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="H182" s="34" t="s">
-        <v>89</v>
+        <v>199</v>
+      </c>
+      <c r="H182" s="33" t="s">
+        <v>25</v>
       </c>
       <c r="I182" s="33" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="J182" s="34"/>
       <c r="K182" s="34"/>
       <c r="L182" s="34"/>
       <c r="M182" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="183" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A183" s="30">
-        <v>46505</v>
+        <v>46501</v>
       </c>
       <c r="B183" s="31"/>
-      <c r="C183" s="32">
-        <v>0.34375</v>
-      </c>
-      <c r="D183" s="32">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="E183" s="34" t="s">
+      <c r="C183" s="35">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D183" s="35">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="E183" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F183" s="34"/>
       <c r="G183" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="H183" s="33" t="s">
-        <v>54</v>
+        <v>200</v>
+      </c>
+      <c r="H183" s="34" t="s">
+        <v>89</v>
       </c>
       <c r="I183" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="J183" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="K183" s="33" t="s">
-        <v>23</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="J183" s="34"/>
+      <c r="K183" s="34"/>
       <c r="L183" s="34"/>
       <c r="M183" s="34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="184" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A184" s="30">
-        <v>46507</v>
+        <v>46505</v>
       </c>
       <c r="B184" s="31"/>
-      <c r="C184" s="32"/>
-      <c r="D184" s="32"/>
+      <c r="C184" s="32">
+        <v>0.34375</v>
+      </c>
+      <c r="D184" s="32">
+        <v>0.52083333333333337</v>
+      </c>
       <c r="E184" s="34" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F184" s="34"/>
       <c r="G184" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="H184" s="34"/>
-      <c r="I184" s="34"/>
-      <c r="J184" s="34"/>
-      <c r="K184" s="34"/>
+        <v>53</v>
+      </c>
+      <c r="H184" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="I184" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="J184" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="K184" s="33" t="s">
+        <v>23</v>
+      </c>
       <c r="L184" s="34"/>
       <c r="M184" s="34" t="s">
         <v>18</v>
@@ -11056,21 +11086,17 @@
         <v>46507</v>
       </c>
       <c r="B185" s="31"/>
-      <c r="C185" s="35"/>
-      <c r="D185" s="35"/>
-      <c r="E185" s="33" t="s">
-        <v>13</v>
+      <c r="C185" s="32"/>
+      <c r="D185" s="32"/>
+      <c r="E185" s="34" t="s">
+        <v>56</v>
       </c>
       <c r="F185" s="34"/>
       <c r="G185" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="H185" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="I185" s="33" t="s">
-        <v>26</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="H185" s="34"/>
+      <c r="I185" s="34"/>
       <c r="J185" s="34"/>
       <c r="K185" s="34"/>
       <c r="L185" s="34"/>
@@ -11080,136 +11106,128 @@
     </row>
     <row r="186" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A186" s="30">
-        <v>46511</v>
+        <v>46507</v>
       </c>
       <c r="B186" s="31"/>
-      <c r="C186" s="32">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D186" s="32">
-        <v>0.6875</v>
-      </c>
-      <c r="E186" s="34" t="s">
+      <c r="C186" s="35"/>
+      <c r="D186" s="35"/>
+      <c r="E186" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F186" s="34"/>
       <c r="G186" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="H186" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="I186" s="34" t="s">
-        <v>97</v>
+        <v>202</v>
+      </c>
+      <c r="H186" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="I186" s="33" t="s">
+        <v>26</v>
       </c>
       <c r="J186" s="34"/>
       <c r="K186" s="34"/>
       <c r="L186" s="34"/>
       <c r="M186" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="187" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A187" s="30">
-        <v>46512</v>
+        <v>46511</v>
       </c>
       <c r="B187" s="31"/>
       <c r="C187" s="32">
-        <v>0.35416666666666669</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D187" s="32">
-        <v>0.52083333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="E187" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F187" s="34"/>
       <c r="G187" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="H187" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="I187" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="J187" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="K187" s="33" t="s">
-        <v>23</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="H187" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="I187" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="J187" s="34"/>
+      <c r="K187" s="34"/>
       <c r="L187" s="34"/>
       <c r="M187" s="34" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="188" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A188" s="40">
-        <v>46513</v>
-      </c>
-      <c r="B188" s="41"/>
-      <c r="C188" s="42">
-        <v>0.625</v>
-      </c>
-      <c r="D188" s="42">
-        <v>0.6875</v>
-      </c>
-      <c r="E188" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="F188" s="41"/>
-      <c r="G188" s="41" t="s">
-        <v>75</v>
-      </c>
-      <c r="H188" s="34" t="s">
-        <v>50</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="188" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A188" s="30">
+        <v>46512</v>
+      </c>
+      <c r="B188" s="31"/>
+      <c r="C188" s="32">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D188" s="32">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E188" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F188" s="34"/>
+      <c r="G188" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="H188" s="33" t="s">
+        <v>20</v>
       </c>
       <c r="I188" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="J188" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="K188" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="L188" s="43"/>
+        <v>21</v>
+      </c>
+      <c r="J188" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="K188" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="L188" s="34"/>
       <c r="M188" s="34" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="189" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A189" s="30">
-        <v>46519</v>
-      </c>
-      <c r="B189" s="47"/>
-      <c r="C189" s="32">
-        <v>0.34375</v>
-      </c>
-      <c r="D189" s="32">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="E189" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="F189" s="34"/>
-      <c r="G189" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="H189" s="33" t="s">
-        <v>54</v>
+    <row r="189" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A189" s="40">
+        <v>46513</v>
+      </c>
+      <c r="B189" s="41"/>
+      <c r="C189" s="42">
+        <v>0.625</v>
+      </c>
+      <c r="D189" s="42">
+        <v>0.6875</v>
+      </c>
+      <c r="E189" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F189" s="41"/>
+      <c r="G189" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="H189" s="34" t="s">
+        <v>50</v>
       </c>
       <c r="I189" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="J189" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="K189" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="L189" s="34"/>
+      <c r="J189" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="K189" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="L189" s="43"/>
       <c r="M189" s="34" t="s">
         <v>18</v>
       </c>
@@ -11220,29 +11238,29 @@
       </c>
       <c r="B190" s="47"/>
       <c r="C190" s="32">
+        <v>0.34375</v>
+      </c>
+      <c r="D190" s="32">
         <v>0.52083333333333337</v>
       </c>
-      <c r="D190" s="32">
-        <v>0.54166666666666663</v>
-      </c>
       <c r="E190" s="34" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F190" s="34"/>
       <c r="G190" s="33" t="s">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="H190" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="I190" s="34" t="s">
-        <v>203</v>
-      </c>
-      <c r="J190" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K190" s="34" t="s">
-        <v>204</v>
+        <v>54</v>
+      </c>
+      <c r="I190" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="J190" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="K190" s="33" t="s">
+        <v>23</v>
       </c>
       <c r="L190" s="34"/>
       <c r="M190" s="34" t="s">
@@ -11255,28 +11273,30 @@
       </c>
       <c r="B191" s="47"/>
       <c r="C191" s="32">
-        <v>0.35416666666666669</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D191" s="32">
-        <v>0.5</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="E191" s="34" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="F191" s="34"/>
       <c r="G191" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="H191" s="34" t="s">
-        <v>15</v>
+        <v>91</v>
+      </c>
+      <c r="H191" s="33" t="s">
+        <v>58</v>
       </c>
       <c r="I191" s="34" t="s">
-        <v>16</v>
+        <v>203</v>
       </c>
       <c r="J191" s="34" t="s">
-        <v>144</v>
-      </c>
-      <c r="K191" s="34"/>
+        <v>17</v>
+      </c>
+      <c r="K191" s="34" t="s">
+        <v>204</v>
+      </c>
       <c r="L191" s="34"/>
       <c r="M191" s="34" t="s">
         <v>18</v>
@@ -11284,30 +11304,32 @@
     </row>
     <row r="192" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A192" s="30">
-        <v>46521</v>
+        <v>46519</v>
       </c>
       <c r="B192" s="47"/>
       <c r="C192" s="32">
         <v>0.35416666666666669</v>
       </c>
       <c r="D192" s="32">
-        <v>0.4375</v>
+        <v>0.5</v>
       </c>
       <c r="E192" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F192" s="34"/>
       <c r="G192" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="H192" s="34"/>
-      <c r="I192" s="33" t="s">
-        <v>51</v>
+        <v>14</v>
+      </c>
+      <c r="H192" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="I192" s="34" t="s">
+        <v>16</v>
       </c>
       <c r="J192" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K192" s="33"/>
+        <v>144</v>
+      </c>
+      <c r="K192" s="34"/>
       <c r="L192" s="34"/>
       <c r="M192" s="34" t="s">
         <v>18</v>
@@ -11315,70 +11337,66 @@
     </row>
     <row r="193" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A193" s="30">
-        <v>46522</v>
+        <v>46521</v>
       </c>
       <c r="B193" s="47"/>
-      <c r="C193" s="35">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D193" s="35">
-        <v>0.5</v>
-      </c>
-      <c r="E193" s="33" t="s">
+      <c r="C193" s="32">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D193" s="32">
+        <v>0.4375</v>
+      </c>
+      <c r="E193" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F193" s="34"/>
       <c r="G193" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="H193" s="33" t="s">
-        <v>46</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="H193" s="34"/>
       <c r="I193" s="33" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="J193" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="K193" s="34"/>
+        <v>17</v>
+      </c>
+      <c r="K193" s="33"/>
       <c r="L193" s="34"/>
       <c r="M193" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="194" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A194" s="30">
-        <v>46526</v>
+        <v>46522</v>
       </c>
       <c r="B194" s="47"/>
-      <c r="C194" s="32">
-        <v>0.34375</v>
-      </c>
-      <c r="D194" s="32">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="E194" s="34" t="s">
+      <c r="C194" s="35">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D194" s="35">
+        <v>0.5</v>
+      </c>
+      <c r="E194" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F194" s="34"/>
       <c r="G194" s="33" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="H194" s="33" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I194" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="J194" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="K194" s="33" t="s">
-        <v>23</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="J194" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="K194" s="34"/>
       <c r="L194" s="34"/>
       <c r="M194" s="34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="195" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -11386,23 +11404,31 @@
         <v>46526</v>
       </c>
       <c r="B195" s="47"/>
-      <c r="C195" s="32"/>
-      <c r="D195" s="32"/>
+      <c r="C195" s="32">
+        <v>0.34375</v>
+      </c>
+      <c r="D195" s="32">
+        <v>0.52083333333333337</v>
+      </c>
       <c r="E195" s="34" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F195" s="34"/>
       <c r="G195" s="33" t="s">
-        <v>205</v>
-      </c>
-      <c r="H195" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="I195" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="J195" s="34"/>
-      <c r="K195" s="34"/>
+        <v>53</v>
+      </c>
+      <c r="H195" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="I195" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="J195" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="K195" s="33" t="s">
+        <v>23</v>
+      </c>
       <c r="L195" s="34"/>
       <c r="M195" s="34" t="s">
         <v>18</v>
@@ -11410,34 +11436,26 @@
     </row>
     <row r="196" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A196" s="30">
-        <v>46533</v>
+        <v>46526</v>
       </c>
       <c r="B196" s="47"/>
-      <c r="C196" s="32">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D196" s="32">
-        <v>0.5</v>
-      </c>
+      <c r="C196" s="32"/>
+      <c r="D196" s="32"/>
       <c r="E196" s="34" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="F196" s="34"/>
       <c r="G196" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="H196" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="I196" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="J196" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="K196" s="33" t="s">
-        <v>23</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="H196" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="I196" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="J196" s="34"/>
+      <c r="K196" s="34"/>
       <c r="L196" s="34"/>
       <c r="M196" s="34" t="s">
         <v>18</v>
@@ -11445,45 +11463,57 @@
     </row>
     <row r="197" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A197" s="30">
-        <v>46534</v>
+        <v>46533</v>
       </c>
       <c r="B197" s="47"/>
-      <c r="C197" s="32"/>
-      <c r="D197" s="32"/>
+      <c r="C197" s="32">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D197" s="32">
+        <v>0.5</v>
+      </c>
       <c r="E197" s="34" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F197" s="34"/>
       <c r="G197" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="H197" s="34"/>
+        <v>99</v>
+      </c>
+      <c r="H197" s="33" t="s">
+        <v>100</v>
+      </c>
       <c r="I197" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="J197" s="34"/>
-      <c r="K197" s="34"/>
+        <v>35</v>
+      </c>
+      <c r="J197" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="K197" s="33" t="s">
+        <v>23</v>
+      </c>
       <c r="L197" s="34"/>
       <c r="M197" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="198" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A198" s="30">
-        <v>46535</v>
+        <v>46534</v>
       </c>
       <c r="B198" s="47"/>
       <c r="C198" s="32"/>
       <c r="D198" s="32"/>
       <c r="E198" s="34" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="F198" s="34"/>
       <c r="G198" s="33" t="s">
-        <v>206</v>
+        <v>145</v>
       </c>
       <c r="H198" s="34"/>
-      <c r="I198" s="34"/>
+      <c r="I198" s="33" t="s">
+        <v>63</v>
+      </c>
       <c r="J198" s="34"/>
       <c r="K198" s="34"/>
       <c r="L198" s="34"/>
@@ -11493,28 +11523,20 @@
     </row>
     <row r="199" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A199" s="30">
-        <v>46539</v>
+        <v>46535</v>
       </c>
       <c r="B199" s="47"/>
-      <c r="C199" s="32">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D199" s="32">
-        <v>0.6875</v>
-      </c>
+      <c r="C199" s="32"/>
+      <c r="D199" s="32"/>
       <c r="E199" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F199" s="34"/>
       <c r="G199" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="H199" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="I199" s="34" t="s">
-        <v>97</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="H199" s="34"/>
+      <c r="I199" s="34"/>
       <c r="J199" s="34"/>
       <c r="K199" s="34"/>
       <c r="L199" s="34"/>
@@ -11524,37 +11546,33 @@
     </row>
     <row r="200" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A200" s="30">
-        <v>46540</v>
+        <v>46539</v>
       </c>
       <c r="B200" s="47"/>
       <c r="C200" s="32">
-        <v>0.35416666666666669</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D200" s="32">
-        <v>0.52083333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="E200" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F200" s="34"/>
       <c r="G200" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="H200" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="I200" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="J200" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="K200" s="33" t="s">
-        <v>23</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="H200" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="I200" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="J200" s="34"/>
+      <c r="K200" s="34"/>
       <c r="L200" s="34"/>
       <c r="M200" s="34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="201" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -11566,25 +11584,27 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D201" s="32">
-        <v>0.5</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="E201" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F201" s="34"/>
       <c r="G201" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="H201" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="I201" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="J201" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K201" s="33"/>
+        <v>19</v>
+      </c>
+      <c r="H201" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="I201" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="J201" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="K201" s="33" t="s">
+        <v>23</v>
+      </c>
       <c r="L201" s="34"/>
       <c r="M201" s="34" t="s">
         <v>18</v>
@@ -11592,25 +11612,27 @@
     </row>
     <row r="202" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A202" s="30">
-        <v>46542</v>
+        <v>46540</v>
       </c>
       <c r="B202" s="47"/>
       <c r="C202" s="32">
         <v>0.35416666666666669</v>
       </c>
       <c r="D202" s="32">
-        <v>0.4375</v>
+        <v>0.5</v>
       </c>
       <c r="E202" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F202" s="34"/>
       <c r="G202" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="H202" s="34"/>
-      <c r="I202" s="33" t="s">
-        <v>51</v>
+        <v>14</v>
+      </c>
+      <c r="H202" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="I202" s="34" t="s">
+        <v>16</v>
       </c>
       <c r="J202" s="34" t="s">
         <v>17</v>
@@ -11627,224 +11649,224 @@
       </c>
       <c r="B203" s="47"/>
       <c r="C203" s="32">
-        <v>0.45833333333333331</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D203" s="32">
-        <v>0.66666666666666663</v>
+        <v>0.4375</v>
       </c>
       <c r="E203" s="34" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F203" s="34"/>
       <c r="G203" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="H203" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="I203" s="34" t="s">
-        <v>16</v>
+        <v>49</v>
+      </c>
+      <c r="H203" s="34"/>
+      <c r="I203" s="33" t="s">
+        <v>51</v>
       </c>
       <c r="J203" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="K203" s="34" t="s">
-        <v>208</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="K203" s="33"/>
       <c r="L203" s="34"/>
       <c r="M203" s="34" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="204" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A204" s="48">
+      <c r="A204" s="30">
+        <v>46542</v>
+      </c>
+      <c r="B204" s="47"/>
+      <c r="C204" s="32">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D204" s="32">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E204" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="F204" s="34"/>
+      <c r="G204" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="H204" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="I204" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="J204" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="K204" s="34" t="s">
+        <v>208</v>
+      </c>
+      <c r="L204" s="34"/>
+      <c r="M204" s="34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="205" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A205" s="48">
         <v>46543</v>
       </c>
-      <c r="B204" s="49"/>
-      <c r="C204" s="50">
+      <c r="B205" s="49"/>
+      <c r="C205" s="50">
         <v>0.33333333333333331</v>
       </c>
-      <c r="D204" s="50">
+      <c r="D205" s="50">
         <v>0.5</v>
       </c>
-      <c r="E204" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="F204" s="51"/>
-      <c r="G204" s="37" t="s">
+      <c r="E205" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="F205" s="51"/>
+      <c r="G205" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="H204" s="33" t="s">
+      <c r="H205" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="I204" s="33" t="s">
+      <c r="I205" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="J204" s="51" t="s">
+      <c r="J205" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="K204" s="51"/>
-      <c r="L204" s="51"/>
-      <c r="M204" s="34" t="s">
+      <c r="K205" s="51"/>
+      <c r="L205" s="51"/>
+      <c r="M205" s="34" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="205" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A205" s="52">
+    <row r="206" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A206" s="52">
         <v>46545</v>
       </c>
-      <c r="B205" s="53"/>
-      <c r="C205" s="54">
+      <c r="B206" s="53"/>
+      <c r="C206" s="54">
         <v>0.625</v>
       </c>
-      <c r="D205" s="54">
+      <c r="D206" s="54">
         <v>0.6875</v>
       </c>
-      <c r="E205" s="53" t="s">
-        <v>13</v>
-      </c>
-      <c r="F205" s="53"/>
-      <c r="G205" s="53" t="s">
+      <c r="E206" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="F206" s="53"/>
+      <c r="G206" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="H205" s="34" t="s">
+      <c r="H206" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="I205" s="33" t="s">
+      <c r="I206" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="J205" s="53" t="s">
+      <c r="J206" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="K205" s="53" t="s">
+      <c r="K206" s="53" t="s">
         <v>123</v>
       </c>
-      <c r="L205" s="38"/>
-      <c r="M205" s="34" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="206" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A206" s="48">
-        <v>46549</v>
-      </c>
-      <c r="B206" s="49"/>
-      <c r="C206" s="50"/>
-      <c r="D206" s="50"/>
-      <c r="E206" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="F206" s="51"/>
-      <c r="G206" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="H206" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="I206" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="J206" s="51"/>
-      <c r="K206" s="51"/>
-      <c r="L206" s="51"/>
+      <c r="L206" s="38"/>
       <c r="M206" s="34" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="207" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A207" s="48">
-        <v>46552</v>
-      </c>
-      <c r="B207" s="55" t="s">
-        <v>209</v>
-      </c>
-      <c r="C207" s="50">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D207" s="50">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="E207" s="51" t="s">
-        <v>56</v>
+        <v>46549</v>
+      </c>
+      <c r="B207" s="49"/>
+      <c r="C207" s="50"/>
+      <c r="D207" s="50"/>
+      <c r="E207" s="37" t="s">
+        <v>13</v>
       </c>
       <c r="F207" s="51"/>
       <c r="G207" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="H207" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="I207" s="34" t="s">
-        <v>16</v>
+        <v>52</v>
+      </c>
+      <c r="H207" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="I207" s="33" t="s">
+        <v>26</v>
       </c>
       <c r="J207" s="51"/>
       <c r="K207" s="51"/>
       <c r="L207" s="51"/>
       <c r="M207" s="34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="208" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A208" s="48">
-        <v>46554</v>
-      </c>
-      <c r="B208" s="49"/>
-      <c r="C208" s="56">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D208" s="56">
-        <v>0.54166666666666663</v>
+        <v>46552</v>
+      </c>
+      <c r="B208" s="55" t="s">
+        <v>209</v>
+      </c>
+      <c r="C208" s="50">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D208" s="50">
+        <v>0.64583333333333337</v>
       </c>
       <c r="E208" s="51" t="s">
         <v>56</v>
       </c>
       <c r="F208" s="51"/>
       <c r="G208" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="H208" s="33" t="s">
-        <v>58</v>
+        <v>210</v>
+      </c>
+      <c r="H208" s="34" t="s">
+        <v>46</v>
       </c>
       <c r="I208" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="J208" s="51" t="s">
-        <v>17</v>
-      </c>
-      <c r="K208" s="51" t="s">
-        <v>211</v>
-      </c>
+      <c r="J208" s="51"/>
+      <c r="K208" s="51"/>
       <c r="L208" s="51"/>
       <c r="M208" s="34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="209" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A209" s="48">
-        <v>46563</v>
+        <v>46554</v>
       </c>
       <c r="B209" s="49"/>
       <c r="C209" s="56">
-        <v>0.35416666666666669</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D209" s="56">
-        <v>0.4375</v>
-      </c>
-      <c r="E209" s="34" t="s">
-        <v>13</v>
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="E209" s="51" t="s">
+        <v>56</v>
       </c>
       <c r="F209" s="51"/>
       <c r="G209" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="H209" s="34"/>
-      <c r="I209" s="33" t="s">
-        <v>51</v>
+        <v>91</v>
+      </c>
+      <c r="H209" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="I209" s="34" t="s">
+        <v>16</v>
       </c>
       <c r="J209" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="K209" s="37"/>
+      <c r="K209" s="51" t="s">
+        <v>211</v>
+      </c>
       <c r="L209" s="51"/>
       <c r="M209" s="34" t="s">
         <v>18</v>
@@ -11852,24 +11874,30 @@
     </row>
     <row r="210" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A210" s="48">
-        <v>46568</v>
+        <v>46563</v>
       </c>
       <c r="B210" s="49"/>
-      <c r="C210" s="56"/>
-      <c r="D210" s="56"/>
-      <c r="E210" s="51" t="s">
+      <c r="C210" s="56">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D210" s="56">
+        <v>0.4375</v>
+      </c>
+      <c r="E210" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F210" s="51"/>
       <c r="G210" s="37" t="s">
-        <v>212</v>
+        <v>49</v>
       </c>
       <c r="H210" s="34"/>
-      <c r="I210" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="J210" s="51"/>
-      <c r="K210" s="51"/>
+      <c r="I210" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="J210" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="K210" s="37"/>
       <c r="L210" s="51"/>
       <c r="M210" s="34" t="s">
         <v>18</v>
@@ -11877,22 +11905,20 @@
     </row>
     <row r="211" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A211" s="48">
-        <v>46592</v>
+        <v>46568</v>
       </c>
       <c r="B211" s="49"/>
       <c r="C211" s="56"/>
       <c r="D211" s="56"/>
       <c r="E211" s="51" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F211" s="51"/>
       <c r="G211" s="37" t="s">
-        <v>213</v>
-      </c>
-      <c r="H211" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="I211" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="H211" s="34"/>
+      <c r="I211" s="34" t="s">
         <v>26</v>
       </c>
       <c r="J211" s="51"/>
@@ -11904,17 +11930,17 @@
     </row>
     <row r="212" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A212" s="48">
-        <v>46597</v>
+        <v>46592</v>
       </c>
       <c r="B212" s="49"/>
-      <c r="C212" s="50"/>
-      <c r="D212" s="50"/>
-      <c r="E212" s="37" t="s">
-        <v>13</v>
+      <c r="C212" s="56"/>
+      <c r="D212" s="56"/>
+      <c r="E212" s="51" t="s">
+        <v>56</v>
       </c>
       <c r="F212" s="51"/>
       <c r="G212" s="37" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H212" s="33" t="s">
         <v>25</v>
@@ -11931,20 +11957,24 @@
     </row>
     <row r="213" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A213" s="48">
-        <v>46623</v>
+        <v>46597</v>
       </c>
       <c r="B213" s="49"/>
-      <c r="C213" s="56"/>
-      <c r="D213" s="56"/>
-      <c r="E213" s="51" t="s">
+      <c r="C213" s="50"/>
+      <c r="D213" s="50"/>
+      <c r="E213" s="37" t="s">
         <v>13</v>
       </c>
       <c r="F213" s="51"/>
       <c r="G213" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="H213" s="34"/>
-      <c r="I213" s="34"/>
+        <v>214</v>
+      </c>
+      <c r="H213" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="I213" s="33" t="s">
+        <v>26</v>
+      </c>
       <c r="J213" s="51"/>
       <c r="K213" s="51"/>
       <c r="L213" s="51"/>
@@ -11954,17 +11984,17 @@
     </row>
     <row r="214" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A214" s="48">
-        <v>46630</v>
+        <v>46623</v>
       </c>
       <c r="B214" s="49"/>
       <c r="C214" s="56"/>
       <c r="D214" s="56"/>
       <c r="E214" s="51" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F214" s="51"/>
       <c r="G214" s="37" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H214" s="34"/>
       <c r="I214" s="34"/>
@@ -11976,10 +12006,27 @@
       </c>
     </row>
     <row r="215" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A215" s="28"/>
-      <c r="B215" s="25"/>
-      <c r="J215" s="26"/>
-      <c r="K215" s="26"/>
+      <c r="A215" s="48">
+        <v>46630</v>
+      </c>
+      <c r="B215" s="49"/>
+      <c r="C215" s="56"/>
+      <c r="D215" s="56"/>
+      <c r="E215" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="F215" s="51"/>
+      <c r="G215" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="H215" s="34"/>
+      <c r="I215" s="34"/>
+      <c r="J215" s="51"/>
+      <c r="K215" s="51"/>
+      <c r="L215" s="51"/>
+      <c r="M215" s="34" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="216" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A216" s="28"/>
@@ -16685,19 +16732,25 @@
       <c r="J999" s="26"/>
       <c r="K999" s="26"/>
     </row>
+    <row r="1000" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1000" s="28"/>
+      <c r="B1000" s="25"/>
+      <c r="J1000" s="26"/>
+      <c r="K1000" s="26"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M214" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M214">
-      <sortCondition ref="A1:A214"/>
+  <autoFilter ref="A1:M215" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M215">
+      <sortCondition ref="A1:A215"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M214">
-    <sortCondition ref="A180:A214"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M215">
+    <sortCondition ref="A181:A215"/>
   </sortState>
   <customSheetViews>
     <customSheetView guid="{8F656852-D603-4744-997A-DE0F92A7585E}" filter="1" showAutoFilter="1">
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-      <autoFilter ref="A1:M198" xr:uid="{5B42E301-AFBF-4844-8441-330416FFB861}">
+      <autoFilter ref="A1:M198" xr:uid="{9237A487-101A-C944-BC11-9A705AB0315F}">
         <filterColumn colId="6">
           <filters>
             <filter val="GSPP Action Planning Implementation Pathways Region E Day 1  🌁"/>
@@ -16713,25 +16766,25 @@
     </customSheetView>
   </customSheetViews>
   <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" sqref="I2:I37 I181:I214 I161:I179 I39:I159" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I37 I182:I215 I162:I180 I39:I160" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"BARRENECHEA, ED,DABAGYAN, ESTHER,ELIAS, MICHELLE,GERTNER, BEN,KASAMANYAN, HOVIK,LE, NANCY,PRICE, TOMOKO,PRAKASH, REKHA,SERRANO, NANCY"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M204:M214 L2:M203" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M205:M215 L2:M204" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E209 E2:E203" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E210 E2:E204" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"● Confirmed,◆ Hold, ☓ Cancel"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I180" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I181" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"BARRENECHEA, ED,DABAGYAN, ESTHER,ELIAS, MICHELLE,GERTNER, BEN,KASAMANYAN, HOVIK,LE, NANCY,PRICE, TOMOKO,PRAKASH, REKHA,SERRANO, NANCY,DE LA TORRE, JUDY"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I160" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I161" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"BARRENECHEA, ED,DABAGYAN, ESTHER,ELIAS, MICHELLE,GERTNER, BEN,KASAMANYAN, HOVIK,LE, NANCY,PRICE, TOMOKO,PRAKASH, REKHA,SERRANO, NANCY,FRANK, JUSTIN"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="I38" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"BARRENECHEA, ED,DABAGYAN, ESTHER,ELIAS, MICHELLE,GERTNER, BEN,KASAMANYAN, HOVIK,LE, NANCY,PRICE, TOMOKO,PRAKASH, REKHA,SERRANO, NANCY,GOLDEN, MICHAEL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H214" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H215" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"All CTE-LL staff,Coaches + Advisors,CTE Advisors,CTE Teachers,CTE-LL Coordinators,CTE-LL Leads,GSPP School Staff,LL Coaches,LL Leads,LL Teachers,LL Team,MiSiS Designees,School Administrators,School Counselors,Select CTE-LL Staff"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16740,7 +16793,7 @@
     <hyperlink ref="K62" r:id="rId2" xr:uid="{98622C98-31A5-41DD-B43F-A720A440A5A9}"/>
     <hyperlink ref="K67" r:id="rId3" xr:uid="{C9D19773-6F55-4BAF-82A9-D84E17C370F2}"/>
     <hyperlink ref="K85" r:id="rId4" xr:uid="{C4884129-06F2-48DB-B3E1-78C695AA16E7}"/>
-    <hyperlink ref="K90" r:id="rId5" xr:uid="{4FA583BB-674C-4565-88E5-E0217B2A9BA1}"/>
+    <hyperlink ref="K91" r:id="rId5" xr:uid="{4FA583BB-674C-4565-88E5-E0217B2A9BA1}"/>
   </hyperlinks>
   <printOptions gridLines="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -19295,12 +19348,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f51bf047-e00d-4111-9acd-3b648a8df45c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb5933e1-39c5-43d4-bb0e-9e063605db7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19533,20 +19588,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f51bf047-e00d-4111-9acd-3b648a8df45c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb5933e1-39c5-43d4-bb0e-9e063605db7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE723B2C-1BFC-4804-B7F3-9EA38C1D43D6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B318E1E-A80F-4091-9E4D-E3248AE98C97}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f51bf047-e00d-4111-9acd-3b648a8df45c"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="bb5933e1-39c5-43d4-bb0e-9e063605db7e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -19571,18 +19633,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B318E1E-A80F-4091-9E4D-E3248AE98C97}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE723B2C-1BFC-4804-B7F3-9EA38C1D43D6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="f51bf047-e00d-4111-9acd-3b648a8df45c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="bb5933e1-39c5-43d4-bb0e-9e063605db7e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>